--- a/source-data/trading-data.xlsx
+++ b/source-data/trading-data.xlsx
@@ -21646,7 +21646,7 @@
         <v>26.5</v>
       </c>
       <c r="D506" s="3">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="E506" s="3">
         <v>1100</v>
@@ -24850,10 +24850,10 @@
         <v>32.5</v>
       </c>
       <c r="D667" s="3">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="E667" s="3">
-        <v>1000</v>
+        <v>1250</v>
       </c>
       <c r="F667" s="3">
         <v>4000</v>
@@ -25742,7 +25742,7 @@
         <v>25</v>
       </c>
       <c r="D712" s="3">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E712" s="3">
         <v>700</v>

--- a/source-data/trading-data.xlsx
+++ b/source-data/trading-data.xlsx
@@ -2,9 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R2a60f105029f424e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pets" sheetId="2" r:id="R8cdea5118bb64ba9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pet Wear" sheetId="3" r:id="R5d4f0856ef164f85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R7968ab44598f474f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pets" sheetId="2" r:id="Rde8f79b9e6884248"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pet Wear" sheetId="3" r:id="R5d8d4aceaf864a16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eggs" sheetId="4" r:id="Rf0cc971cd576435b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Toys" sheetId="5" r:id="Ra95b80afe9dc4ae9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,15 +17,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <x:numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <x:numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <x:numFmt numFmtId="178" formatCode="0.########"/>
     <x:numFmt numFmtId="200" formatCode="0.##"/>
+    <x:numFmt numFmtId="201" formatCode="0.###"/>
   </x:numFmts>
-  <x:fonts count="29">
+  <x:fonts count="31">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -183,8 +186,18 @@
       <x:color rgb="FF334155"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0F172A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF92400E"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="42">
+  <x:fills count="46">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -389,6 +402,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFBEB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFEF3C7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFBEB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF59E0B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -846,7 +879,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="170">
+  <x:cellXfs count="240">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -1285,6 +1318,164 @@
     <x:xf numFmtId="0" fontId="27" fillId="41" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="42" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="42" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="42" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="42" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="44" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="44" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="44" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="44" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="44" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="44" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="44" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="44" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="44" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="44" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="44" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="44" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="29" fillId="45" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="29" fillId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="45" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="45" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="45" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="29" fillId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="29" fillId="45" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="29" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="29" fillId="42" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="30" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="30" fillId="42" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1337,7 +1528,7 @@
     <x:cellStyle name="40% - Accent6" xfId="47"/>
     <x:cellStyle name="60% - Accent6" xfId="48"/>
   </x:cellStyles>
-  <x:dxfs count="19">
+  <x:dxfs count="23">
     <x:dxf>
       <x:fill>
         <x:patternFill>
@@ -1518,14 +1709,42 @@
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE0F2FE"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
+          <x:bgColor rgb="FFE0F2FE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE0F2FE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE0F2FE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE0F2FE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill>
           <x:bgColor rgb="FFE0F2FE"/>
         </x:patternFill>
       </x:fill>
@@ -1862,6 +2081,22 @@
         <x:v>Review source-data/trading-data-validation.json after generation for invalid values, unmatched items, duplicates, and image warnings.</x:v>
       </x:c>
     </x:row>
+    <x:row r="19" ht="38" customHeight="1">
+      <x:c r="A19" s="202" t="str">
+        <x:v>Eggs and Toys</x:v>
+      </x:c>
+      <x:c r="B19" s="208" t="str">
+        <x:v>Edit GCash values in the Eggs and Toys sheets. Use only GCASH REGULAR VALUE; leave unavailable values blank.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="38" customHeight="1">
+      <x:c r="A20" s="203" t="str">
+        <x:v>Editable columns</x:v>
+      </x:c>
+      <x:c r="B20" s="209" t="str">
+        <x:v>Yellow GCash cells are maintained manually by CSBT. Elve Shark cells are reference snapshots; generated website values come from the separate Elve updater.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A12:F12"/>
@@ -21696,7 +21931,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63ebaa8d309b4aba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc3ad9d67a2c41fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38642,7 +38877,9145 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6178b68faac44ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb632e63c44054df8"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="48" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="221" t="str">
+        <x:v>ITEM NAME</x:v>
+      </x:c>
+      <x:c r="B1" s="222" t="str">
+        <x:v>ITEM IMAGE</x:v>
+      </x:c>
+      <x:c r="C1" s="222" t="str">
+        <x:v>GCASH REGULAR VALUE</x:v>
+      </x:c>
+      <x:c r="D1" s="223" t="str">
+        <x:v>ELVE SHARK REGULAR VALUE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="A2" s="230" t="str">
+        <x:v>Admin Abuse Egg</x:v>
+      </x:c>
+      <x:c r="B2" s="230" t="str">
+        <x:v>/images/pets/Admin Abuse Egg.png</x:v>
+      </x:c>
+      <x:c r="C2" s="238"/>
+      <x:c r="D2" s="234" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19" customHeight="1">
+      <x:c r="A3" s="230" t="str">
+        <x:v>Aussie Egg</x:v>
+      </x:c>
+      <x:c r="B3" s="230" t="str">
+        <x:v>/images/pets/Aussie Egg.png</x:v>
+      </x:c>
+      <x:c r="C3" s="238"/>
+      <x:c r="D3" s="234" t="n">
+        <x:v>5.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="19" customHeight="1">
+      <x:c r="A4" s="230" t="str">
+        <x:v>Aztec Egg</x:v>
+      </x:c>
+      <x:c r="B4" s="230" t="str">
+        <x:v>/images/pets/Aztec Egg.png</x:v>
+      </x:c>
+      <x:c r="C4" s="238"/>
+      <x:c r="D4" s="234" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="19" customHeight="1">
+      <x:c r="A5" s="230" t="str">
+        <x:v>Basic Egg</x:v>
+      </x:c>
+      <x:c r="B5" s="230" t="str">
+        <x:v>/images/pets/Basic Egg.png</x:v>
+      </x:c>
+      <x:c r="C5" s="238"/>
+      <x:c r="D5" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="19" customHeight="1">
+      <x:c r="A6" s="230" t="str">
+        <x:v>Blue Egg</x:v>
+      </x:c>
+      <x:c r="B6" s="230" t="str">
+        <x:v>/images/pets/Blue Egg.png</x:v>
+      </x:c>
+      <x:c r="C6" s="238"/>
+      <x:c r="D6" s="234" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="19" customHeight="1">
+      <x:c r="A7" s="230" t="str">
+        <x:v>Christmas Egg</x:v>
+      </x:c>
+      <x:c r="B7" s="230" t="str">
+        <x:v>/images/pets/Christmas Egg.png</x:v>
+      </x:c>
+      <x:c r="C7" s="238"/>
+      <x:c r="D7" s="234" t="n">
+        <x:v>17.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="19" customHeight="1">
+      <x:c r="A8" s="230" t="str">
+        <x:v>Christmas Future Egg</x:v>
+      </x:c>
+      <x:c r="B8" s="230" t="str">
+        <x:v>/images/pets/Christmas Future Egg.png</x:v>
+      </x:c>
+      <x:c r="C8" s="238"/>
+      <x:c r="D8" s="234" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="19" customHeight="1">
+      <x:c r="A9" s="230" t="str">
+        <x:v>Cracked Egg</x:v>
+      </x:c>
+      <x:c r="B9" s="230" t="str">
+        <x:v>/images/pets/Cracked Egg.png</x:v>
+      </x:c>
+      <x:c r="C9" s="238"/>
+      <x:c r="D9" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="19" customHeight="1">
+      <x:c r="A10" s="230" t="str">
+        <x:v>Crystal Egg</x:v>
+      </x:c>
+      <x:c r="B10" s="230" t="str">
+        <x:v>/images/pets/Crystal Egg.png</x:v>
+      </x:c>
+      <x:c r="C10" s="238"/>
+      <x:c r="D10" s="234" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="19" customHeight="1">
+      <x:c r="A11" s="230" t="str">
+        <x:v>Danger Egg</x:v>
+      </x:c>
+      <x:c r="B11" s="230" t="str">
+        <x:v>/images/pets/Danger Egg.png</x:v>
+      </x:c>
+      <x:c r="C11" s="238"/>
+      <x:c r="D11" s="234" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="19" customHeight="1">
+      <x:c r="A12" s="230" t="str">
+        <x:v>Desert Egg</x:v>
+      </x:c>
+      <x:c r="B12" s="230" t="str">
+        <x:v>/images/pets/Desert Egg.png</x:v>
+      </x:c>
+      <x:c r="C12" s="238"/>
+      <x:c r="D12" s="234" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="19" customHeight="1">
+      <x:c r="A13" s="230" t="str">
+        <x:v>Diamond Egg</x:v>
+      </x:c>
+      <x:c r="B13" s="230" t="str">
+        <x:v>/images/pets/Diamond Egg.png</x:v>
+      </x:c>
+      <x:c r="C13" s="238"/>
+      <x:c r="D13" s="234" t="n">
+        <x:v>0.17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="19" customHeight="1">
+      <x:c r="A14" s="230" t="str">
+        <x:v>Easter 2020 Egg</x:v>
+      </x:c>
+      <x:c r="B14" s="230" t="str">
+        <x:v>/images/pets/Easter 2020 Egg.png</x:v>
+      </x:c>
+      <x:c r="C14" s="238"/>
+      <x:c r="D14" s="234" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="19" customHeight="1">
+      <x:c r="A15" s="230" t="str">
+        <x:v>Endangered Egg</x:v>
+      </x:c>
+      <x:c r="B15" s="230" t="str">
+        <x:v>/images/pets/Endangered Egg.png</x:v>
+      </x:c>
+      <x:c r="C15" s="238"/>
+      <x:c r="D15" s="234" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="19" customHeight="1">
+      <x:c r="A16" s="230" t="str">
+        <x:v>Farm Egg</x:v>
+      </x:c>
+      <x:c r="B16" s="230" t="str">
+        <x:v>/images/pets/Farm Egg.png</x:v>
+      </x:c>
+      <x:c r="C16" s="238"/>
+      <x:c r="D16" s="234" t="n">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="19" customHeight="1">
+      <x:c r="A17" s="230" t="str">
+        <x:v>Fool Egg</x:v>
+      </x:c>
+      <x:c r="B17" s="230" t="str">
+        <x:v>/images/pets/Fool Egg.png</x:v>
+      </x:c>
+      <x:c r="C17" s="238"/>
+      <x:c r="D17" s="234" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="19" customHeight="1">
+      <x:c r="A18" s="230" t="str">
+        <x:v>Fossil Egg</x:v>
+      </x:c>
+      <x:c r="B18" s="230" t="str">
+        <x:v>/images/pets/Fossil Egg.png</x:v>
+      </x:c>
+      <x:c r="C18" s="238"/>
+      <x:c r="D18" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="19" customHeight="1">
+      <x:c r="A19" s="230" t="str">
+        <x:v>Garden Egg</x:v>
+      </x:c>
+      <x:c r="B19" s="230" t="str">
+        <x:v>/images/pets/Garden Egg.png</x:v>
+      </x:c>
+      <x:c r="C19" s="238"/>
+      <x:c r="D19" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="19" customHeight="1">
+      <x:c r="A20" s="230" t="str">
+        <x:v>Golden Egg</x:v>
+      </x:c>
+      <x:c r="B20" s="230" t="str">
+        <x:v>/images/pets/Golden Egg.png</x:v>
+      </x:c>
+      <x:c r="C20" s="238"/>
+      <x:c r="D20" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="19" customHeight="1">
+      <x:c r="A21" s="230" t="str">
+        <x:v>Japan Egg</x:v>
+      </x:c>
+      <x:c r="B21" s="230" t="str">
+        <x:v>/images/pets/Japan Egg.png</x:v>
+      </x:c>
+      <x:c r="C21" s="238"/>
+      <x:c r="D21" s="234" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="19" customHeight="1">
+      <x:c r="A22" s="230" t="str">
+        <x:v>Jungle Egg</x:v>
+      </x:c>
+      <x:c r="B22" s="230" t="str">
+        <x:v>/images/pets/Jungle Egg.png</x:v>
+      </x:c>
+      <x:c r="C22" s="238"/>
+      <x:c r="D22" s="234" t="n">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="19" customHeight="1">
+      <x:c r="A23" s="230" t="str">
+        <x:v>Moon Egg</x:v>
+      </x:c>
+      <x:c r="B23" s="230" t="str">
+        <x:v>/images/pets/Moon Egg.png</x:v>
+      </x:c>
+      <x:c r="C23" s="238"/>
+      <x:c r="D23" s="234" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="19" customHeight="1">
+      <x:c r="A24" s="230" t="str">
+        <x:v>Mythic Egg</x:v>
+      </x:c>
+      <x:c r="B24" s="230" t="str">
+        <x:v>/images/pets/Mythic Egg.png</x:v>
+      </x:c>
+      <x:c r="C24" s="238"/>
+      <x:c r="D24" s="234" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="19" customHeight="1">
+      <x:c r="A25" s="230" t="str">
+        <x:v>Ocean Egg</x:v>
+      </x:c>
+      <x:c r="B25" s="230" t="str">
+        <x:v>/images/pets/Ocean Egg.png</x:v>
+      </x:c>
+      <x:c r="C25" s="238"/>
+      <x:c r="D25" s="234" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="19" customHeight="1">
+      <x:c r="A26" s="230" t="str">
+        <x:v>Pet Egg</x:v>
+      </x:c>
+      <x:c r="B26" s="230" t="str">
+        <x:v>/images/pets/Pet Egg.png</x:v>
+      </x:c>
+      <x:c r="C26" s="238"/>
+      <x:c r="D26" s="234" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="19" customHeight="1">
+      <x:c r="A27" s="230" t="str">
+        <x:v>Pink Egg</x:v>
+      </x:c>
+      <x:c r="B27" s="230" t="str">
+        <x:v>/images/pets/Pink Egg.png</x:v>
+      </x:c>
+      <x:c r="C27" s="238"/>
+      <x:c r="D27" s="234" t="n">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="19" customHeight="1">
+      <x:c r="A28" s="230" t="str">
+        <x:v>Retired Egg</x:v>
+      </x:c>
+      <x:c r="B28" s="230" t="str">
+        <x:v>/images/pets/Retired Egg.png</x:v>
+      </x:c>
+      <x:c r="C28" s="238"/>
+      <x:c r="D28" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="19" customHeight="1">
+      <x:c r="A29" s="230" t="str">
+        <x:v>Royal Aztec Egg</x:v>
+      </x:c>
+      <x:c r="B29" s="230" t="str">
+        <x:v>/images/pets/Royal Aztec Egg.png</x:v>
+      </x:c>
+      <x:c r="C29" s="238"/>
+      <x:c r="D29" s="234" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="19" customHeight="1">
+      <x:c r="A30" s="230" t="str">
+        <x:v>Royal Desert Egg</x:v>
+      </x:c>
+      <x:c r="B30" s="230" t="str">
+        <x:v>/images/pets/Royal Desert Egg.png</x:v>
+      </x:c>
+      <x:c r="C30" s="238"/>
+      <x:c r="D30" s="234" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="19" customHeight="1">
+      <x:c r="A31" s="230" t="str">
+        <x:v>Royal Egg</x:v>
+      </x:c>
+      <x:c r="B31" s="230" t="str">
+        <x:v>/images/pets/Royal Egg.png</x:v>
+      </x:c>
+      <x:c r="C31" s="238"/>
+      <x:c r="D31" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="19" customHeight="1">
+      <x:c r="A32" s="230" t="str">
+        <x:v>Royal Moon Egg</x:v>
+      </x:c>
+      <x:c r="B32" s="230" t="str">
+        <x:v>/images/pets/Royal Moon Egg.png</x:v>
+      </x:c>
+      <x:c r="C32" s="238"/>
+      <x:c r="D32" s="234" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="19" customHeight="1">
+      <x:c r="A33" s="230" t="str">
+        <x:v>Safari Egg</x:v>
+      </x:c>
+      <x:c r="B33" s="230" t="str">
+        <x:v>/images/pets/Safari Egg.png</x:v>
+      </x:c>
+      <x:c r="C33" s="238"/>
+      <x:c r="D33" s="234" t="n">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="19" customHeight="1">
+      <x:c r="A34" s="230" t="str">
+        <x:v>Southeast Asia Egg</x:v>
+      </x:c>
+      <x:c r="B34" s="230" t="str">
+        <x:v>/images/pets/Southeast Asia Egg.png</x:v>
+      </x:c>
+      <x:c r="C34" s="238"/>
+      <x:c r="D34" s="234" t="n">
+        <x:v>0.17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="19" customHeight="1">
+      <x:c r="A35" s="230" t="str">
+        <x:v>Urban Egg</x:v>
+      </x:c>
+      <x:c r="B35" s="230" t="str">
+        <x:v>/images/pets/Urban Egg.png</x:v>
+      </x:c>
+      <x:c r="C35" s="238"/>
+      <x:c r="D35" s="234" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="19" customHeight="1">
+      <x:c r="A36" s="230" t="str">
+        <x:v>Woodland Egg</x:v>
+      </x:c>
+      <x:c r="B36" s="230" t="str">
+        <x:v>/images/pets/Woodland Egg.png</x:v>
+      </x:c>
+      <x:c r="C36" s="238"/>
+      <x:c r="D36" s="234" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="19" customHeight="1">
+      <x:c r="A37" s="230" t="str">
+        <x:v>Wrapped Doll</x:v>
+      </x:c>
+      <x:c r="B37" s="230" t="str">
+        <x:v>/images/pets/Wrapped Doll.png</x:v>
+      </x:c>
+      <x:c r="C37" s="238"/>
+      <x:c r="D37" s="234" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="19" customHeight="1">
+      <x:c r="A38" s="231" t="str">
+        <x:v>Zodiac Minion Egg</x:v>
+      </x:c>
+      <x:c r="B38" s="231" t="str">
+        <x:v>/images/pets/Zodiac Minion Egg.png</x:v>
+      </x:c>
+      <x:c r="C38" s="239"/>
+      <x:c r="D38" s="235" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:conditionalFormatting sqref="A2:B38">
+    <x:cfRule type="expression" dxfId="19" priority="1">
+      <x:formula>MOD(ROW(),2)=0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="D2:D38">
+    <x:cfRule type="expression" dxfId="20" priority="2">
+      <x:formula>MOD(ROW(),2)=0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="48" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="221" t="str">
+        <x:v>ITEM NAME</x:v>
+      </x:c>
+      <x:c r="B1" s="222" t="str">
+        <x:v>ITEM IMAGE</x:v>
+      </x:c>
+      <x:c r="C1" s="222" t="str">
+        <x:v>GCASH REGULAR VALUE</x:v>
+      </x:c>
+      <x:c r="D1" s="223" t="str">
+        <x:v>ELVE SHARK REGULAR VALUE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="A2" s="230" t="str">
+        <x:v>2D Bone Chew Toy</x:v>
+      </x:c>
+      <x:c r="B2" s="230" t="str">
+        <x:v>/images/pets/2D Bone Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C2" s="238"/>
+      <x:c r="D2" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19" customHeight="1">
+      <x:c r="A3" s="230" t="str">
+        <x:v>2D Pencil Rattle</x:v>
+      </x:c>
+      <x:c r="B3" s="230" t="str">
+        <x:v>/images/pets/2D Pencil Rattle.png</x:v>
+      </x:c>
+      <x:c r="C3" s="238"/>
+      <x:c r="D3" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="19" customHeight="1">
+      <x:c r="A4" s="230" t="str">
+        <x:v>Abyss Propeller</x:v>
+      </x:c>
+      <x:c r="B4" s="230" t="str">
+        <x:v>/images/pets/Abyss Propeller.png</x:v>
+      </x:c>
+      <x:c r="C4" s="238"/>
+      <x:c r="D4" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="19" customHeight="1">
+      <x:c r="A5" s="230" t="str">
+        <x:v>Accordion</x:v>
+      </x:c>
+      <x:c r="B5" s="230" t="str">
+        <x:v>/images/pets/Accordion.png</x:v>
+      </x:c>
+      <x:c r="C5" s="238"/>
+      <x:c r="D5" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="19" customHeight="1">
+      <x:c r="A6" s="230" t="str">
+        <x:v>Ace Flag</x:v>
+      </x:c>
+      <x:c r="B6" s="230" t="str">
+        <x:v>/images/pets/Ace Flag.png</x:v>
+      </x:c>
+      <x:c r="C6" s="238"/>
+      <x:c r="D6" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="19" customHeight="1">
+      <x:c r="A7" s="230" t="str">
+        <x:v>Acorn Plushie</x:v>
+      </x:c>
+      <x:c r="B7" s="230" t="str">
+        <x:v>/images/pets/Acorn Plushie.png</x:v>
+      </x:c>
+      <x:c r="C7" s="238"/>
+      <x:c r="D7" s="234" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="19" customHeight="1">
+      <x:c r="A8" s="230" t="str">
+        <x:v>Agender Flag</x:v>
+      </x:c>
+      <x:c r="B8" s="230" t="str">
+        <x:v>/images/pets/Agender Flag.png</x:v>
+      </x:c>
+      <x:c r="C8" s="238"/>
+      <x:c r="D8" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="19" customHeight="1">
+      <x:c r="A9" s="230" t="str">
+        <x:v>Airplane Propeller</x:v>
+      </x:c>
+      <x:c r="B9" s="230" t="str">
+        <x:v>/images/pets/Airplane Propeller.png</x:v>
+      </x:c>
+      <x:c r="C9" s="238"/>
+      <x:c r="D9" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="19" customHeight="1">
+      <x:c r="A10" s="230" t="str">
+        <x:v>Amber Bone</x:v>
+      </x:c>
+      <x:c r="B10" s="230" t="str">
+        <x:v>/images/pets/Amber Bone.png</x:v>
+      </x:c>
+      <x:c r="C10" s="238"/>
+      <x:c r="D10" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="19" customHeight="1">
+      <x:c r="A11" s="230" t="str">
+        <x:v>Amethyst Skies Mega Neon Paint</x:v>
+      </x:c>
+      <x:c r="B11" s="230" t="str">
+        <x:v>/images/pets/Amethyst Skies Mega Neon Paint.png</x:v>
+      </x:c>
+      <x:c r="C11" s="238"/>
+      <x:c r="D11" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="19" customHeight="1">
+      <x:c r="A12" s="230" t="str">
+        <x:v>Amethyst Skies Mega Neon Pet Paint</x:v>
+      </x:c>
+      <x:c r="B12" s="230" t="str">
+        <x:v>/images/pets/Amethyst Skies Mega Neon Pet Paint.png</x:v>
+      </x:c>
+      <x:c r="C12" s="238"/>
+      <x:c r="D12" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="19" customHeight="1">
+      <x:c r="A13" s="230" t="str">
+        <x:v>Ammonite Flying Disc</x:v>
+      </x:c>
+      <x:c r="B13" s="230" t="str">
+        <x:v>/images/pets/Ammonite Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C13" s="238"/>
+      <x:c r="D13" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="19" customHeight="1">
+      <x:c r="A14" s="230" t="str">
+        <x:v>Anchor Balloon</x:v>
+      </x:c>
+      <x:c r="B14" s="230" t="str">
+        <x:v>/images/pets/Anchor Balloon.png</x:v>
+      </x:c>
+      <x:c r="C14" s="238"/>
+      <x:c r="D14" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="19" customHeight="1">
+      <x:c r="A15" s="230" t="str">
+        <x:v>Anchor Propeller</x:v>
+      </x:c>
+      <x:c r="B15" s="230" t="str">
+        <x:v>/images/pets/Anchor Propeller.png</x:v>
+      </x:c>
+      <x:c r="C15" s="238"/>
+      <x:c r="D15" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="19" customHeight="1">
+      <x:c r="A16" s="230" t="str">
+        <x:v>Angelic Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B16" s="230" t="str">
+        <x:v>/images/pets/Angelic Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C16" s="238"/>
+      <x:c r="D16" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="19" customHeight="1">
+      <x:c r="A17" s="230" t="str">
+        <x:v>Angelic Pogostick</x:v>
+      </x:c>
+      <x:c r="B17" s="230" t="str">
+        <x:v>/images/pets/Angelic Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C17" s="238"/>
+      <x:c r="D17" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="19" customHeight="1">
+      <x:c r="A18" s="230" t="str">
+        <x:v>Angelic Propeller</x:v>
+      </x:c>
+      <x:c r="B18" s="230" t="str">
+        <x:v>/images/pets/Angelic Propeller.png</x:v>
+      </x:c>
+      <x:c r="C18" s="238"/>
+      <x:c r="D18" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="19" customHeight="1">
+      <x:c r="A19" s="230" t="str">
+        <x:v>Anhk Pogostick</x:v>
+      </x:c>
+      <x:c r="B19" s="230" t="str">
+        <x:v>/images/pets/Anhk Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C19" s="238"/>
+      <x:c r="D19" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="19" customHeight="1">
+      <x:c r="A20" s="230" t="str">
+        <x:v>Ankylosaurus Fossil</x:v>
+      </x:c>
+      <x:c r="B20" s="230" t="str">
+        <x:v>/images/pets/Ankylosaurus Fossil.png</x:v>
+      </x:c>
+      <x:c r="C20" s="238"/>
+      <x:c r="D20" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="19" customHeight="1">
+      <x:c r="A21" s="230" t="str">
+        <x:v>Anna Rattle</x:v>
+      </x:c>
+      <x:c r="B21" s="230" t="str">
+        <x:v>/images/pets/Anna Rattle.png</x:v>
+      </x:c>
+      <x:c r="C21" s="238"/>
+      <x:c r="D21" s="234" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="19" customHeight="1">
+      <x:c r="A22" s="230" t="str">
+        <x:v>Antler Chew Toy</x:v>
+      </x:c>
+      <x:c r="B22" s="230" t="str">
+        <x:v>/images/pets/Antler Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C22" s="238"/>
+      <x:c r="D22" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="19" customHeight="1">
+      <x:c r="A23" s="230" t="str">
+        <x:v>Anvil Balloon</x:v>
+      </x:c>
+      <x:c r="B23" s="230" t="str">
+        <x:v>/images/pets/Anvil Balloon.png</x:v>
+      </x:c>
+      <x:c r="C23" s="238"/>
+      <x:c r="D23" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="19" customHeight="1">
+      <x:c r="A24" s="230" t="str">
+        <x:v>Armchair Float</x:v>
+      </x:c>
+      <x:c r="B24" s="230" t="str">
+        <x:v>/images/pets/Armchair Float.png</x:v>
+      </x:c>
+      <x:c r="C24" s="238"/>
+      <x:c r="D24" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="19" customHeight="1">
+      <x:c r="A25" s="230" t="str">
+        <x:v>Aromantic Flag</x:v>
+      </x:c>
+      <x:c r="B25" s="230" t="str">
+        <x:v>/images/pets/Aromantic Flag.png</x:v>
+      </x:c>
+      <x:c r="C25" s="238"/>
+      <x:c r="D25" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="19" customHeight="1">
+      <x:c r="A26" s="230" t="str">
+        <x:v>Astro Ball</x:v>
+      </x:c>
+      <x:c r="B26" s="230" t="str">
+        <x:v>/images/pets/Astro Ball.png</x:v>
+      </x:c>
+      <x:c r="C26" s="238"/>
+      <x:c r="D26" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="19" customHeight="1">
+      <x:c r="A27" s="230" t="str">
+        <x:v>Avocado Robinado Plush</x:v>
+      </x:c>
+      <x:c r="B27" s="230" t="str">
+        <x:v>/images/pets/Avocado Robinado Plush.png</x:v>
+      </x:c>
+      <x:c r="C27" s="238"/>
+      <x:c r="D27" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="19" customHeight="1">
+      <x:c r="A28" s="230" t="str">
+        <x:v>Axe Rattle</x:v>
+      </x:c>
+      <x:c r="B28" s="230" t="str">
+        <x:v>/images/pets/Axe Rattle.png</x:v>
+      </x:c>
+      <x:c r="C28" s="238"/>
+      <x:c r="D28" s="234" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="19" customHeight="1">
+      <x:c r="A29" s="230" t="str">
+        <x:v>Bacon And Eggs Throw Toy</x:v>
+      </x:c>
+      <x:c r="B29" s="230" t="str">
+        <x:v>/images/pets/Bacon And Eggs Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C29" s="238"/>
+      <x:c r="D29" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="19" customHeight="1">
+      <x:c r="A30" s="230" t="str">
+        <x:v>Badly Wrapped Toy Sword</x:v>
+      </x:c>
+      <x:c r="B30" s="230" t="str">
+        <x:v>/images/pets/Badly Wrapped Toy Sword.png</x:v>
+      </x:c>
+      <x:c r="C30" s="238"/>
+      <x:c r="D30" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="19" customHeight="1">
+      <x:c r="A31" s="230" t="str">
+        <x:v>Balloon</x:v>
+      </x:c>
+      <x:c r="B31" s="230" t="str">
+        <x:v>/images/pets/Balloon.png</x:v>
+      </x:c>
+      <x:c r="C31" s="238"/>
+      <x:c r="D31" s="234" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="19" customHeight="1">
+      <x:c r="A32" s="230" t="str">
+        <x:v>Balloon Pogostick</x:v>
+      </x:c>
+      <x:c r="B32" s="230" t="str">
+        <x:v>/images/pets/Balloon Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C32" s="238"/>
+      <x:c r="D32" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="19" customHeight="1">
+      <x:c r="A33" s="230" t="str">
+        <x:v>Balloons</x:v>
+      </x:c>
+      <x:c r="B33" s="230" t="str">
+        <x:v>/images/pets/Balloons.png</x:v>
+      </x:c>
+      <x:c r="C33" s="238"/>
+      <x:c r="D33" s="234" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="19" customHeight="1">
+      <x:c r="A34" s="230" t="str">
+        <x:v>Banana Chew Toy</x:v>
+      </x:c>
+      <x:c r="B34" s="230" t="str">
+        <x:v>/images/pets/Banana Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C34" s="238"/>
+      <x:c r="D34" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="19" customHeight="1">
+      <x:c r="A35" s="230" t="str">
+        <x:v>Banana Plush</x:v>
+      </x:c>
+      <x:c r="B35" s="230" t="str">
+        <x:v>/images/pets/Banana Plush.png</x:v>
+      </x:c>
+      <x:c r="C35" s="238"/>
+      <x:c r="D35" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="19" customHeight="1">
+      <x:c r="A36" s="230" t="str">
+        <x:v>Banana Pogo</x:v>
+      </x:c>
+      <x:c r="B36" s="230" t="str">
+        <x:v>/images/pets/Banana Pogo.png</x:v>
+      </x:c>
+      <x:c r="C36" s="238"/>
+      <x:c r="D36" s="234" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="19" customHeight="1">
+      <x:c r="A37" s="230" t="str">
+        <x:v>Banana Rattle</x:v>
+      </x:c>
+      <x:c r="B37" s="230" t="str">
+        <x:v>/images/pets/Banana Rattle.png</x:v>
+      </x:c>
+      <x:c r="C37" s="238"/>
+      <x:c r="D37" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="19" customHeight="1">
+      <x:c r="A38" s="230" t="str">
+        <x:v>Banana Tree Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B38" s="230" t="str">
+        <x:v>/images/pets/Banana Tree Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C38" s="238"/>
+      <x:c r="D38" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="19" customHeight="1">
+      <x:c r="A39" s="230" t="str">
+        <x:v>Bandage Propeller</x:v>
+      </x:c>
+      <x:c r="B39" s="230" t="str">
+        <x:v>/images/pets/Bandage Propeller.png</x:v>
+      </x:c>
+      <x:c r="C39" s="238"/>
+      <x:c r="D39" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="19" customHeight="1">
+      <x:c r="A40" s="230" t="str">
+        <x:v>Banjo</x:v>
+      </x:c>
+      <x:c r="B40" s="230" t="str">
+        <x:v>/images/pets/Banjo.png</x:v>
+      </x:c>
+      <x:c r="C40" s="238"/>
+      <x:c r="D40" s="234" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="19" customHeight="1">
+      <x:c r="A41" s="230" t="str">
+        <x:v>Baseball Toy</x:v>
+      </x:c>
+      <x:c r="B41" s="230" t="str">
+        <x:v>/images/pets/Baseball Toy.png</x:v>
+      </x:c>
+      <x:c r="C41" s="238"/>
+      <x:c r="D41" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="19" customHeight="1">
+      <x:c r="A42" s="230" t="str">
+        <x:v>Basic Pickaxe</x:v>
+      </x:c>
+      <x:c r="B42" s="230" t="str">
+        <x:v>/images/pets/Basic Pickaxe.png</x:v>
+      </x:c>
+      <x:c r="C42" s="238"/>
+      <x:c r="D42" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="19" customHeight="1">
+      <x:c r="A43" s="230" t="str">
+        <x:v>Bat Key Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B43" s="230" t="str">
+        <x:v>/images/pets/Bat Key Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C43" s="238"/>
+      <x:c r="D43" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="19" customHeight="1">
+      <x:c r="A44" s="230" t="str">
+        <x:v>Bat Wing Balloon</x:v>
+      </x:c>
+      <x:c r="B44" s="230" t="str">
+        <x:v>/images/pets/Bat Wing Balloon.png</x:v>
+      </x:c>
+      <x:c r="C44" s="238"/>
+      <x:c r="D44" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="19" customHeight="1">
+      <x:c r="A45" s="230" t="str">
+        <x:v>Bauble Balloon</x:v>
+      </x:c>
+      <x:c r="B45" s="230" t="str">
+        <x:v>/images/pets/Bauble Balloon.png</x:v>
+      </x:c>
+      <x:c r="C45" s="238"/>
+      <x:c r="D45" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="19" customHeight="1">
+      <x:c r="A46" s="230" t="str">
+        <x:v>Bauble Throw Toy</x:v>
+      </x:c>
+      <x:c r="B46" s="230" t="str">
+        <x:v>/images/pets/Bauble Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C46" s="238"/>
+      <x:c r="D46" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="19" customHeight="1">
+      <x:c r="A47" s="230" t="str">
+        <x:v>Bear Head Plush</x:v>
+      </x:c>
+      <x:c r="B47" s="230" t="str">
+        <x:v>/images/pets/Bear Head Plush.png</x:v>
+      </x:c>
+      <x:c r="C47" s="238"/>
+      <x:c r="D47" s="234" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="19" customHeight="1">
+      <x:c r="A48" s="230" t="str">
+        <x:v>Bench</x:v>
+      </x:c>
+      <x:c r="B48" s="230" t="str">
+        <x:v>/images/pets/Bench.png</x:v>
+      </x:c>
+      <x:c r="C48" s="238"/>
+      <x:c r="D48" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="19" customHeight="1">
+      <x:c r="A49" s="230" t="str">
+        <x:v>Bi Flag</x:v>
+      </x:c>
+      <x:c r="B49" s="230" t="str">
+        <x:v>/images/pets/Bi Flag.png</x:v>
+      </x:c>
+      <x:c r="C49" s="238"/>
+      <x:c r="D49" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="19" customHeight="1">
+      <x:c r="A50" s="230" t="str">
+        <x:v>Big Log Throw Toy</x:v>
+      </x:c>
+      <x:c r="B50" s="230" t="str">
+        <x:v>/images/pets/Big Log Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C50" s="238"/>
+      <x:c r="D50" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="19" customHeight="1">
+      <x:c r="A51" s="230" t="str">
+        <x:v>Big Mushroom</x:v>
+      </x:c>
+      <x:c r="B51" s="230" t="str">
+        <x:v>/images/pets/Big Mushroom.png</x:v>
+      </x:c>
+      <x:c r="C51" s="238"/>
+      <x:c r="D51" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="19" customHeight="1">
+      <x:c r="A52" s="230" t="str">
+        <x:v>Bird Feeder Pogo</x:v>
+      </x:c>
+      <x:c r="B52" s="230" t="str">
+        <x:v>/images/pets/Bird Feeder Pogo.png</x:v>
+      </x:c>
+      <x:c r="C52" s="238"/>
+      <x:c r="D52" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="19" customHeight="1">
+      <x:c r="A53" s="230" t="str">
+        <x:v>Black Fern</x:v>
+      </x:c>
+      <x:c r="B53" s="230" t="str">
+        <x:v>/images/pets/Black Fern.png</x:v>
+      </x:c>
+      <x:c r="C53" s="238"/>
+      <x:c r="D53" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="19" customHeight="1">
+      <x:c r="A54" s="230" t="str">
+        <x:v>Black Pogostick</x:v>
+      </x:c>
+      <x:c r="B54" s="230" t="str">
+        <x:v>/images/pets/Black Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C54" s="238"/>
+      <x:c r="D54" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="19" customHeight="1">
+      <x:c r="A55" s="230" t="str">
+        <x:v>Blossom Propeller</x:v>
+      </x:c>
+      <x:c r="B55" s="230" t="str">
+        <x:v>/images/pets/Blossom Propeller.png</x:v>
+      </x:c>
+      <x:c r="C55" s="238"/>
+      <x:c r="D55" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="19" customHeight="1">
+      <x:c r="A56" s="230" t="str">
+        <x:v>Blue Pogostick</x:v>
+      </x:c>
+      <x:c r="B56" s="230" t="str">
+        <x:v>/images/pets/Blue Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C56" s="238"/>
+      <x:c r="D56" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="19" customHeight="1">
+      <x:c r="A57" s="230" t="str">
+        <x:v>Boba Tea Chew Toy</x:v>
+      </x:c>
+      <x:c r="B57" s="230" t="str">
+        <x:v>/images/pets/Boba Tea Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C57" s="238"/>
+      <x:c r="D57" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="19" customHeight="1">
+      <x:c r="A58" s="230" t="str">
+        <x:v>Bone Throw Toy</x:v>
+      </x:c>
+      <x:c r="B58" s="230" t="str">
+        <x:v>/images/pets/Bone Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C58" s="238"/>
+      <x:c r="D58" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="19" customHeight="1">
+      <x:c r="A59" s="230" t="str">
+        <x:v>Bone Xylophone</x:v>
+      </x:c>
+      <x:c r="B59" s="230" t="str">
+        <x:v>/images/pets/Bone Xylophone.png</x:v>
+      </x:c>
+      <x:c r="C59" s="238"/>
+      <x:c r="D59" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="19" customHeight="1">
+      <x:c r="A60" s="230" t="str">
+        <x:v>Bongos</x:v>
+      </x:c>
+      <x:c r="B60" s="230" t="str">
+        <x:v>/images/pets/Bongos.png</x:v>
+      </x:c>
+      <x:c r="C60" s="238"/>
+      <x:c r="D60" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="19" customHeight="1">
+      <x:c r="A61" s="230" t="str">
+        <x:v>Book of Binding Leash</x:v>
+      </x:c>
+      <x:c r="B61" s="230" t="str">
+        <x:v>/images/pets/Book of Binding Leash.png</x:v>
+      </x:c>
+      <x:c r="C61" s="238"/>
+      <x:c r="D61" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="19" customHeight="1">
+      <x:c r="A62" s="230" t="str">
+        <x:v>Boomerang Throw Toy</x:v>
+      </x:c>
+      <x:c r="B62" s="230" t="str">
+        <x:v>/images/pets/Boomerang Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C62" s="238"/>
+      <x:c r="D62" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="19" customHeight="1">
+      <x:c r="A63" s="230" t="str">
+        <x:v>Bouncy Ball Pogo</x:v>
+      </x:c>
+      <x:c r="B63" s="230" t="str">
+        <x:v>/images/pets/Bouncy Ball Pogo.png</x:v>
+      </x:c>
+      <x:c r="C63" s="238"/>
+      <x:c r="D63" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="19" customHeight="1">
+      <x:c r="A64" s="230" t="str">
+        <x:v>Bouquet Chew Toy</x:v>
+      </x:c>
+      <x:c r="B64" s="230" t="str">
+        <x:v>/images/pets/Bouquet Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C64" s="238"/>
+      <x:c r="D64" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="19" customHeight="1">
+      <x:c r="A65" s="230" t="str">
+        <x:v>Brachiosaurus Fossil</x:v>
+      </x:c>
+      <x:c r="B65" s="230" t="str">
+        <x:v>/images/pets/Brachiosaurus Fossil.png</x:v>
+      </x:c>
+      <x:c r="C65" s="238"/>
+      <x:c r="D65" s="234" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="19" customHeight="1">
+      <x:c r="A66" s="230" t="str">
+        <x:v>Briefcase Ingredient</x:v>
+      </x:c>
+      <x:c r="B66" s="230" t="str">
+        <x:v>/images/pets/Briefcase Ingredient.png</x:v>
+      </x:c>
+      <x:c r="C66" s="238"/>
+      <x:c r="D66" s="234" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="19" customHeight="1">
+      <x:c r="A67" s="230" t="str">
+        <x:v>Brown Pogostick</x:v>
+      </x:c>
+      <x:c r="B67" s="230" t="str">
+        <x:v>/images/pets/Brown Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C67" s="238"/>
+      <x:c r="D67" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="19" customHeight="1">
+      <x:c r="A68" s="230" t="str">
+        <x:v>Bubble Wand</x:v>
+      </x:c>
+      <x:c r="B68" s="230" t="str">
+        <x:v>/images/pets/Bubble Wand.png</x:v>
+      </x:c>
+      <x:c r="C68" s="238"/>
+      <x:c r="D68" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="19" customHeight="1">
+      <x:c r="A69" s="230" t="str">
+        <x:v>Bubblegum Machine Rattle</x:v>
+      </x:c>
+      <x:c r="B69" s="230" t="str">
+        <x:v>/images/pets/Bubblegum Machine Rattle.png</x:v>
+      </x:c>
+      <x:c r="C69" s="238"/>
+      <x:c r="D69" s="234" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="19" customHeight="1">
+      <x:c r="A70" s="230" t="str">
+        <x:v>Bumblebee Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B70" s="230" t="str">
+        <x:v>/images/pets/Bumblebee Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C70" s="238"/>
+      <x:c r="D70" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="19" customHeight="1">
+      <x:c r="A71" s="230" t="str">
+        <x:v>Bumblebee Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B71" s="230" t="str">
+        <x:v>/images/pets/Bumblebee Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C71" s="238"/>
+      <x:c r="D71" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="19" customHeight="1">
+      <x:c r="A72" s="230" t="str">
+        <x:v>Bunny Balloon</x:v>
+      </x:c>
+      <x:c r="B72" s="230" t="str">
+        <x:v>/images/pets/Bunny Balloon.png</x:v>
+      </x:c>
+      <x:c r="C72" s="238"/>
+      <x:c r="D72" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="19" customHeight="1">
+      <x:c r="A73" s="230" t="str">
+        <x:v>Bunny Plush</x:v>
+      </x:c>
+      <x:c r="B73" s="230" t="str">
+        <x:v>/images/pets/Bunny Plush.png</x:v>
+      </x:c>
+      <x:c r="C73" s="238"/>
+      <x:c r="D73" s="234" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="19" customHeight="1">
+      <x:c r="A74" s="230" t="str">
+        <x:v>Bunting Leash</x:v>
+      </x:c>
+      <x:c r="B74" s="230" t="str">
+        <x:v>/images/pets/Bunting Leash.png</x:v>
+      </x:c>
+      <x:c r="C74" s="238"/>
+      <x:c r="D74" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="19" customHeight="1">
+      <x:c r="A75" s="230" t="str">
+        <x:v>Burger Balloon</x:v>
+      </x:c>
+      <x:c r="B75" s="230" t="str">
+        <x:v>/images/pets/Burger Balloon.png</x:v>
+      </x:c>
+      <x:c r="C75" s="238"/>
+      <x:c r="D75" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="19" customHeight="1">
+      <x:c r="A76" s="230" t="str">
+        <x:v>Burger Plushie</x:v>
+      </x:c>
+      <x:c r="B76" s="230" t="str">
+        <x:v>/images/pets/Burger Plushie.png</x:v>
+      </x:c>
+      <x:c r="C76" s="238"/>
+      <x:c r="D76" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="19" customHeight="1">
+      <x:c r="A77" s="230" t="str">
+        <x:v>Cactus Balloon</x:v>
+      </x:c>
+      <x:c r="B77" s="230" t="str">
+        <x:v>/images/pets/Cactus Balloon.png</x:v>
+      </x:c>
+      <x:c r="C77" s="238"/>
+      <x:c r="D77" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="19" customHeight="1">
+      <x:c r="A78" s="230" t="str">
+        <x:v>Cactus Friend Plushie</x:v>
+      </x:c>
+      <x:c r="B78" s="230" t="str">
+        <x:v>/images/pets/Cactus Friend Plushie.png</x:v>
+      </x:c>
+      <x:c r="C78" s="238"/>
+      <x:c r="D78" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="19" customHeight="1">
+      <x:c r="A79" s="230" t="str">
+        <x:v>Cactus Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B79" s="230" t="str">
+        <x:v>/images/pets/Cactus Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C79" s="238"/>
+      <x:c r="D79" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="19" customHeight="1">
+      <x:c r="A80" s="230" t="str">
+        <x:v>Cactus Plushie Chew Toy</x:v>
+      </x:c>
+      <x:c r="B80" s="230" t="str">
+        <x:v>/images/pets/Cactus Plushie Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C80" s="238"/>
+      <x:c r="D80" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="19" customHeight="1">
+      <x:c r="A81" s="230" t="str">
+        <x:v>Camera</x:v>
+      </x:c>
+      <x:c r="B81" s="230" t="str">
+        <x:v>/images/pets/Camera.png</x:v>
+      </x:c>
+      <x:c r="C81" s="238"/>
+      <x:c r="D81" s="234" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="19" customHeight="1">
+      <x:c r="A82" s="230" t="str">
+        <x:v>Camper's Bench</x:v>
+      </x:c>
+      <x:c r="B82" s="230" t="str">
+        <x:v>/images/pets/Camper's Bench.png</x:v>
+      </x:c>
+      <x:c r="C82" s="238"/>
+      <x:c r="D82" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="19" customHeight="1">
+      <x:c r="A83" s="230" t="str">
+        <x:v>Camper's Bongos</x:v>
+      </x:c>
+      <x:c r="B83" s="230" t="str">
+        <x:v>/images/pets/Camper's Bongos.png</x:v>
+      </x:c>
+      <x:c r="C83" s="238"/>
+      <x:c r="D83" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="19" customHeight="1">
+      <x:c r="A84" s="230" t="str">
+        <x:v>Camper's Flashlight</x:v>
+      </x:c>
+      <x:c r="B84" s="230" t="str">
+        <x:v>/images/pets/Camper's Flashlight.png</x:v>
+      </x:c>
+      <x:c r="C84" s="238"/>
+      <x:c r="D84" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="19" customHeight="1">
+      <x:c r="A85" s="230" t="str">
+        <x:v>Camper's Guitar</x:v>
+      </x:c>
+      <x:c r="B85" s="230" t="str">
+        <x:v>/images/pets/Camper's Guitar.png</x:v>
+      </x:c>
+      <x:c r="C85" s="238"/>
+      <x:c r="D85" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="19" customHeight="1">
+      <x:c r="A86" s="230" t="str">
+        <x:v>Camper's Sleeping Bag</x:v>
+      </x:c>
+      <x:c r="B86" s="230" t="str">
+        <x:v>/images/pets/Camper's Sleeping Bag.png</x:v>
+      </x:c>
+      <x:c r="C86" s="238"/>
+      <x:c r="D86" s="234" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="19" customHeight="1">
+      <x:c r="A87" s="230" t="str">
+        <x:v>Camper's Sparkler</x:v>
+      </x:c>
+      <x:c r="B87" s="230" t="str">
+        <x:v>/images/pets/Camper's Sparkler.png</x:v>
+      </x:c>
+      <x:c r="C87" s="238"/>
+      <x:c r="D87" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="19" customHeight="1">
+      <x:c r="A88" s="230" t="str">
+        <x:v>Camper's Tent</x:v>
+      </x:c>
+      <x:c r="B88" s="230" t="str">
+        <x:v>/images/pets/Camper's Tent.png</x:v>
+      </x:c>
+      <x:c r="C88" s="238"/>
+      <x:c r="D88" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="19" customHeight="1">
+      <x:c r="A89" s="230" t="str">
+        <x:v>Campfire Stories Mega Neon Paint</x:v>
+      </x:c>
+      <x:c r="B89" s="230" t="str">
+        <x:v>/images/pets/Campfire Stories Mega Neon Paint.png</x:v>
+      </x:c>
+      <x:c r="C89" s="238"/>
+      <x:c r="D89" s="234" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="19" customHeight="1">
+      <x:c r="A90" s="230" t="str">
+        <x:v>Camping Tent</x:v>
+      </x:c>
+      <x:c r="B90" s="230" t="str">
+        <x:v>/images/pets/Camping Tent.png</x:v>
+      </x:c>
+      <x:c r="C90" s="238"/>
+      <x:c r="D90" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="19" customHeight="1">
+      <x:c r="A91" s="230" t="str">
+        <x:v>Candihorn Instrument</x:v>
+      </x:c>
+      <x:c r="B91" s="230" t="str">
+        <x:v>/images/pets/Candihorn Instrument.png</x:v>
+      </x:c>
+      <x:c r="C91" s="238"/>
+      <x:c r="D91" s="234" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="19" customHeight="1">
+      <x:c r="A92" s="230" t="str">
+        <x:v>Candle</x:v>
+      </x:c>
+      <x:c r="B92" s="230" t="str">
+        <x:v>/images/pets/Candle.png</x:v>
+      </x:c>
+      <x:c r="C92" s="238"/>
+      <x:c r="D92" s="234" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="19" customHeight="1">
+      <x:c r="A93" s="230" t="str">
+        <x:v>Candy Cane Chew Toy</x:v>
+      </x:c>
+      <x:c r="B93" s="230" t="str">
+        <x:v>/images/pets/Candy Cane Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C93" s="238"/>
+      <x:c r="D93" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="19" customHeight="1">
+      <x:c r="A94" s="230" t="str">
+        <x:v>Candy Cane Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B94" s="230" t="str">
+        <x:v>/images/pets/Candy Cane Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C94" s="238"/>
+      <x:c r="D94" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="19" customHeight="1">
+      <x:c r="A95" s="230" t="str">
+        <x:v>Candy Cane Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B95" s="230" t="str">
+        <x:v>/images/pets/Candy Cane Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C95" s="238"/>
+      <x:c r="D95" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="19" customHeight="1">
+      <x:c r="A96" s="230" t="str">
+        <x:v>Candy Cannon</x:v>
+      </x:c>
+      <x:c r="B96" s="230" t="str">
+        <x:v>/images/pets/Candy Cannon.png</x:v>
+      </x:c>
+      <x:c r="C96" s="238"/>
+      <x:c r="D96" s="234" t="n">
+        <x:v>265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="19" customHeight="1">
+      <x:c r="A97" s="230" t="str">
+        <x:v>Candy Flare Mega Neon Paint</x:v>
+      </x:c>
+      <x:c r="B97" s="230" t="str">
+        <x:v>/images/pets/Candy Flare Mega Neon Paint.png</x:v>
+      </x:c>
+      <x:c r="C97" s="238"/>
+      <x:c r="D97" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="19" customHeight="1">
+      <x:c r="A98" s="230" t="str">
+        <x:v>Candy Flare Mega Neon Pet Paint</x:v>
+      </x:c>
+      <x:c r="B98" s="230" t="str">
+        <x:v>/images/pets/Candy Flare Mega Neon Pet Paint.png</x:v>
+      </x:c>
+      <x:c r="C98" s="238"/>
+      <x:c r="D98" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="19" customHeight="1">
+      <x:c r="A99" s="230" t="str">
+        <x:v>Candy Skewer</x:v>
+      </x:c>
+      <x:c r="B99" s="230" t="str">
+        <x:v>/images/pets/Candy Skewer.png</x:v>
+      </x:c>
+      <x:c r="C99" s="238"/>
+      <x:c r="D99" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="19" customHeight="1">
+      <x:c r="A100" s="230" t="str">
+        <x:v>CandyFloss Mega Neon Paint</x:v>
+      </x:c>
+      <x:c r="B100" s="230" t="str">
+        <x:v>/images/pets/CandyFloss Mega Neon Paint.png</x:v>
+      </x:c>
+      <x:c r="C100" s="238"/>
+      <x:c r="D100" s="234" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="19" customHeight="1">
+      <x:c r="A101" s="230" t="str">
+        <x:v>Captain's Wheel Throw Toy</x:v>
+      </x:c>
+      <x:c r="B101" s="230" t="str">
+        <x:v>/images/pets/Captain's Wheel Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C101" s="238"/>
+      <x:c r="D101" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="19" customHeight="1">
+      <x:c r="A102" s="230" t="str">
+        <x:v>Carousel Propeller</x:v>
+      </x:c>
+      <x:c r="B102" s="230" t="str">
+        <x:v>/images/pets/Carousel Propeller.png</x:v>
+      </x:c>
+      <x:c r="C102" s="238"/>
+      <x:c r="D102" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="19" customHeight="1">
+      <x:c r="A103" s="230" t="str">
+        <x:v>Carrot Bushel</x:v>
+      </x:c>
+      <x:c r="B103" s="230" t="str">
+        <x:v>/images/pets/Carrot Bushel.png</x:v>
+      </x:c>
+      <x:c r="C103" s="238"/>
+      <x:c r="D103" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="19" customHeight="1">
+      <x:c r="A104" s="230" t="str">
+        <x:v>Carrot Friend Plushie</x:v>
+      </x:c>
+      <x:c r="B104" s="230" t="str">
+        <x:v>/images/pets/Carrot Friend Plushie.png</x:v>
+      </x:c>
+      <x:c r="C104" s="238"/>
+      <x:c r="D104" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="19" customHeight="1">
+      <x:c r="A105" s="230" t="str">
+        <x:v>Carrot Lamb Plush</x:v>
+      </x:c>
+      <x:c r="B105" s="230" t="str">
+        <x:v>/images/pets/Carrot Lamb Plush.png</x:v>
+      </x:c>
+      <x:c r="C105" s="238"/>
+      <x:c r="D105" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="19" customHeight="1">
+      <x:c r="A106" s="230" t="str">
+        <x:v>Carrot Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B106" s="230" t="str">
+        <x:v>/images/pets/Carrot Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C106" s="238"/>
+      <x:c r="D106" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="19" customHeight="1">
+      <x:c r="A107" s="230" t="str">
+        <x:v>Carrot Rattle</x:v>
+      </x:c>
+      <x:c r="B107" s="230" t="str">
+        <x:v>/images/pets/Carrot Rattle.png</x:v>
+      </x:c>
+      <x:c r="C107" s="238"/>
+      <x:c r="D107" s="234" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="19" customHeight="1">
+      <x:c r="A108" s="230" t="str">
+        <x:v>Cat Plush</x:v>
+      </x:c>
+      <x:c r="B108" s="230" t="str">
+        <x:v>/images/pets/Cat Plush.png</x:v>
+      </x:c>
+      <x:c r="C108" s="238"/>
+      <x:c r="D108" s="234" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="19" customHeight="1">
+      <x:c r="A109" s="230" t="str">
+        <x:v>Caticorn Rattle</x:v>
+      </x:c>
+      <x:c r="B109" s="230" t="str">
+        <x:v>/images/pets/Caticorn Rattle.png</x:v>
+      </x:c>
+      <x:c r="C109" s="238"/>
+      <x:c r="D109" s="234" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="19" customHeight="1">
+      <x:c r="A110" s="230" t="str">
+        <x:v>CD Throwing Disc</x:v>
+      </x:c>
+      <x:c r="B110" s="230" t="str">
+        <x:v>/images/pets/CD Throwing Disc.png</x:v>
+      </x:c>
+      <x:c r="C110" s="238"/>
+      <x:c r="D110" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="19" customHeight="1">
+      <x:c r="A111" s="230" t="str">
+        <x:v>Celebration Firework Launcher</x:v>
+      </x:c>
+      <x:c r="B111" s="230" t="str">
+        <x:v>/images/pets/Celebration Firework Launcher.png</x:v>
+      </x:c>
+      <x:c r="C111" s="238"/>
+      <x:c r="D111" s="234" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="19" customHeight="1">
+      <x:c r="A112" s="230" t="str">
+        <x:v>Celestial Balloon</x:v>
+      </x:c>
+      <x:c r="B112" s="230" t="str">
+        <x:v>/images/pets/Celestial Balloon.png</x:v>
+      </x:c>
+      <x:c r="C112" s="238"/>
+      <x:c r="D112" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="19" customHeight="1">
+      <x:c r="A113" s="230" t="str">
+        <x:v>Celestial Leash</x:v>
+      </x:c>
+      <x:c r="B113" s="230" t="str">
+        <x:v>/images/pets/Celestial Leash.png</x:v>
+      </x:c>
+      <x:c r="C113" s="238"/>
+      <x:c r="D113" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="19" customHeight="1">
+      <x:c r="A114" s="230" t="str">
+        <x:v>Celestial Propeller</x:v>
+      </x:c>
+      <x:c r="B114" s="230" t="str">
+        <x:v>/images/pets/Celestial Propeller.png</x:v>
+      </x:c>
+      <x:c r="C114" s="238"/>
+      <x:c r="D114" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="19" customHeight="1">
+      <x:c r="A115" s="230" t="str">
+        <x:v>Chainsaw Rattle</x:v>
+      </x:c>
+      <x:c r="B115" s="230" t="str">
+        <x:v>/images/pets/Chainsaw Rattle.png</x:v>
+      </x:c>
+      <x:c r="C115" s="238"/>
+      <x:c r="D115" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="19" customHeight="1">
+      <x:c r="A116" s="230" t="str">
+        <x:v>Chair Swing Propeller</x:v>
+      </x:c>
+      <x:c r="B116" s="230" t="str">
+        <x:v>/images/pets/Chair Swing Propeller.png</x:v>
+      </x:c>
+      <x:c r="C116" s="238"/>
+      <x:c r="D116" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="19" customHeight="1">
+      <x:c r="A117" s="230" t="str">
+        <x:v>Chakram Flying Disc</x:v>
+      </x:c>
+      <x:c r="B117" s="230" t="str">
+        <x:v>/images/pets/Chakram Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C117" s="238"/>
+      <x:c r="D117" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="19" customHeight="1">
+      <x:c r="A118" s="230" t="str">
+        <x:v>Chakram Flying Disk</x:v>
+      </x:c>
+      <x:c r="B118" s="230" t="str">
+        <x:v>/images/pets/Chakram Flying Disk.png</x:v>
+      </x:c>
+      <x:c r="C118" s="238"/>
+      <x:c r="D118" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="19" customHeight="1">
+      <x:c r="A119" s="230" t="str">
+        <x:v>Chandelier Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B119" s="230" t="str">
+        <x:v>/images/pets/Chandelier Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C119" s="238"/>
+      <x:c r="D119" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="19" customHeight="1">
+      <x:c r="A120" s="230" t="str">
+        <x:v>Chattering Teeth Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B120" s="230" t="str">
+        <x:v>/images/pets/Chattering Teeth Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C120" s="238"/>
+      <x:c r="D120" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="19" customHeight="1">
+      <x:c r="A121" s="230" t="str">
+        <x:v>Chattering Teeth Toy</x:v>
+      </x:c>
+      <x:c r="B121" s="230" t="str">
+        <x:v>/images/pets/Chattering Teeth Toy.png</x:v>
+      </x:c>
+      <x:c r="C121" s="238"/>
+      <x:c r="D121" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="19" customHeight="1">
+      <x:c r="A122" s="230" t="str">
+        <x:v>Cherry Balloon</x:v>
+      </x:c>
+      <x:c r="B122" s="230" t="str">
+        <x:v>/images/pets/Cherry Balloon.png</x:v>
+      </x:c>
+      <x:c r="C122" s="238"/>
+      <x:c r="D122" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="19" customHeight="1">
+      <x:c r="A123" s="230" t="str">
+        <x:v>Cherry Blossom Hang Glider</x:v>
+      </x:c>
+      <x:c r="B123" s="230" t="str">
+        <x:v>/images/pets/Cherry Blossom Hang Glider.png</x:v>
+      </x:c>
+      <x:c r="C123" s="238"/>
+      <x:c r="D123" s="234" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="19" customHeight="1">
+      <x:c r="A124" s="230" t="str">
+        <x:v>Cherub Staff Throw Toy</x:v>
+      </x:c>
+      <x:c r="B124" s="230" t="str">
+        <x:v>/images/pets/Cherub Staff Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C124" s="238"/>
+      <x:c r="D124" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="19" customHeight="1">
+      <x:c r="A125" s="230" t="str">
+        <x:v>Chew Ball</x:v>
+      </x:c>
+      <x:c r="B125" s="230" t="str">
+        <x:v>/images/pets/Chew Ball.png</x:v>
+      </x:c>
+      <x:c r="C125" s="238"/>
+      <x:c r="D125" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="19" customHeight="1">
+      <x:c r="A126" s="230" t="str">
+        <x:v>Chick Plush</x:v>
+      </x:c>
+      <x:c r="B126" s="230" t="str">
+        <x:v>/images/pets/Chick Plush.png</x:v>
+      </x:c>
+      <x:c r="C126" s="238"/>
+      <x:c r="D126" s="234" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="19" customHeight="1">
+      <x:c r="A127" s="230" t="str">
+        <x:v>Chinese Lantern</x:v>
+      </x:c>
+      <x:c r="B127" s="230" t="str">
+        <x:v>/images/pets/Chinese Lantern.png</x:v>
+      </x:c>
+      <x:c r="C127" s="238"/>
+      <x:c r="D127" s="234" t="n">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="19" customHeight="1">
+      <x:c r="A128" s="230" t="str">
+        <x:v>Chocolate Bunny Balloon</x:v>
+      </x:c>
+      <x:c r="B128" s="230" t="str">
+        <x:v>/images/pets/Chocolate Bunny Balloon.png</x:v>
+      </x:c>
+      <x:c r="C128" s="238"/>
+      <x:c r="D128" s="234" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="19" customHeight="1">
+      <x:c r="A129" s="230" t="str">
+        <x:v>Christmas Cat Rattle</x:v>
+      </x:c>
+      <x:c r="B129" s="230" t="str">
+        <x:v>/images/pets/Christmas Cat Rattle.png</x:v>
+      </x:c>
+      <x:c r="C129" s="238"/>
+      <x:c r="D129" s="234" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="19" customHeight="1">
+      <x:c r="A130" s="230" t="str">
+        <x:v>Christmas Doge Rattle</x:v>
+      </x:c>
+      <x:c r="B130" s="230" t="str">
+        <x:v>/images/pets/Christmas Doge Rattle.png</x:v>
+      </x:c>
+      <x:c r="C130" s="238"/>
+      <x:c r="D130" s="234" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="19" customHeight="1">
+      <x:c r="A131" s="230" t="str">
+        <x:v>Christmas Star Flying Disc</x:v>
+      </x:c>
+      <x:c r="B131" s="230" t="str">
+        <x:v>/images/pets/Christmas Star Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C131" s="238"/>
+      <x:c r="D131" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="19" customHeight="1">
+      <x:c r="A132" s="230" t="str">
+        <x:v>Christmas Star Frisbee</x:v>
+      </x:c>
+      <x:c r="B132" s="230" t="str">
+        <x:v>/images/pets/Christmas Star Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C132" s="238"/>
+      <x:c r="D132" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="19" customHeight="1">
+      <x:c r="A133" s="230" t="str">
+        <x:v>Cinnamon Stick</x:v>
+      </x:c>
+      <x:c r="B133" s="230" t="str">
+        <x:v>/images/pets/Cinnamon Stick.png</x:v>
+      </x:c>
+      <x:c r="C133" s="238"/>
+      <x:c r="D133" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="19" customHeight="1">
+      <x:c r="A134" s="230" t="str">
+        <x:v>Cinnamon Swirl Propeller</x:v>
+      </x:c>
+      <x:c r="B134" s="230" t="str">
+        <x:v>/images/pets/Cinnamon Swirl Propeller.png</x:v>
+      </x:c>
+      <x:c r="C134" s="238"/>
+      <x:c r="D134" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="19" customHeight="1">
+      <x:c r="A135" s="230" t="str">
+        <x:v>Circus Tent Propeller</x:v>
+      </x:c>
+      <x:c r="B135" s="230" t="str">
+        <x:v>/images/pets/Circus Tent Propeller.png</x:v>
+      </x:c>
+      <x:c r="C135" s="238"/>
+      <x:c r="D135" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="19" customHeight="1">
+      <x:c r="A136" s="230" t="str">
+        <x:v>Classic Trade Stand</x:v>
+      </x:c>
+      <x:c r="B136" s="230" t="str">
+        <x:v>/images/pets/Classic Trade Stand.png</x:v>
+      </x:c>
+      <x:c r="C136" s="238"/>
+      <x:c r="D136" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="19" customHeight="1">
+      <x:c r="A137" s="230" t="str">
+        <x:v>Claw</x:v>
+      </x:c>
+      <x:c r="B137" s="230" t="str">
+        <x:v>/images/pets/Claw.png</x:v>
+      </x:c>
+      <x:c r="C137" s="238"/>
+      <x:c r="D137" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="19" customHeight="1">
+      <x:c r="A138" s="230" t="str">
+        <x:v>Clouds &amp; Rainbow Rattle</x:v>
+      </x:c>
+      <x:c r="B138" s="230" t="str">
+        <x:v>/images/pets/Clouds &amp; Rainbow Rattle.png</x:v>
+      </x:c>
+      <x:c r="C138" s="238"/>
+      <x:c r="D138" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="19" customHeight="1">
+      <x:c r="A139" s="230" t="str">
+        <x:v>Clover Balloon</x:v>
+      </x:c>
+      <x:c r="B139" s="230" t="str">
+        <x:v>/images/pets/Clover Balloon.png</x:v>
+      </x:c>
+      <x:c r="C139" s="238"/>
+      <x:c r="D139" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="19" customHeight="1">
+      <x:c r="A140" s="230" t="str">
+        <x:v>Clown Umbrella</x:v>
+      </x:c>
+      <x:c r="B140" s="230" t="str">
+        <x:v>/images/pets/Clown Umbrella.png</x:v>
+      </x:c>
+      <x:c r="C140" s="238"/>
+      <x:c r="D140" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="19" customHeight="1">
+      <x:c r="A141" s="230" t="str">
+        <x:v>Compass</x:v>
+      </x:c>
+      <x:c r="B141" s="230" t="str">
+        <x:v>/images/pets/Compass.png</x:v>
+      </x:c>
+      <x:c r="C141" s="238"/>
+      <x:c r="D141" s="234" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="19" customHeight="1">
+      <x:c r="A142" s="230" t="str">
+        <x:v>Controller Balloon</x:v>
+      </x:c>
+      <x:c r="B142" s="230" t="str">
+        <x:v>/images/pets/Controller Balloon.png</x:v>
+      </x:c>
+      <x:c r="C142" s="238"/>
+      <x:c r="D142" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="19" customHeight="1">
+      <x:c r="A143" s="230" t="str">
+        <x:v>Cookie Dough Plush</x:v>
+      </x:c>
+      <x:c r="B143" s="230" t="str">
+        <x:v>/images/pets/Cookie Dough Plush.png</x:v>
+      </x:c>
+      <x:c r="C143" s="238"/>
+      <x:c r="D143" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="19" customHeight="1">
+      <x:c r="A144" s="230" t="str">
+        <x:v>Cookie Flying Disc</x:v>
+      </x:c>
+      <x:c r="B144" s="230" t="str">
+        <x:v>/images/pets/Cookie Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C144" s="238"/>
+      <x:c r="D144" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="19" customHeight="1">
+      <x:c r="A145" s="230" t="str">
+        <x:v>Cookie Frisbee</x:v>
+      </x:c>
+      <x:c r="B145" s="230" t="str">
+        <x:v>/images/pets/Cookie Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C145" s="238"/>
+      <x:c r="D145" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="19" customHeight="1">
+      <x:c r="A146" s="230" t="str">
+        <x:v>Cookie Plate Propeller</x:v>
+      </x:c>
+      <x:c r="B146" s="230" t="str">
+        <x:v>/images/pets/Cookie Plate Propeller.png</x:v>
+      </x:c>
+      <x:c r="C146" s="238"/>
+      <x:c r="D146" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="19" customHeight="1">
+      <x:c r="A147" s="230" t="str">
+        <x:v>Cookie Sabre</x:v>
+      </x:c>
+      <x:c r="B147" s="230" t="str">
+        <x:v>/images/pets/Cookie Sabre.png</x:v>
+      </x:c>
+      <x:c r="C147" s="238"/>
+      <x:c r="D147" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="19" customHeight="1">
+      <x:c r="A148" s="230" t="str">
+        <x:v>Cool Flying Disc</x:v>
+      </x:c>
+      <x:c r="B148" s="230" t="str">
+        <x:v>/images/pets/Cool Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C148" s="238"/>
+      <x:c r="D148" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="19" customHeight="1">
+      <x:c r="A149" s="230" t="str">
+        <x:v>Cool Frisbee</x:v>
+      </x:c>
+      <x:c r="B149" s="230" t="str">
+        <x:v>/images/pets/Cool Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C149" s="238"/>
+      <x:c r="D149" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="19" customHeight="1">
+      <x:c r="A150" s="230" t="str">
+        <x:v>Copper Pickaxe</x:v>
+      </x:c>
+      <x:c r="B150" s="230" t="str">
+        <x:v>/images/pets/Copper Pickaxe.png</x:v>
+      </x:c>
+      <x:c r="C150" s="238"/>
+      <x:c r="D150" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="19" customHeight="1">
+      <x:c r="A151" s="230" t="str">
+        <x:v>Cork Gun Grapple</x:v>
+      </x:c>
+      <x:c r="B151" s="230" t="str">
+        <x:v>/images/pets/Cork Gun Grapple.png</x:v>
+      </x:c>
+      <x:c r="C151" s="238"/>
+      <x:c r="D151" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="19" customHeight="1">
+      <x:c r="A152" s="230" t="str">
+        <x:v>Cotton Candy Stand</x:v>
+      </x:c>
+      <x:c r="B152" s="230" t="str">
+        <x:v>/images/pets/Cotton Candy Stand.png</x:v>
+      </x:c>
+      <x:c r="C152" s="238"/>
+      <x:c r="D152" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="19" customHeight="1">
+      <x:c r="A153" s="230" t="str">
+        <x:v>Crab Apple Friend</x:v>
+      </x:c>
+      <x:c r="B153" s="230" t="str">
+        <x:v>/images/pets/Crab Apple Friend.png</x:v>
+      </x:c>
+      <x:c r="C153" s="238"/>
+      <x:c r="D153" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="19" customHeight="1">
+      <x:c r="A154" s="230" t="str">
+        <x:v>Creator Rattle (Bethink)</x:v>
+      </x:c>
+      <x:c r="B154" s="230" t="str">
+        <x:v>/images/pets/Creator Rattle (Bethink).png</x:v>
+      </x:c>
+      <x:c r="C154" s="238"/>
+      <x:c r="D154" s="234" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="19" customHeight="1">
+      <x:c r="A155" s="230" t="str">
+        <x:v>Creator Rattle (NewFissy)</x:v>
+      </x:c>
+      <x:c r="B155" s="230" t="str">
+        <x:v>/images/pets/Creator Rattle (NewFissy).png</x:v>
+      </x:c>
+      <x:c r="C155" s="238"/>
+      <x:c r="D155" s="234" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="19" customHeight="1">
+      <x:c r="A156" s="230" t="str">
+        <x:v>Creepy Balloon</x:v>
+      </x:c>
+      <x:c r="B156" s="230" t="str">
+        <x:v>/images/pets/Creepy Balloon.png</x:v>
+      </x:c>
+      <x:c r="C156" s="238"/>
+      <x:c r="D156" s="234" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="19" customHeight="1">
+      <x:c r="A157" s="230" t="str">
+        <x:v>Croc Plush</x:v>
+      </x:c>
+      <x:c r="B157" s="230" t="str">
+        <x:v>/images/pets/Croc Plush.png</x:v>
+      </x:c>
+      <x:c r="C157" s="238"/>
+      <x:c r="D157" s="234" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="19" customHeight="1">
+      <x:c r="A158" s="230" t="str">
+        <x:v>Crook Throw Toy</x:v>
+      </x:c>
+      <x:c r="B158" s="230" t="str">
+        <x:v>/images/pets/Crook Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C158" s="238"/>
+      <x:c r="D158" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="19" customHeight="1">
+      <x:c r="A159" s="230" t="str">
+        <x:v>Crossbow Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B159" s="230" t="str">
+        <x:v>/images/pets/Crossbow Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C159" s="238"/>
+      <x:c r="D159" s="234" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="19" customHeight="1">
+      <x:c r="A160" s="230" t="str">
+        <x:v>Crow's Nest Balloon</x:v>
+      </x:c>
+      <x:c r="B160" s="230" t="str">
+        <x:v>/images/pets/Crow's Nest Balloon.png</x:v>
+      </x:c>
+      <x:c r="C160" s="238"/>
+      <x:c r="D160" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="19" customHeight="1">
+      <x:c r="A161" s="230" t="str">
+        <x:v>Crow's Nest Propeller</x:v>
+      </x:c>
+      <x:c r="B161" s="230" t="str">
+        <x:v>/images/pets/Crow's Nest Propeller.png</x:v>
+      </x:c>
+      <x:c r="C161" s="238"/>
+      <x:c r="D161" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="19" customHeight="1">
+      <x:c r="A162" s="230" t="str">
+        <x:v>Crown Flying Disc</x:v>
+      </x:c>
+      <x:c r="B162" s="230" t="str">
+        <x:v>/images/pets/Crown Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C162" s="238"/>
+      <x:c r="D162" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="19" customHeight="1">
+      <x:c r="A163" s="230" t="str">
+        <x:v>Crown Frisbee</x:v>
+      </x:c>
+      <x:c r="B163" s="230" t="str">
+        <x:v>/images/pets/Crown Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C163" s="238"/>
+      <x:c r="D163" s="234" t="n">
+        <x:v>0.035</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="19" customHeight="1">
+      <x:c r="A164" s="230" t="str">
+        <x:v>Crystal Ball Rattle</x:v>
+      </x:c>
+      <x:c r="B164" s="230" t="str">
+        <x:v>/images/pets/Crystal Ball Rattle.png</x:v>
+      </x:c>
+      <x:c r="C164" s="238"/>
+      <x:c r="D164" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="19" customHeight="1">
+      <x:c r="A165" s="230" t="str">
+        <x:v>Cupid's Bow Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B165" s="230" t="str">
+        <x:v>/images/pets/Cupid's Bow Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C165" s="238"/>
+      <x:c r="D165" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="19" customHeight="1">
+      <x:c r="A166" s="230" t="str">
+        <x:v>Cursed Skull Balloon</x:v>
+      </x:c>
+      <x:c r="B166" s="230" t="str">
+        <x:v>/images/pets/Cursed Skull Balloon.png</x:v>
+      </x:c>
+      <x:c r="C166" s="238"/>
+      <x:c r="D166" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="19" customHeight="1">
+      <x:c r="A167" s="230" t="str">
+        <x:v>Cymbal Ingredient</x:v>
+      </x:c>
+      <x:c r="B167" s="230" t="str">
+        <x:v>/images/pets/Cymbal Ingredient.png</x:v>
+      </x:c>
+      <x:c r="C167" s="238"/>
+      <x:c r="D167" s="234" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="19" customHeight="1">
+      <x:c r="A168" s="230" t="str">
+        <x:v>Da Vinci Propeller</x:v>
+      </x:c>
+      <x:c r="B168" s="230" t="str">
+        <x:v>/images/pets/Da Vinci Propeller.png</x:v>
+      </x:c>
+      <x:c r="C168" s="238"/>
+      <x:c r="D168" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="19" customHeight="1">
+      <x:c r="A169" s="230" t="str">
+        <x:v>Daisy Flying Disc</x:v>
+      </x:c>
+      <x:c r="B169" s="230" t="str">
+        <x:v>/images/pets/Daisy Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C169" s="238"/>
+      <x:c r="D169" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="19" customHeight="1">
+      <x:c r="A170" s="230" t="str">
+        <x:v>Daltokki Kite</x:v>
+      </x:c>
+      <x:c r="B170" s="230" t="str">
+        <x:v>/images/pets/Daltokki Kite.png</x:v>
+      </x:c>
+      <x:c r="C170" s="238"/>
+      <x:c r="D170" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="19" customHeight="1">
+      <x:c r="A171" s="230" t="str">
+        <x:v>Dance Arcade Stand</x:v>
+      </x:c>
+      <x:c r="B171" s="230" t="str">
+        <x:v>/images/pets/Dance Arcade Stand.png</x:v>
+      </x:c>
+      <x:c r="C171" s="238"/>
+      <x:c r="D171" s="234" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="19" customHeight="1">
+      <x:c r="A172" s="230" t="str">
+        <x:v>Dandelion Plush</x:v>
+      </x:c>
+      <x:c r="B172" s="230" t="str">
+        <x:v>/images/pets/Dandelion Plush.png</x:v>
+      </x:c>
+      <x:c r="C172" s="238"/>
+      <x:c r="D172" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="19" customHeight="1">
+      <x:c r="A173" s="230" t="str">
+        <x:v>Dandelion Propeller</x:v>
+      </x:c>
+      <x:c r="B173" s="230" t="str">
+        <x:v>/images/pets/Dandelion Propeller.png</x:v>
+      </x:c>
+      <x:c r="C173" s="238"/>
+      <x:c r="D173" s="234" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="19" customHeight="1">
+      <x:c r="A174" s="230" t="str">
+        <x:v>Demi Flag</x:v>
+      </x:c>
+      <x:c r="B174" s="230" t="str">
+        <x:v>/images/pets/Demi Flag.png</x:v>
+      </x:c>
+      <x:c r="C174" s="238"/>
+      <x:c r="D174" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="19" customHeight="1">
+      <x:c r="A175" s="230" t="str">
+        <x:v>Desert Drum</x:v>
+      </x:c>
+      <x:c r="B175" s="230" t="str">
+        <x:v>/images/pets/Desert Drum.png</x:v>
+      </x:c>
+      <x:c r="C175" s="238"/>
+      <x:c r="D175" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="19" customHeight="1">
+      <x:c r="A176" s="230" t="str">
+        <x:v>Diamond Fanghorn Kite</x:v>
+      </x:c>
+      <x:c r="B176" s="230" t="str">
+        <x:v>/images/pets/Diamond Fanghorn Kite.png</x:v>
+      </x:c>
+      <x:c r="C176" s="238"/>
+      <x:c r="D176" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="19" customHeight="1">
+      <x:c r="A177" s="230" t="str">
+        <x:v>Diamond Pickaxe</x:v>
+      </x:c>
+      <x:c r="B177" s="230" t="str">
+        <x:v>/images/pets/Diamond Pickaxe.png</x:v>
+      </x:c>
+      <x:c r="C177" s="238"/>
+      <x:c r="D177" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="19" customHeight="1">
+      <x:c r="A178" s="230" t="str">
+        <x:v>Dice Throw Toy</x:v>
+      </x:c>
+      <x:c r="B178" s="230" t="str">
+        <x:v>/images/pets/Dice Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C178" s="238"/>
+      <x:c r="D178" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="19" customHeight="1">
+      <x:c r="A179" s="230" t="str">
+        <x:v>Didgeridoo</x:v>
+      </x:c>
+      <x:c r="B179" s="230" t="str">
+        <x:v>/images/pets/Didgeridoo.png</x:v>
+      </x:c>
+      <x:c r="C179" s="238"/>
+      <x:c r="D179" s="234" t="n">
+        <x:v>0.015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="19" customHeight="1">
+      <x:c r="A180" s="230" t="str">
+        <x:v>Dimorphodon Fossil</x:v>
+      </x:c>
+      <x:c r="B180" s="230" t="str">
+        <x:v>/images/pets/Dimorphodon Fossil.png</x:v>
+      </x:c>
+      <x:c r="C180" s="238"/>
+      <x:c r="D180" s="234" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="19" customHeight="1">
+      <x:c r="A181" s="230" t="str">
+        <x:v>Disco Ball Balloon</x:v>
+      </x:c>
+      <x:c r="B181" s="230" t="str">
+        <x:v>/images/pets/Disco Ball Balloon.png</x:v>
+      </x:c>
+      <x:c r="C181" s="238"/>
+      <x:c r="D181" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="19" customHeight="1">
+      <x:c r="A182" s="230" t="str">
+        <x:v>Discosplosion</x:v>
+      </x:c>
+      <x:c r="B182" s="230" t="str">
+        <x:v>/images/pets/Discosplosion.png</x:v>
+      </x:c>
+      <x:c r="C182" s="238"/>
+      <x:c r="D182" s="234" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="19" customHeight="1">
+      <x:c r="A183" s="230" t="str">
+        <x:v>Dog Food Flying Disc</x:v>
+      </x:c>
+      <x:c r="B183" s="230" t="str">
+        <x:v>/images/pets/Dog Food Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C183" s="238"/>
+      <x:c r="D183" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="19" customHeight="1">
+      <x:c r="A184" s="230" t="str">
+        <x:v>Dog Food Frisbee</x:v>
+      </x:c>
+      <x:c r="B184" s="230" t="str">
+        <x:v>/images/pets/Dog Food Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C184" s="238"/>
+      <x:c r="D184" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="19" customHeight="1">
+      <x:c r="A185" s="230" t="str">
+        <x:v>Dog Leash</x:v>
+      </x:c>
+      <x:c r="B185" s="230" t="str">
+        <x:v>/images/pets/Dog Leash.png</x:v>
+      </x:c>
+      <x:c r="C185" s="238"/>
+      <x:c r="D185" s="234" t="n">
+        <x:v>0.015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="19" customHeight="1">
+      <x:c r="A186" s="230" t="str">
+        <x:v>Doge Rattle</x:v>
+      </x:c>
+      <x:c r="B186" s="230" t="str">
+        <x:v>/images/pets/Doge Rattle.png</x:v>
+      </x:c>
+      <x:c r="C186" s="238"/>
+      <x:c r="D186" s="234" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="19" customHeight="1">
+      <x:c r="A187" s="230" t="str">
+        <x:v>Donut Flying Disc</x:v>
+      </x:c>
+      <x:c r="B187" s="230" t="str">
+        <x:v>/images/pets/Donut Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C187" s="238"/>
+      <x:c r="D187" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="19" customHeight="1">
+      <x:c r="A188" s="230" t="str">
+        <x:v>Donut Frisbee</x:v>
+      </x:c>
+      <x:c r="B188" s="230" t="str">
+        <x:v>/images/pets/Donut Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C188" s="238"/>
+      <x:c r="D188" s="234" t="n">
+        <x:v>0.035</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="19" customHeight="1">
+      <x:c r="A189" s="230" t="str">
+        <x:v>Donut Rattle</x:v>
+      </x:c>
+      <x:c r="B189" s="230" t="str">
+        <x:v>/images/pets/Donut Rattle.png</x:v>
+      </x:c>
+      <x:c r="C189" s="238"/>
+      <x:c r="D189" s="234" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="19" customHeight="1">
+      <x:c r="A190" s="230" t="str">
+        <x:v>Donut Throw Toy</x:v>
+      </x:c>
+      <x:c r="B190" s="230" t="str">
+        <x:v>/images/pets/Donut Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C190" s="238"/>
+      <x:c r="D190" s="234" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="19" customHeight="1">
+      <x:c r="A191" s="230" t="str">
+        <x:v>Dragon Balloon</x:v>
+      </x:c>
+      <x:c r="B191" s="230" t="str">
+        <x:v>/images/pets/Dragon Balloon.png</x:v>
+      </x:c>
+      <x:c r="C191" s="238"/>
+      <x:c r="D191" s="234" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="19" customHeight="1">
+      <x:c r="A192" s="230" t="str">
+        <x:v>Drone Balloon</x:v>
+      </x:c>
+      <x:c r="B192" s="230" t="str">
+        <x:v>/images/pets/Drone Balloon.png</x:v>
+      </x:c>
+      <x:c r="C192" s="238"/>
+      <x:c r="D192" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="19" customHeight="1">
+      <x:c r="A193" s="230" t="str">
+        <x:v>Drone Propeller</x:v>
+      </x:c>
+      <x:c r="B193" s="230" t="str">
+        <x:v>/images/pets/Drone Propeller.png</x:v>
+      </x:c>
+      <x:c r="C193" s="238"/>
+      <x:c r="D193" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="19" customHeight="1">
+      <x:c r="A194" s="230" t="str">
+        <x:v>Drooping Orchid Propeller</x:v>
+      </x:c>
+      <x:c r="B194" s="230" t="str">
+        <x:v>/images/pets/Drooping Orchid Propeller.png</x:v>
+      </x:c>
+      <x:c r="C194" s="238"/>
+      <x:c r="D194" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="19" customHeight="1">
+      <x:c r="A195" s="230" t="str">
+        <x:v>Duck Balloon</x:v>
+      </x:c>
+      <x:c r="B195" s="230" t="str">
+        <x:v>/images/pets/Duck Balloon.png</x:v>
+      </x:c>
+      <x:c r="C195" s="238"/>
+      <x:c r="D195" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="19" customHeight="1">
+      <x:c r="A196" s="230" t="str">
+        <x:v>Duck Rattle</x:v>
+      </x:c>
+      <x:c r="B196" s="230" t="str">
+        <x:v>/images/pets/Duck Rattle.png</x:v>
+      </x:c>
+      <x:c r="C196" s="238"/>
+      <x:c r="D196" s="234" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="19" customHeight="1">
+      <x:c r="A197" s="230" t="str">
+        <x:v>Dumbbell</x:v>
+      </x:c>
+      <x:c r="B197" s="230" t="str">
+        <x:v>/images/pets/Dumbbell.png</x:v>
+      </x:c>
+      <x:c r="C197" s="238"/>
+      <x:c r="D197" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="19" customHeight="1">
+      <x:c r="A198" s="230" t="str">
+        <x:v>Easter Bunny Plush</x:v>
+      </x:c>
+      <x:c r="B198" s="230" t="str">
+        <x:v>/images/pets/Easter Bunny Plush.png</x:v>
+      </x:c>
+      <x:c r="C198" s="238"/>
+      <x:c r="D198" s="234" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="19" customHeight="1">
+      <x:c r="A199" s="230" t="str">
+        <x:v>Easter Chick Rattle</x:v>
+      </x:c>
+      <x:c r="B199" s="230" t="str">
+        <x:v>/images/pets/Easter Chick Rattle.png</x:v>
+      </x:c>
+      <x:c r="C199" s="238"/>
+      <x:c r="D199" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="19" customHeight="1">
+      <x:c r="A200" s="230" t="str">
+        <x:v>Eclipse Balloon</x:v>
+      </x:c>
+      <x:c r="B200" s="230" t="str">
+        <x:v>/images/pets/Eclipse Balloon.png</x:v>
+      </x:c>
+      <x:c r="C200" s="238"/>
+      <x:c r="D200" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="19" customHeight="1">
+      <x:c r="A201" s="230" t="str">
+        <x:v>Eclipse Flying Disc</x:v>
+      </x:c>
+      <x:c r="B201" s="230" t="str">
+        <x:v>/images/pets/Eclipse Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C201" s="238"/>
+      <x:c r="D201" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="19" customHeight="1">
+      <x:c r="A202" s="230" t="str">
+        <x:v>Egg Rattle</x:v>
+      </x:c>
+      <x:c r="B202" s="230" t="str">
+        <x:v>/images/pets/Egg Rattle.png</x:v>
+      </x:c>
+      <x:c r="C202" s="238"/>
+      <x:c r="D202" s="234" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="19" customHeight="1">
+      <x:c r="A203" s="230" t="str">
+        <x:v>Eggy Plush</x:v>
+      </x:c>
+      <x:c r="B203" s="230" t="str">
+        <x:v>/images/pets/Eggy Plush.png</x:v>
+      </x:c>
+      <x:c r="C203" s="238"/>
+      <x:c r="D203" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="19" customHeight="1">
+      <x:c r="A204" s="230" t="str">
+        <x:v>Elasmosaurus Fossil</x:v>
+      </x:c>
+      <x:c r="B204" s="230" t="str">
+        <x:v>/images/pets/Elasmosaurus Fossil.png</x:v>
+      </x:c>
+      <x:c r="C204" s="238"/>
+      <x:c r="D204" s="234" t="n">
+        <x:v>0.015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="19" customHeight="1">
+      <x:c r="A205" s="230" t="str">
+        <x:v>Electric Tide Mega Neon Paint</x:v>
+      </x:c>
+      <x:c r="B205" s="230" t="str">
+        <x:v>/images/pets/Electric Tide Mega Neon Paint.png</x:v>
+      </x:c>
+      <x:c r="C205" s="238"/>
+      <x:c r="D205" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="19" customHeight="1">
+      <x:c r="A206" s="230" t="str">
+        <x:v>Electric Tide Mega Neon Pet Paint</x:v>
+      </x:c>
+      <x:c r="B206" s="230" t="str">
+        <x:v>/images/pets/Electric Tide Mega Neon Pet Paint.png</x:v>
+      </x:c>
+      <x:c r="C206" s="238"/>
+      <x:c r="D206" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="19" customHeight="1">
+      <x:c r="A207" s="230" t="str">
+        <x:v>Elephant Plush</x:v>
+      </x:c>
+      <x:c r="B207" s="230" t="str">
+        <x:v>/images/pets/Elephant Plush.png</x:v>
+      </x:c>
+      <x:c r="C207" s="238"/>
+      <x:c r="D207" s="234" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="19" customHeight="1">
+      <x:c r="A208" s="230" t="str">
+        <x:v>Elf Plush</x:v>
+      </x:c>
+      <x:c r="B208" s="230" t="str">
+        <x:v>/images/pets/Elf Plush.png</x:v>
+      </x:c>
+      <x:c r="C208" s="238"/>
+      <x:c r="D208" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="19" customHeight="1">
+      <x:c r="A209" s="230" t="str">
+        <x:v>Elf Rattle</x:v>
+      </x:c>
+      <x:c r="B209" s="230" t="str">
+        <x:v>/images/pets/Elf Rattle.png</x:v>
+      </x:c>
+      <x:c r="C209" s="238"/>
+      <x:c r="D209" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="19" customHeight="1">
+      <x:c r="A210" s="230" t="str">
+        <x:v>Enby Flag</x:v>
+      </x:c>
+      <x:c r="B210" s="230" t="str">
+        <x:v>/images/pets/Enby Flag.png</x:v>
+      </x:c>
+      <x:c r="C210" s="238"/>
+      <x:c r="D210" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="19" customHeight="1">
+      <x:c r="A211" s="230" t="str">
+        <x:v>Energy Ball Throw Toy</x:v>
+      </x:c>
+      <x:c r="B211" s="230" t="str">
+        <x:v>/images/pets/Energy Ball Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C211" s="238"/>
+      <x:c r="D211" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="19" customHeight="1">
+      <x:c r="A212" s="230" t="str">
+        <x:v>Eyeball Rattle</x:v>
+      </x:c>
+      <x:c r="B212" s="230" t="str">
+        <x:v>/images/pets/Eyeball Rattle.png</x:v>
+      </x:c>
+      <x:c r="C212" s="238"/>
+      <x:c r="D212" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="19" customHeight="1">
+      <x:c r="A213" s="230" t="str">
+        <x:v>Fairground Pogo</x:v>
+      </x:c>
+      <x:c r="B213" s="230" t="str">
+        <x:v>/images/pets/Fairground Pogo.png</x:v>
+      </x:c>
+      <x:c r="C213" s="238"/>
+      <x:c r="D213" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="19" customHeight="1">
+      <x:c r="A214" s="230" t="str">
+        <x:v>Fairy Rose Light Rattle</x:v>
+      </x:c>
+      <x:c r="B214" s="230" t="str">
+        <x:v>/images/pets/Fairy Rose Light Rattle.png</x:v>
+      </x:c>
+      <x:c r="C214" s="238"/>
+      <x:c r="D214" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="19" customHeight="1">
+      <x:c r="A215" s="230" t="str">
+        <x:v>Fall Corn Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B215" s="230" t="str">
+        <x:v>/images/pets/Fall Corn Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C215" s="238"/>
+      <x:c r="D215" s="234" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="19" customHeight="1">
+      <x:c r="A216" s="230" t="str">
+        <x:v>Fall Rains Balloon</x:v>
+      </x:c>
+      <x:c r="B216" s="230" t="str">
+        <x:v>/images/pets/Fall Rains Balloon.png</x:v>
+      </x:c>
+      <x:c r="C216" s="238"/>
+      <x:c r="D216" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="19" customHeight="1">
+      <x:c r="A217" s="230" t="str">
+        <x:v>Fan Flying Disc</x:v>
+      </x:c>
+      <x:c r="B217" s="230" t="str">
+        <x:v>/images/pets/Fan Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C217" s="238"/>
+      <x:c r="D217" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="19" customHeight="1">
+      <x:c r="A218" s="230" t="str">
+        <x:v>Fan Propeller</x:v>
+      </x:c>
+      <x:c r="B218" s="230" t="str">
+        <x:v>/images/pets/Fan Propeller.png</x:v>
+      </x:c>
+      <x:c r="C218" s="238"/>
+      <x:c r="D218" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="19" customHeight="1">
+      <x:c r="A219" s="230" t="str">
+        <x:v>Fancy Balloon</x:v>
+      </x:c>
+      <x:c r="B219" s="230" t="str">
+        <x:v>/images/pets/Fancy Balloon.png</x:v>
+      </x:c>
+      <x:c r="C219" s="238"/>
+      <x:c r="D219" s="234" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="19" customHeight="1">
+      <x:c r="A220" s="230" t="str">
+        <x:v>Fancy Umbrella</x:v>
+      </x:c>
+      <x:c r="B220" s="230" t="str">
+        <x:v>/images/pets/Fancy Umbrella.png</x:v>
+      </x:c>
+      <x:c r="C220" s="238"/>
+      <x:c r="D220" s="234" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="19" customHeight="1">
+      <x:c r="A221" s="230" t="str">
+        <x:v>Fanghorn Kite</x:v>
+      </x:c>
+      <x:c r="B221" s="230" t="str">
+        <x:v>/images/pets/Fanghorn Kite.png</x:v>
+      </x:c>
+      <x:c r="C221" s="238"/>
+      <x:c r="D221" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="19" customHeight="1">
+      <x:c r="A222" s="230" t="str">
+        <x:v>Fern Propeller</x:v>
+      </x:c>
+      <x:c r="B222" s="230" t="str">
+        <x:v>/images/pets/Fern Propeller.png</x:v>
+      </x:c>
+      <x:c r="C222" s="238"/>
+      <x:c r="D222" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="19" customHeight="1">
+      <x:c r="A223" s="230" t="str">
+        <x:v>Ferris Wheel Propeller</x:v>
+      </x:c>
+      <x:c r="B223" s="230" t="str">
+        <x:v>/images/pets/Ferris Wheel Propeller.png</x:v>
+      </x:c>
+      <x:c r="C223" s="238"/>
+      <x:c r="D223" s="234" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="19" customHeight="1">
+      <x:c r="A224" s="230" t="str">
+        <x:v>Festive Bells Balloon</x:v>
+      </x:c>
+      <x:c r="B224" s="230" t="str">
+        <x:v>/images/pets/Festive Bells Balloon.png</x:v>
+      </x:c>
+      <x:c r="C224" s="238"/>
+      <x:c r="D224" s="234" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="19" customHeight="1">
+      <x:c r="A225" s="230" t="str">
+        <x:v>Festive Holly Propeller</x:v>
+      </x:c>
+      <x:c r="B225" s="230" t="str">
+        <x:v>/images/pets/Festive Holly Propeller.png</x:v>
+      </x:c>
+      <x:c r="C225" s="238"/>
+      <x:c r="D225" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="19" customHeight="1">
+      <x:c r="A226" s="230" t="str">
+        <x:v>Festive Pogo</x:v>
+      </x:c>
+      <x:c r="B226" s="230" t="str">
+        <x:v>/images/pets/Festive Pogo.png</x:v>
+      </x:c>
+      <x:c r="C226" s="238"/>
+      <x:c r="D226" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="19" customHeight="1">
+      <x:c r="A227" s="230" t="str">
+        <x:v>Festive Snow Globe Rattle</x:v>
+      </x:c>
+      <x:c r="B227" s="230" t="str">
+        <x:v>/images/pets/Festive Snow Globe Rattle.png</x:v>
+      </x:c>
+      <x:c r="C227" s="238"/>
+      <x:c r="D227" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="19" customHeight="1">
+      <x:c r="A228" s="230" t="str">
+        <x:v>Festive Tree Throwing Disc</x:v>
+      </x:c>
+      <x:c r="B228" s="230" t="str">
+        <x:v>/images/pets/Festive Tree Throwing Disc.png</x:v>
+      </x:c>
+      <x:c r="C228" s="238"/>
+      <x:c r="D228" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="19" customHeight="1">
+      <x:c r="A229" s="230" t="str">
+        <x:v>Figgy Pudding Chew Toy</x:v>
+      </x:c>
+      <x:c r="B229" s="230" t="str">
+        <x:v>/images/pets/Figgy Pudding Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C229" s="238"/>
+      <x:c r="D229" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="19" customHeight="1">
+      <x:c r="A230" s="230" t="str">
+        <x:v>Filipino Fan Throw Toy</x:v>
+      </x:c>
+      <x:c r="B230" s="230" t="str">
+        <x:v>/images/pets/Filipino Fan Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C230" s="238"/>
+      <x:c r="D230" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="19" customHeight="1">
+      <x:c r="A231" s="230" t="str">
+        <x:v>Finger Piano</x:v>
+      </x:c>
+      <x:c r="B231" s="230" t="str">
+        <x:v>/images/pets/Finger Piano.png</x:v>
+      </x:c>
+      <x:c r="C231" s="238"/>
+      <x:c r="D231" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="19" customHeight="1">
+      <x:c r="A232" s="230" t="str">
+        <x:v>Fire Ring Propeller</x:v>
+      </x:c>
+      <x:c r="B232" s="230" t="str">
+        <x:v>/images/pets/Fire Ring Propeller.png</x:v>
+      </x:c>
+      <x:c r="C232" s="238"/>
+      <x:c r="D232" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="19" customHeight="1">
+      <x:c r="A233" s="230" t="str">
+        <x:v>Firecrackers</x:v>
+      </x:c>
+      <x:c r="B233" s="230" t="str">
+        <x:v>/images/pets/Firecrackers.png</x:v>
+      </x:c>
+      <x:c r="C233" s="238"/>
+      <x:c r="D233" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="19" customHeight="1">
+      <x:c r="A234" s="230" t="str">
+        <x:v>Fish on a Stick Chew Toy</x:v>
+      </x:c>
+      <x:c r="B234" s="230" t="str">
+        <x:v>/images/pets/Fish on a Stick Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C234" s="238"/>
+      <x:c r="D234" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="19" customHeight="1">
+      <x:c r="A235" s="230" t="str">
+        <x:v>Fishing Tackle Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B235" s="230" t="str">
+        <x:v>/images/pets/Fishing Tackle Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C235" s="238"/>
+      <x:c r="D235" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="19" customHeight="1">
+      <x:c r="A236" s="230" t="str">
+        <x:v>Flame Balloon</x:v>
+      </x:c>
+      <x:c r="B236" s="230" t="str">
+        <x:v>/images/pets/Flame Balloon.png</x:v>
+      </x:c>
+      <x:c r="C236" s="238"/>
+      <x:c r="D236" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="19" customHeight="1">
+      <x:c r="A237" s="230" t="str">
+        <x:v>Flame Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B237" s="230" t="str">
+        <x:v>/images/pets/Flame Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C237" s="238"/>
+      <x:c r="D237" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="19" customHeight="1">
+      <x:c r="A238" s="230" t="str">
+        <x:v>Flame Pogostick</x:v>
+      </x:c>
+      <x:c r="B238" s="230" t="str">
+        <x:v>/images/pets/Flame Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C238" s="238"/>
+      <x:c r="D238" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="19" customHeight="1">
+      <x:c r="A239" s="230" t="str">
+        <x:v>Flame Sword</x:v>
+      </x:c>
+      <x:c r="B239" s="230" t="str">
+        <x:v>/images/pets/Flame Sword.png</x:v>
+      </x:c>
+      <x:c r="C239" s="238"/>
+      <x:c r="D239" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="19" customHeight="1">
+      <x:c r="A240" s="230" t="str">
+        <x:v>Flashlight</x:v>
+      </x:c>
+      <x:c r="B240" s="230" t="str">
+        <x:v>/images/pets/Flashlight.png</x:v>
+      </x:c>
+      <x:c r="C240" s="238"/>
+      <x:c r="D240" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="19" customHeight="1">
+      <x:c r="A241" s="230" t="str">
+        <x:v>Flatfish Throwing Disc</x:v>
+      </x:c>
+      <x:c r="B241" s="230" t="str">
+        <x:v>/images/pets/Flatfish Throwing Disc.png</x:v>
+      </x:c>
+      <x:c r="C241" s="238"/>
+      <x:c r="D241" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="19" customHeight="1">
+      <x:c r="A242" s="230" t="str">
+        <x:v>Flip Phone Toy</x:v>
+      </x:c>
+      <x:c r="B242" s="230" t="str">
+        <x:v>/images/pets/Flip Phone Toy.png</x:v>
+      </x:c>
+      <x:c r="C242" s="238"/>
+      <x:c r="D242" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="19" customHeight="1">
+      <x:c r="A243" s="230" t="str">
+        <x:v>Flipflop Throw Toy</x:v>
+      </x:c>
+      <x:c r="B243" s="230" t="str">
+        <x:v>/images/pets/Flipflop Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C243" s="238"/>
+      <x:c r="D243" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="19" customHeight="1">
+      <x:c r="A244" s="230" t="str">
+        <x:v>Floatie Raft</x:v>
+      </x:c>
+      <x:c r="B244" s="230" t="str">
+        <x:v>/images/pets/Floatie Raft.png</x:v>
+      </x:c>
+      <x:c r="C244" s="238"/>
+      <x:c r="D244" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="19" customHeight="1">
+      <x:c r="A245" s="230" t="str">
+        <x:v>Floaties</x:v>
+      </x:c>
+      <x:c r="B245" s="230" t="str">
+        <x:v>/images/pets/Floaties.png</x:v>
+      </x:c>
+      <x:c r="C245" s="238"/>
+      <x:c r="D245" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" ht="19" customHeight="1">
+      <x:c r="A246" s="230" t="str">
+        <x:v>Floppy Bunny Plushie</x:v>
+      </x:c>
+      <x:c r="B246" s="230" t="str">
+        <x:v>/images/pets/Floppy Bunny Plushie.png</x:v>
+      </x:c>
+      <x:c r="C246" s="238"/>
+      <x:c r="D246" s="234" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" ht="19" customHeight="1">
+      <x:c r="A247" s="230" t="str">
+        <x:v>Flower Cloud Plush</x:v>
+      </x:c>
+      <x:c r="B247" s="230" t="str">
+        <x:v>/images/pets/Flower Cloud Plush.png</x:v>
+      </x:c>
+      <x:c r="C247" s="238"/>
+      <x:c r="D247" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" ht="19" customHeight="1">
+      <x:c r="A248" s="230" t="str">
+        <x:v>Flower Flying Disc</x:v>
+      </x:c>
+      <x:c r="B248" s="230" t="str">
+        <x:v>/images/pets/Flower Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C248" s="238"/>
+      <x:c r="D248" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" ht="19" customHeight="1">
+      <x:c r="A249" s="230" t="str">
+        <x:v>Flower Frisbee</x:v>
+      </x:c>
+      <x:c r="B249" s="230" t="str">
+        <x:v>/images/pets/Flower Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C249" s="238"/>
+      <x:c r="D249" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" ht="19" customHeight="1">
+      <x:c r="A250" s="230" t="str">
+        <x:v>Flower Mirror Chew Toy</x:v>
+      </x:c>
+      <x:c r="B250" s="230" t="str">
+        <x:v>/images/pets/Flower Mirror Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C250" s="238"/>
+      <x:c r="D250" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" ht="19" customHeight="1">
+      <x:c r="A251" s="230" t="str">
+        <x:v>Flower Rattle</x:v>
+      </x:c>
+      <x:c r="B251" s="230" t="str">
+        <x:v>/images/pets/Flower Rattle.png</x:v>
+      </x:c>
+      <x:c r="C251" s="238"/>
+      <x:c r="D251" s="234" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" ht="19" customHeight="1">
+      <x:c r="A252" s="230" t="str">
+        <x:v>Flying Broomstick</x:v>
+      </x:c>
+      <x:c r="B252" s="230" t="str">
+        <x:v>/images/pets/Flying Broomstick.png</x:v>
+      </x:c>
+      <x:c r="C252" s="238"/>
+      <x:c r="D252" s="234" t="n">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" ht="19" customHeight="1">
+      <x:c r="A253" s="230" t="str">
+        <x:v>Flying Clock</x:v>
+      </x:c>
+      <x:c r="B253" s="230" t="str">
+        <x:v>/images/pets/Flying Clock.png</x:v>
+      </x:c>
+      <x:c r="C253" s="238"/>
+      <x:c r="D253" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" ht="19" customHeight="1">
+      <x:c r="A254" s="230" t="str">
+        <x:v>Flying Disc</x:v>
+      </x:c>
+      <x:c r="B254" s="230" t="str">
+        <x:v>/images/pets/Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C254" s="238"/>
+      <x:c r="D254" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" ht="19" customHeight="1">
+      <x:c r="A255" s="230" t="str">
+        <x:v>Flying Disc Umbrella</x:v>
+      </x:c>
+      <x:c r="B255" s="230" t="str">
+        <x:v>/images/pets/Flying Disc Umbrella.png</x:v>
+      </x:c>
+      <x:c r="C255" s="238"/>
+      <x:c r="D255" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" ht="19" customHeight="1">
+      <x:c r="A256" s="230" t="str">
+        <x:v>Flying Saucer Disc</x:v>
+      </x:c>
+      <x:c r="B256" s="230" t="str">
+        <x:v>/images/pets/Flying Saucer Disc.png</x:v>
+      </x:c>
+      <x:c r="C256" s="238"/>
+      <x:c r="D256" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" ht="19" customHeight="1">
+      <x:c r="A257" s="230" t="str">
+        <x:v>Football Throw Toy</x:v>
+      </x:c>
+      <x:c r="B257" s="230" t="str">
+        <x:v>/images/pets/Football Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C257" s="238"/>
+      <x:c r="D257" s="234" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" ht="19" customHeight="1">
+      <x:c r="A258" s="230" t="str">
+        <x:v>Fortune Wheel Flying Disc</x:v>
+      </x:c>
+      <x:c r="B258" s="230" t="str">
+        <x:v>/images/pets/Fortune Wheel Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C258" s="238"/>
+      <x:c r="D258" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" ht="19" customHeight="1">
+      <x:c r="A259" s="230" t="str">
+        <x:v>Fossil</x:v>
+      </x:c>
+      <x:c r="B259" s="230" t="str">
+        <x:v>/images/pets/Fossil.png</x:v>
+      </x:c>
+      <x:c r="C259" s="238"/>
+      <x:c r="D259" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" ht="19" customHeight="1">
+      <x:c r="A260" s="230" t="str">
+        <x:v>Founder's Key Throw Toy</x:v>
+      </x:c>
+      <x:c r="B260" s="230" t="str">
+        <x:v>/images/pets/Founder's Key Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C260" s="238"/>
+      <x:c r="D260" s="234" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" ht="19" customHeight="1">
+      <x:c r="A261" s="230" t="str">
+        <x:v>Frisbee</x:v>
+      </x:c>
+      <x:c r="B261" s="230" t="str">
+        <x:v>/images/pets/Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C261" s="238"/>
+      <x:c r="D261" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" ht="19" customHeight="1">
+      <x:c r="A262" s="230" t="str">
+        <x:v>Frisbee Umbrella</x:v>
+      </x:c>
+      <x:c r="B262" s="230" t="str">
+        <x:v>/images/pets/Frisbee Umbrella.png</x:v>
+      </x:c>
+      <x:c r="C262" s="238"/>
+      <x:c r="D262" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" ht="19" customHeight="1">
+      <x:c r="A263" s="230" t="str">
+        <x:v>Frog In A Pitcher Leash</x:v>
+      </x:c>
+      <x:c r="B263" s="230" t="str">
+        <x:v>/images/pets/Frog In A Pitcher Leash.png</x:v>
+      </x:c>
+      <x:c r="C263" s="238"/>
+      <x:c r="D263" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" ht="19" customHeight="1">
+      <x:c r="A264" s="230" t="str">
+        <x:v>Frostbite Grapple</x:v>
+      </x:c>
+      <x:c r="B264" s="230" t="str">
+        <x:v>/images/pets/Frostbite Grapple.png</x:v>
+      </x:c>
+      <x:c r="C264" s="238"/>
+      <x:c r="D264" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" ht="19" customHeight="1">
+      <x:c r="A265" s="230" t="str">
+        <x:v>Frostclaw Plush</x:v>
+      </x:c>
+      <x:c r="B265" s="230" t="str">
+        <x:v>/images/pets/Frostclaw Plush.png</x:v>
+      </x:c>
+      <x:c r="C265" s="238"/>
+      <x:c r="D265" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" ht="19" customHeight="1">
+      <x:c r="A266" s="230" t="str">
+        <x:v>Frosty Glow Mega Neon Paint</x:v>
+      </x:c>
+      <x:c r="B266" s="230" t="str">
+        <x:v>/images/pets/Frosty Glow Mega Neon Paint.png</x:v>
+      </x:c>
+      <x:c r="C266" s="238"/>
+      <x:c r="D266" s="234" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" ht="19" customHeight="1">
+      <x:c r="A267" s="230" t="str">
+        <x:v>Frozen Balloon</x:v>
+      </x:c>
+      <x:c r="B267" s="230" t="str">
+        <x:v>/images/pets/Frozen Balloon.png</x:v>
+      </x:c>
+      <x:c r="C267" s="238"/>
+      <x:c r="D267" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" ht="19" customHeight="1">
+      <x:c r="A268" s="230" t="str">
+        <x:v>Full Moon Flying Disc</x:v>
+      </x:c>
+      <x:c r="B268" s="230" t="str">
+        <x:v>/images/pets/Full Moon Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C268" s="238"/>
+      <x:c r="D268" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" ht="19" customHeight="1">
+      <x:c r="A269" s="230" t="str">
+        <x:v>Fun Flying Disc</x:v>
+      </x:c>
+      <x:c r="B269" s="230" t="str">
+        <x:v>/images/pets/Fun Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C269" s="238"/>
+      <x:c r="D269" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" ht="19" customHeight="1">
+      <x:c r="A270" s="230" t="str">
+        <x:v>Fun Frisbee</x:v>
+      </x:c>
+      <x:c r="B270" s="230" t="str">
+        <x:v>/images/pets/Fun Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C270" s="238"/>
+      <x:c r="D270" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" ht="19" customHeight="1">
+      <x:c r="A271" s="230" t="str">
+        <x:v>Futuristic Grapple</x:v>
+      </x:c>
+      <x:c r="B271" s="230" t="str">
+        <x:v>/images/pets/Futuristic Grapple.png</x:v>
+      </x:c>
+      <x:c r="C271" s="238"/>
+      <x:c r="D271" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" ht="19" customHeight="1">
+      <x:c r="A272" s="230" t="str">
+        <x:v>Futuristic Turbine Propeller</x:v>
+      </x:c>
+      <x:c r="B272" s="230" t="str">
+        <x:v>/images/pets/Futuristic Turbine Propeller.png</x:v>
+      </x:c>
+      <x:c r="C272" s="238"/>
+      <x:c r="D272" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" ht="19" customHeight="1">
+      <x:c r="A273" s="230" t="str">
+        <x:v>Galaxy Flying Disc</x:v>
+      </x:c>
+      <x:c r="B273" s="230" t="str">
+        <x:v>/images/pets/Galaxy Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C273" s="238"/>
+      <x:c r="D273" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" ht="19" customHeight="1">
+      <x:c r="A274" s="230" t="str">
+        <x:v>Galaxy Propeller</x:v>
+      </x:c>
+      <x:c r="B274" s="230" t="str">
+        <x:v>/images/pets/Galaxy Propeller.png</x:v>
+      </x:c>
+      <x:c r="C274" s="238"/>
+      <x:c r="D274" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" ht="19" customHeight="1">
+      <x:c r="A275" s="230" t="str">
+        <x:v>Gay Flag</x:v>
+      </x:c>
+      <x:c r="B275" s="230" t="str">
+        <x:v>/images/pets/Gay Flag.png</x:v>
+      </x:c>
+      <x:c r="C275" s="238"/>
+      <x:c r="D275" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" ht="19" customHeight="1">
+      <x:c r="A276" s="230" t="str">
+        <x:v>Gay Man Flag</x:v>
+      </x:c>
+      <x:c r="B276" s="230" t="str">
+        <x:v>/images/pets/Gay Man Flag.png</x:v>
+      </x:c>
+      <x:c r="C276" s="238"/>
+      <x:c r="D276" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" ht="19" customHeight="1">
+      <x:c r="A277" s="230" t="str">
+        <x:v>Gender Fluid Flag</x:v>
+      </x:c>
+      <x:c r="B277" s="230" t="str">
+        <x:v>/images/pets/Gender Fluid Flag.png</x:v>
+      </x:c>
+      <x:c r="C277" s="238"/>
+      <x:c r="D277" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" ht="19" customHeight="1">
+      <x:c r="A278" s="230" t="str">
+        <x:v>Gender Queer Flag</x:v>
+      </x:c>
+      <x:c r="B278" s="230" t="str">
+        <x:v>/images/pets/Gender Queer Flag.png</x:v>
+      </x:c>
+      <x:c r="C278" s="238"/>
+      <x:c r="D278" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" ht="19" customHeight="1">
+      <x:c r="A279" s="230" t="str">
+        <x:v>Ghost Finder Rattle</x:v>
+      </x:c>
+      <x:c r="B279" s="230" t="str">
+        <x:v>/images/pets/Ghost Finder Rattle.png</x:v>
+      </x:c>
+      <x:c r="C279" s="238"/>
+      <x:c r="D279" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" ht="19" customHeight="1">
+      <x:c r="A280" s="230" t="str">
+        <x:v>Gift Sack Pogo</x:v>
+      </x:c>
+      <x:c r="B280" s="230" t="str">
+        <x:v>/images/pets/Gift Sack Pogo.png</x:v>
+      </x:c>
+      <x:c r="C280" s="238"/>
+      <x:c r="D280" s="234" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" ht="19" customHeight="1">
+      <x:c r="A281" s="230" t="str">
+        <x:v>Gift Stack Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B281" s="230" t="str">
+        <x:v>/images/pets/Gift Stack Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C281" s="238"/>
+      <x:c r="D281" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" ht="19" customHeight="1">
+      <x:c r="A282" s="230" t="str">
+        <x:v>Gift Throw Toy</x:v>
+      </x:c>
+      <x:c r="B282" s="230" t="str">
+        <x:v>/images/pets/Gift Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C282" s="238"/>
+      <x:c r="D282" s="234" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" ht="19" customHeight="1">
+      <x:c r="A283" s="230" t="str">
+        <x:v>Giggle Puff Balloon</x:v>
+      </x:c>
+      <x:c r="B283" s="230" t="str">
+        <x:v>/images/pets/Giggle Puff Balloon.png</x:v>
+      </x:c>
+      <x:c r="C283" s="238"/>
+      <x:c r="D283" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" ht="19" customHeight="1">
+      <x:c r="A284" s="230" t="str">
+        <x:v>Gingerbread Balloon</x:v>
+      </x:c>
+      <x:c r="B284" s="230" t="str">
+        <x:v>/images/pets/Gingerbread Balloon.png</x:v>
+      </x:c>
+      <x:c r="C284" s="238"/>
+      <x:c r="D284" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" ht="19" customHeight="1">
+      <x:c r="A285" s="230" t="str">
+        <x:v>Gingerbread Bear Balloon</x:v>
+      </x:c>
+      <x:c r="B285" s="230" t="str">
+        <x:v>/images/pets/Gingerbread Bear Balloon.png</x:v>
+      </x:c>
+      <x:c r="C285" s="238"/>
+      <x:c r="D285" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" ht="19" customHeight="1">
+      <x:c r="A286" s="230" t="str">
+        <x:v>Gingerbread Face Flying Disc</x:v>
+      </x:c>
+      <x:c r="B286" s="230" t="str">
+        <x:v>/images/pets/Gingerbread Face Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C286" s="238"/>
+      <x:c r="D286" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" ht="19" customHeight="1">
+      <x:c r="A287" s="230" t="str">
+        <x:v>Gingerbread Heart Flying Disc</x:v>
+      </x:c>
+      <x:c r="B287" s="230" t="str">
+        <x:v>/images/pets/Gingerbread Heart Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C287" s="238"/>
+      <x:c r="D287" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" ht="19" customHeight="1">
+      <x:c r="A288" s="230" t="str">
+        <x:v>Gingerbread Holly Flying Disc</x:v>
+      </x:c>
+      <x:c r="B288" s="230" t="str">
+        <x:v>/images/pets/Gingerbread Holly Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C288" s="238"/>
+      <x:c r="D288" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" ht="19" customHeight="1">
+      <x:c r="A289" s="230" t="str">
+        <x:v>Gingerbread House Throw Toy</x:v>
+      </x:c>
+      <x:c r="B289" s="230" t="str">
+        <x:v>/images/pets/Gingerbread House Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C289" s="238"/>
+      <x:c r="D289" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" ht="19" customHeight="1">
+      <x:c r="A290" s="230" t="str">
+        <x:v>Gingerbread Kitty Throw Toy</x:v>
+      </x:c>
+      <x:c r="B290" s="230" t="str">
+        <x:v>/images/pets/Gingerbread Kitty Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C290" s="238"/>
+      <x:c r="D290" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" ht="19" customHeight="1">
+      <x:c r="A291" s="230" t="str">
+        <x:v>Gingerbread Leash</x:v>
+      </x:c>
+      <x:c r="B291" s="230" t="str">
+        <x:v>/images/pets/Gingerbread Leash.png</x:v>
+      </x:c>
+      <x:c r="C291" s="238"/>
+      <x:c r="D291" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" ht="19" customHeight="1">
+      <x:c r="A292" s="230" t="str">
+        <x:v>Gingerbread Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B292" s="230" t="str">
+        <x:v>/images/pets/Gingerbread Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C292" s="238"/>
+      <x:c r="D292" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" ht="19" customHeight="1">
+      <x:c r="A293" s="230" t="str">
+        <x:v>Gingerbread Rattle</x:v>
+      </x:c>
+      <x:c r="B293" s="230" t="str">
+        <x:v>/images/pets/Gingerbread Rattle.png</x:v>
+      </x:c>
+      <x:c r="C293" s="238"/>
+      <x:c r="D293" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" ht="19" customHeight="1">
+      <x:c r="A294" s="230" t="str">
+        <x:v>Gingerbread Star Propeller</x:v>
+      </x:c>
+      <x:c r="B294" s="230" t="str">
+        <x:v>/images/pets/Gingerbread Star Propeller.png</x:v>
+      </x:c>
+      <x:c r="C294" s="238"/>
+      <x:c r="D294" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" ht="19" customHeight="1">
+      <x:c r="A295" s="230" t="str">
+        <x:v>Gingerbread Stocking Toy</x:v>
+      </x:c>
+      <x:c r="B295" s="230" t="str">
+        <x:v>/images/pets/Gingerbread Stocking Toy.png</x:v>
+      </x:c>
+      <x:c r="C295" s="238"/>
+      <x:c r="D295" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" ht="19" customHeight="1">
+      <x:c r="A296" s="230" t="str">
+        <x:v>Gingerbread Wreath Flying Disc</x:v>
+      </x:c>
+      <x:c r="B296" s="230" t="str">
+        <x:v>/images/pets/Gingerbread Wreath Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C296" s="238"/>
+      <x:c r="D296" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" ht="19" customHeight="1">
+      <x:c r="A297" s="230" t="str">
+        <x:v>Glider</x:v>
+      </x:c>
+      <x:c r="B297" s="230" t="str">
+        <x:v>/images/pets/Glider.png</x:v>
+      </x:c>
+      <x:c r="C297" s="238"/>
+      <x:c r="D297" s="234" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" ht="19" customHeight="1">
+      <x:c r="A298" s="230" t="str">
+        <x:v>Glyptoball</x:v>
+      </x:c>
+      <x:c r="B298" s="230" t="str">
+        <x:v>/images/pets/Glyptoball.png</x:v>
+      </x:c>
+      <x:c r="C298" s="238"/>
+      <x:c r="D298" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" ht="19" customHeight="1">
+      <x:c r="A299" s="230" t="str">
+        <x:v>Gold Star</x:v>
+      </x:c>
+      <x:c r="B299" s="230" t="str">
+        <x:v>/images/pets/Gold Star.png</x:v>
+      </x:c>
+      <x:c r="C299" s="238"/>
+      <x:c r="D299" s="234" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" ht="19" customHeight="1">
+      <x:c r="A300" s="230" t="str">
+        <x:v>Golden Goblet</x:v>
+      </x:c>
+      <x:c r="B300" s="230" t="str">
+        <x:v>/images/pets/Golden Goblet.png</x:v>
+      </x:c>
+      <x:c r="C300" s="238"/>
+      <x:c r="D300" s="234" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" ht="19" customHeight="1">
+      <x:c r="A301" s="230" t="str">
+        <x:v>Golden Maned Unicorn Rattle</x:v>
+      </x:c>
+      <x:c r="B301" s="230" t="str">
+        <x:v>/images/pets/Golden Maned Unicorn Rattle.png</x:v>
+      </x:c>
+      <x:c r="C301" s="238"/>
+      <x:c r="D301" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" ht="19" customHeight="1">
+      <x:c r="A302" s="230" t="str">
+        <x:v>Golden Rings Flying Disc</x:v>
+      </x:c>
+      <x:c r="B302" s="230" t="str">
+        <x:v>/images/pets/Golden Rings Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C302" s="238"/>
+      <x:c r="D302" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" ht="19" customHeight="1">
+      <x:c r="A303" s="230" t="str">
+        <x:v>Golden Scale Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B303" s="230" t="str">
+        <x:v>/images/pets/Golden Scale Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C303" s="238"/>
+      <x:c r="D303" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" ht="19" customHeight="1">
+      <x:c r="A304" s="230" t="str">
+        <x:v>Googly Eye Conker Plush</x:v>
+      </x:c>
+      <x:c r="B304" s="230" t="str">
+        <x:v>/images/pets/Googly Eye Conker Plush.png</x:v>
+      </x:c>
+      <x:c r="C304" s="238"/>
+      <x:c r="D304" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" ht="19" customHeight="1">
+      <x:c r="A305" s="230" t="str">
+        <x:v>Grapplenana</x:v>
+      </x:c>
+      <x:c r="B305" s="230" t="str">
+        <x:v>/images/pets/Grapplenana.png</x:v>
+      </x:c>
+      <x:c r="C305" s="238"/>
+      <x:c r="D305" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" ht="19" customHeight="1">
+      <x:c r="A306" s="230" t="str">
+        <x:v>Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B306" s="230" t="str">
+        <x:v>/images/pets/Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C306" s="238"/>
+      <x:c r="D306" s="234" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" ht="19" customHeight="1">
+      <x:c r="A307" s="230" t="str">
+        <x:v>Green Pogostick</x:v>
+      </x:c>
+      <x:c r="B307" s="230" t="str">
+        <x:v>/images/pets/Green Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C307" s="238"/>
+      <x:c r="D307" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" ht="19" customHeight="1">
+      <x:c r="A308" s="230" t="str">
+        <x:v>Griffin Propeller</x:v>
+      </x:c>
+      <x:c r="B308" s="230" t="str">
+        <x:v>/images/pets/Griffin Propeller.png</x:v>
+      </x:c>
+      <x:c r="C308" s="238"/>
+      <x:c r="D308" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" ht="19" customHeight="1">
+      <x:c r="A309" s="230" t="str">
+        <x:v>Grim Scythe</x:v>
+      </x:c>
+      <x:c r="B309" s="230" t="str">
+        <x:v>/images/pets/Grim Scythe.png</x:v>
+      </x:c>
+      <x:c r="C309" s="238"/>
+      <x:c r="D309" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" ht="19" customHeight="1">
+      <x:c r="A310" s="230" t="str">
+        <x:v>Hairbrush Chew Toy</x:v>
+      </x:c>
+      <x:c r="B310" s="230" t="str">
+        <x:v>/images/pets/Hairbrush Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C310" s="238"/>
+      <x:c r="D310" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" ht="19" customHeight="1">
+      <x:c r="A311" s="230" t="str">
+        <x:v>Half Glow Mushroom</x:v>
+      </x:c>
+      <x:c r="B311" s="230" t="str">
+        <x:v>/images/pets/Half Glow Mushroom.png</x:v>
+      </x:c>
+      <x:c r="C311" s="238"/>
+      <x:c r="D311" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" ht="19" customHeight="1">
+      <x:c r="A312" s="230" t="str">
+        <x:v>Halloween Black Bat Propeller</x:v>
+      </x:c>
+      <x:c r="B312" s="230" t="str">
+        <x:v>/images/pets/Halloween Black Bat Propeller.png</x:v>
+      </x:c>
+      <x:c r="C312" s="238"/>
+      <x:c r="D312" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" ht="19" customHeight="1">
+      <x:c r="A313" s="230" t="str">
+        <x:v>Halloween Black Victorian Candlestick Rattle</x:v>
+      </x:c>
+      <x:c r="B313" s="230" t="str">
+        <x:v>/images/pets/Halloween Black Victorian Candlestick Rattle.png</x:v>
+      </x:c>
+      <x:c r="C313" s="238"/>
+      <x:c r="D313" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" ht="19" customHeight="1">
+      <x:c r="A314" s="230" t="str">
+        <x:v>Halloween Orange Pumpkin Balloon</x:v>
+      </x:c>
+      <x:c r="B314" s="230" t="str">
+        <x:v>/images/pets/Halloween Orange Pumpkin Balloon.png</x:v>
+      </x:c>
+      <x:c r="C314" s="238"/>
+      <x:c r="D314" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" ht="19" customHeight="1">
+      <x:c r="A315" s="230" t="str">
+        <x:v>Halloween Orange Pumpkin Flying Disc</x:v>
+      </x:c>
+      <x:c r="B315" s="230" t="str">
+        <x:v>/images/pets/Halloween Orange Pumpkin Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C315" s="238"/>
+      <x:c r="D315" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" ht="19" customHeight="1">
+      <x:c r="A316" s="230" t="str">
+        <x:v>Halloween Orange Pumpkin Voodoo Doll</x:v>
+      </x:c>
+      <x:c r="B316" s="230" t="str">
+        <x:v>/images/pets/Halloween Orange Pumpkin Voodoo Doll.png</x:v>
+      </x:c>
+      <x:c r="C316" s="238"/>
+      <x:c r="D316" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" ht="19" customHeight="1">
+      <x:c r="A317" s="230" t="str">
+        <x:v>Halloween Slime Mega Neon Paint</x:v>
+      </x:c>
+      <x:c r="B317" s="230" t="str">
+        <x:v>/images/pets/Halloween Slime Mega Neon Paint.png</x:v>
+      </x:c>
+      <x:c r="C317" s="238"/>
+      <x:c r="D317" s="234" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" ht="19" customHeight="1">
+      <x:c r="A318" s="230" t="str">
+        <x:v>Halloween White Ghost Balloon</x:v>
+      </x:c>
+      <x:c r="B318" s="230" t="str">
+        <x:v>/images/pets/Halloween White Ghost Balloon.png</x:v>
+      </x:c>
+      <x:c r="C318" s="238"/>
+      <x:c r="D318" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" ht="19" customHeight="1">
+      <x:c r="A319" s="230" t="str">
+        <x:v>Halloween Wooden Scythe Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B319" s="230" t="str">
+        <x:v>/images/pets/Halloween Wooden Scythe Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C319" s="238"/>
+      <x:c r="D319" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" ht="19" customHeight="1">
+      <x:c r="A320" s="230" t="str">
+        <x:v>Hand Cannon Leash</x:v>
+      </x:c>
+      <x:c r="B320" s="230" t="str">
+        <x:v>/images/pets/Hand Cannon Leash.png</x:v>
+      </x:c>
+      <x:c r="C320" s="238"/>
+      <x:c r="D320" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" ht="19" customHeight="1">
+      <x:c r="A321" s="230" t="str">
+        <x:v>Hang Glider Balloon</x:v>
+      </x:c>
+      <x:c r="B321" s="230" t="str">
+        <x:v>/images/pets/Hang Glider Balloon.png</x:v>
+      </x:c>
+      <x:c r="C321" s="238"/>
+      <x:c r="D321" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" ht="19" customHeight="1">
+      <x:c r="A322" s="230" t="str">
+        <x:v>Happy Tooth Chew Toy</x:v>
+      </x:c>
+      <x:c r="B322" s="230" t="str">
+        <x:v>/images/pets/Happy Tooth Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C322" s="238"/>
+      <x:c r="D322" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" ht="19" customHeight="1">
+      <x:c r="A323" s="230" t="str">
+        <x:v>Harp Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B323" s="230" t="str">
+        <x:v>/images/pets/Harp Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C323" s="238"/>
+      <x:c r="D323" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" ht="19" customHeight="1">
+      <x:c r="A324" s="230" t="str">
+        <x:v>Heart Balloon</x:v>
+      </x:c>
+      <x:c r="B324" s="230" t="str">
+        <x:v>/images/pets/Heart Balloon.png</x:v>
+      </x:c>
+      <x:c r="C324" s="238"/>
+      <x:c r="D324" s="234" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" ht="19" customHeight="1">
+      <x:c r="A325" s="230" t="str">
+        <x:v>Heart Plushie</x:v>
+      </x:c>
+      <x:c r="B325" s="230" t="str">
+        <x:v>/images/pets/Heart Plushie.png</x:v>
+      </x:c>
+      <x:c r="C325" s="238"/>
+      <x:c r="D325" s="234" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" ht="19" customHeight="1">
+      <x:c r="A326" s="230" t="str">
+        <x:v>Heart Rattle</x:v>
+      </x:c>
+      <x:c r="B326" s="230" t="str">
+        <x:v>/images/pets/Heart Rattle.png</x:v>
+      </x:c>
+      <x:c r="C326" s="238"/>
+      <x:c r="D326" s="234" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" ht="19" customHeight="1">
+      <x:c r="A327" s="230" t="str">
+        <x:v>Heart Throwing Disc</x:v>
+      </x:c>
+      <x:c r="B327" s="230" t="str">
+        <x:v>/images/pets/Heart Throwing Disc.png</x:v>
+      </x:c>
+      <x:c r="C327" s="238"/>
+      <x:c r="D327" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" ht="19" customHeight="1">
+      <x:c r="A328" s="230" t="str">
+        <x:v>Holiday Breadstick Chew Toy</x:v>
+      </x:c>
+      <x:c r="B328" s="230" t="str">
+        <x:v>/images/pets/Holiday Breadstick Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C328" s="238"/>
+      <x:c r="D328" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" ht="19" customHeight="1">
+      <x:c r="A329" s="230" t="str">
+        <x:v>Holly Leash</x:v>
+      </x:c>
+      <x:c r="B329" s="230" t="str">
+        <x:v>/images/pets/Holly Leash.png</x:v>
+      </x:c>
+      <x:c r="C329" s="238"/>
+      <x:c r="D329" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" ht="19" customHeight="1">
+      <x:c r="A330" s="230" t="str">
+        <x:v>Homeing Rocket</x:v>
+      </x:c>
+      <x:c r="B330" s="230" t="str">
+        <x:v>/images/pets/Homeing Rocket.png</x:v>
+      </x:c>
+      <x:c r="C330" s="238"/>
+      <x:c r="D330" s="234" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" ht="19" customHeight="1">
+      <x:c r="A331" s="230" t="str">
+        <x:v>Honey Dipper Rattle</x:v>
+      </x:c>
+      <x:c r="B331" s="230" t="str">
+        <x:v>/images/pets/Honey Dipper Rattle.png</x:v>
+      </x:c>
+      <x:c r="C331" s="238"/>
+      <x:c r="D331" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" ht="19" customHeight="1">
+      <x:c r="A332" s="230" t="str">
+        <x:v>Hook Hand Grappling Hood</x:v>
+      </x:c>
+      <x:c r="B332" s="230" t="str">
+        <x:v>/images/pets/Hook Hand Grappling Hood.png</x:v>
+      </x:c>
+      <x:c r="C332" s="238"/>
+      <x:c r="D332" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" ht="19" customHeight="1">
+      <x:c r="A333" s="230" t="str">
+        <x:v>Hook Hand Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B333" s="230" t="str">
+        <x:v>/images/pets/Hook Hand Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C333" s="238"/>
+      <x:c r="D333" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" ht="19" customHeight="1">
+      <x:c r="A334" s="230" t="str">
+        <x:v>Horse Plush</x:v>
+      </x:c>
+      <x:c r="B334" s="230" t="str">
+        <x:v>/images/pets/Horse Plush.png</x:v>
+      </x:c>
+      <x:c r="C334" s="238"/>
+      <x:c r="D334" s="234" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" ht="19" customHeight="1">
+      <x:c r="A335" s="230" t="str">
+        <x:v>Hot Cocoa Stand</x:v>
+      </x:c>
+      <x:c r="B335" s="230" t="str">
+        <x:v>/images/pets/Hot Cocoa Stand.png</x:v>
+      </x:c>
+      <x:c r="C335" s="238"/>
+      <x:c r="D335" s="234" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" ht="19" customHeight="1">
+      <x:c r="A336" s="230" t="str">
+        <x:v>Hotdog Stand</x:v>
+      </x:c>
+      <x:c r="B336" s="230" t="str">
+        <x:v>/images/pets/Hotdog Stand.png</x:v>
+      </x:c>
+      <x:c r="C336" s="238"/>
+      <x:c r="D336" s="234" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" ht="19" customHeight="1">
+      <x:c r="A337" s="230" t="str">
+        <x:v>Huggable Pillow</x:v>
+      </x:c>
+      <x:c r="B337" s="230" t="str">
+        <x:v>/images/pets/Huggable Pillow.png</x:v>
+      </x:c>
+      <x:c r="C337" s="238"/>
+      <x:c r="D337" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338" ht="19" customHeight="1">
+      <x:c r="A338" s="230" t="str">
+        <x:v>Hugging Egg</x:v>
+      </x:c>
+      <x:c r="B338" s="230" t="str">
+        <x:v>/images/pets/Hugging Egg.png</x:v>
+      </x:c>
+      <x:c r="C338" s="238"/>
+      <x:c r="D338" s="234" t="n">
+        <x:v>5.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" ht="19" customHeight="1">
+      <x:c r="A339" s="230" t="str">
+        <x:v>Hypnotic Flying Disc</x:v>
+      </x:c>
+      <x:c r="B339" s="230" t="str">
+        <x:v>/images/pets/Hypnotic Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C339" s="238"/>
+      <x:c r="D339" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" ht="19" customHeight="1">
+      <x:c r="A340" s="230" t="str">
+        <x:v>Hypnotic Frisbee</x:v>
+      </x:c>
+      <x:c r="B340" s="230" t="str">
+        <x:v>/images/pets/Hypnotic Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C340" s="238"/>
+      <x:c r="D340" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341" ht="19" customHeight="1">
+      <x:c r="A341" s="230" t="str">
+        <x:v>Ice Club Rattle</x:v>
+      </x:c>
+      <x:c r="B341" s="230" t="str">
+        <x:v>/images/pets/Ice Club Rattle.png</x:v>
+      </x:c>
+      <x:c r="C341" s="238"/>
+      <x:c r="D341" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" ht="19" customHeight="1">
+      <x:c r="A342" s="230" t="str">
+        <x:v>Ice Cream Plush</x:v>
+      </x:c>
+      <x:c r="B342" s="230" t="str">
+        <x:v>/images/pets/Ice Cream Plush.png</x:v>
+      </x:c>
+      <x:c r="C342" s="238"/>
+      <x:c r="D342" s="234" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" ht="19" customHeight="1">
+      <x:c r="A343" s="230" t="str">
+        <x:v>Ice Cream Rattle</x:v>
+      </x:c>
+      <x:c r="B343" s="230" t="str">
+        <x:v>/images/pets/Ice Cream Rattle.png</x:v>
+      </x:c>
+      <x:c r="C343" s="238"/>
+      <x:c r="D343" s="234" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" ht="19" customHeight="1">
+      <x:c r="A344" s="230" t="str">
+        <x:v>Ice Cream Sandwich Rattle</x:v>
+      </x:c>
+      <x:c r="B344" s="230" t="str">
+        <x:v>/images/pets/Ice Cream Sandwich Rattle.png</x:v>
+      </x:c>
+      <x:c r="C344" s="238"/>
+      <x:c r="D344" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" ht="19" customHeight="1">
+      <x:c r="A345" s="230" t="str">
+        <x:v>Ice Cube Throw Toy</x:v>
+      </x:c>
+      <x:c r="B345" s="230" t="str">
+        <x:v>/images/pets/Ice Cube Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C345" s="238"/>
+      <x:c r="D345" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" ht="19" customHeight="1">
+      <x:c r="A346" s="230" t="str">
+        <x:v>Ice Grapple</x:v>
+      </x:c>
+      <x:c r="B346" s="230" t="str">
+        <x:v>/images/pets/Ice Grapple.png</x:v>
+      </x:c>
+      <x:c r="C346" s="238"/>
+      <x:c r="D346" s="234" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" ht="19" customHeight="1">
+      <x:c r="A347" s="230" t="str">
+        <x:v>Ice Pick Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B347" s="230" t="str">
+        <x:v>/images/pets/Ice Pick Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C347" s="238"/>
+      <x:c r="D347" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" ht="19" customHeight="1">
+      <x:c r="A348" s="230" t="str">
+        <x:v>Ice Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B348" s="230" t="str">
+        <x:v>/images/pets/Ice Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C348" s="238"/>
+      <x:c r="D348" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" ht="19" customHeight="1">
+      <x:c r="A349" s="230" t="str">
+        <x:v>Ice Saber</x:v>
+      </x:c>
+      <x:c r="B349" s="230" t="str">
+        <x:v>/images/pets/Ice Saber.png</x:v>
+      </x:c>
+      <x:c r="C349" s="238"/>
+      <x:c r="D349" s="234" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" ht="19" customHeight="1">
+      <x:c r="A350" s="230" t="str">
+        <x:v>Ice Wand</x:v>
+      </x:c>
+      <x:c r="B350" s="230" t="str">
+        <x:v>/images/pets/Ice Wand.png</x:v>
+      </x:c>
+      <x:c r="C350" s="238"/>
+      <x:c r="D350" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" ht="19" customHeight="1">
+      <x:c r="A351" s="230" t="str">
+        <x:v>Icicle Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B351" s="230" t="str">
+        <x:v>/images/pets/Icicle Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C351" s="238"/>
+      <x:c r="D351" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" ht="19" customHeight="1">
+      <x:c r="A352" s="230" t="str">
+        <x:v>Icicle Throw Toy</x:v>
+      </x:c>
+      <x:c r="B352" s="230" t="str">
+        <x:v>/images/pets/Icicle Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C352" s="238"/>
+      <x:c r="D352" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" ht="19" customHeight="1">
+      <x:c r="A353" s="230" t="str">
+        <x:v>Icing Bag Leash</x:v>
+      </x:c>
+      <x:c r="B353" s="230" t="str">
+        <x:v>/images/pets/Icing Bag Leash.png</x:v>
+      </x:c>
+      <x:c r="C353" s="238"/>
+      <x:c r="D353" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" ht="19" customHeight="1">
+      <x:c r="A354" s="230" t="str">
+        <x:v>Illusionary Throw Hat</x:v>
+      </x:c>
+      <x:c r="B354" s="230" t="str">
+        <x:v>/images/pets/Illusionary Throw Hat.png</x:v>
+      </x:c>
+      <x:c r="C354" s="238"/>
+      <x:c r="D354" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" ht="19" customHeight="1">
+      <x:c r="A355" s="230" t="str">
+        <x:v>Inflatable Sword</x:v>
+      </x:c>
+      <x:c r="B355" s="230" t="str">
+        <x:v>/images/pets/Inflatable Sword.png</x:v>
+      </x:c>
+      <x:c r="C355" s="238"/>
+      <x:c r="D355" s="234" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" ht="19" customHeight="1">
+      <x:c r="A356" s="230" t="str">
+        <x:v>Inner Tube</x:v>
+      </x:c>
+      <x:c r="B356" s="230" t="str">
+        <x:v>/images/pets/Inner Tube.png</x:v>
+      </x:c>
+      <x:c r="C356" s="238"/>
+      <x:c r="D356" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" ht="19" customHeight="1">
+      <x:c r="A357" s="230" t="str">
+        <x:v>Intersex Flag</x:v>
+      </x:c>
+      <x:c r="B357" s="230" t="str">
+        <x:v>/images/pets/Intersex Flag.png</x:v>
+      </x:c>
+      <x:c r="C357" s="238"/>
+      <x:c r="D357" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" ht="19" customHeight="1">
+      <x:c r="A358" s="230" t="str">
+        <x:v>Iron Pickaxe</x:v>
+      </x:c>
+      <x:c r="B358" s="230" t="str">
+        <x:v>/images/pets/Iron Pickaxe.png</x:v>
+      </x:c>
+      <x:c r="C358" s="238"/>
+      <x:c r="D358" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" ht="19" customHeight="1">
+      <x:c r="A359" s="230" t="str">
+        <x:v>Jack O'Bounce Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B359" s="230" t="str">
+        <x:v>/images/pets/Jack O'Bounce Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C359" s="238"/>
+      <x:c r="D359" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" ht="19" customHeight="1">
+      <x:c r="A360" s="230" t="str">
+        <x:v>Jack-O-Lantern Light</x:v>
+      </x:c>
+      <x:c r="B360" s="230" t="str">
+        <x:v>/images/pets/Jack-O-Lantern Light.png</x:v>
+      </x:c>
+      <x:c r="C360" s="238"/>
+      <x:c r="D360" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" ht="19" customHeight="1">
+      <x:c r="A361" s="230" t="str">
+        <x:v>Jackhammer</x:v>
+      </x:c>
+      <x:c r="B361" s="230" t="str">
+        <x:v>/images/pets/Jackhammer.png</x:v>
+      </x:c>
+      <x:c r="C361" s="238"/>
+      <x:c r="D361" s="234" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" ht="19" customHeight="1">
+      <x:c r="A362" s="230" t="str">
+        <x:v>Jegi Throw Toy</x:v>
+      </x:c>
+      <x:c r="B362" s="230" t="str">
+        <x:v>/images/pets/Jegi Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C362" s="238"/>
+      <x:c r="D362" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" ht="19" customHeight="1">
+      <x:c r="A363" s="230" t="str">
+        <x:v>Jelly Propeller</x:v>
+      </x:c>
+      <x:c r="B363" s="230" t="str">
+        <x:v>/images/pets/Jelly Propeller.png</x:v>
+      </x:c>
+      <x:c r="C363" s="238"/>
+      <x:c r="D363" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364" ht="19" customHeight="1">
+      <x:c r="A364" s="230" t="str">
+        <x:v>Jellybean Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B364" s="230" t="str">
+        <x:v>/images/pets/Jellybean Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C364" s="238"/>
+      <x:c r="D364" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365" ht="19" customHeight="1">
+      <x:c r="A365" s="230" t="str">
+        <x:v>Kangaroo Pogo</x:v>
+      </x:c>
+      <x:c r="B365" s="230" t="str">
+        <x:v>/images/pets/Kangaroo Pogo.png</x:v>
+      </x:c>
+      <x:c r="C365" s="238"/>
+      <x:c r="D365" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366" ht="19" customHeight="1">
+      <x:c r="A366" s="230" t="str">
+        <x:v>Kazoo</x:v>
+      </x:c>
+      <x:c r="B366" s="230" t="str">
+        <x:v>/images/pets/Kazoo.png</x:v>
+      </x:c>
+      <x:c r="C366" s="238"/>
+      <x:c r="D366" s="234" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367" ht="19" customHeight="1">
+      <x:c r="A367" s="230" t="str">
+        <x:v>Key Chew Toy</x:v>
+      </x:c>
+      <x:c r="B367" s="230" t="str">
+        <x:v>/images/pets/Key Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C367" s="238"/>
+      <x:c r="D367" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368" ht="19" customHeight="1">
+      <x:c r="A368" s="230" t="str">
+        <x:v>Keyboard Leash</x:v>
+      </x:c>
+      <x:c r="B368" s="230" t="str">
+        <x:v>/images/pets/Keyboard Leash.png</x:v>
+      </x:c>
+      <x:c r="C368" s="238"/>
+      <x:c r="D368" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369" ht="19" customHeight="1">
+      <x:c r="A369" s="230" t="str">
+        <x:v>Kite Balloon</x:v>
+      </x:c>
+      <x:c r="B369" s="230" t="str">
+        <x:v>/images/pets/Kite Balloon.png</x:v>
+      </x:c>
+      <x:c r="C369" s="238"/>
+      <x:c r="D369" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370" ht="19" customHeight="1">
+      <x:c r="A370" s="230" t="str">
+        <x:v>Kitty Propeller</x:v>
+      </x:c>
+      <x:c r="B370" s="230" t="str">
+        <x:v>/images/pets/Kitty Propeller.png</x:v>
+      </x:c>
+      <x:c r="C370" s="238"/>
+      <x:c r="D370" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" ht="19" customHeight="1">
+      <x:c r="A371" s="230" t="str">
+        <x:v>Kitty Rattle</x:v>
+      </x:c>
+      <x:c r="B371" s="230" t="str">
+        <x:v>/images/pets/Kitty Rattle.png</x:v>
+      </x:c>
+      <x:c r="C371" s="238"/>
+      <x:c r="D371" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" ht="19" customHeight="1">
+      <x:c r="A372" s="230" t="str">
+        <x:v>Ladybug Plush</x:v>
+      </x:c>
+      <x:c r="B372" s="230" t="str">
+        <x:v>/images/pets/Ladybug Plush.png</x:v>
+      </x:c>
+      <x:c r="C372" s="238"/>
+      <x:c r="D372" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" ht="19" customHeight="1">
+      <x:c r="A373" s="230" t="str">
+        <x:v>Lasso Propeller</x:v>
+      </x:c>
+      <x:c r="B373" s="230" t="str">
+        <x:v>/images/pets/Lasso Propeller.png</x:v>
+      </x:c>
+      <x:c r="C373" s="238"/>
+      <x:c r="D373" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" ht="19" customHeight="1">
+      <x:c r="A374" s="230" t="str">
+        <x:v>Lavender Bundle</x:v>
+      </x:c>
+      <x:c r="B374" s="230" t="str">
+        <x:v>/images/pets/Lavender Bundle.png</x:v>
+      </x:c>
+      <x:c r="C374" s="238"/>
+      <x:c r="D374" s="234" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" ht="19" customHeight="1">
+      <x:c r="A375" s="230" t="str">
+        <x:v>Lazy Float</x:v>
+      </x:c>
+      <x:c r="B375" s="230" t="str">
+        <x:v>/images/pets/Lazy Float.png</x:v>
+      </x:c>
+      <x:c r="C375" s="238"/>
+      <x:c r="D375" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" ht="19" customHeight="1">
+      <x:c r="A376" s="230" t="str">
+        <x:v>Lead Zeppelin Balloon</x:v>
+      </x:c>
+      <x:c r="B376" s="230" t="str">
+        <x:v>/images/pets/Lead Zeppelin Balloon.png</x:v>
+      </x:c>
+      <x:c r="C376" s="238"/>
+      <x:c r="D376" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" ht="19" customHeight="1">
+      <x:c r="A377" s="230" t="str">
+        <x:v>Leash</x:v>
+      </x:c>
+      <x:c r="B377" s="230" t="str">
+        <x:v>/images/pets/Leash.png</x:v>
+      </x:c>
+      <x:c r="C377" s="238"/>
+      <x:c r="D377" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" ht="19" customHeight="1">
+      <x:c r="A378" s="230" t="str">
+        <x:v>Leek Chew Toy</x:v>
+      </x:c>
+      <x:c r="B378" s="230" t="str">
+        <x:v>/images/pets/Leek Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C378" s="238"/>
+      <x:c r="D378" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" ht="19" customHeight="1">
+      <x:c r="A379" s="230" t="str">
+        <x:v>Lemonade Chew Toy</x:v>
+      </x:c>
+      <x:c r="B379" s="230" t="str">
+        <x:v>/images/pets/Lemonade Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C379" s="238"/>
+      <x:c r="D379" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" ht="19" customHeight="1">
+      <x:c r="A380" s="230" t="str">
+        <x:v>Lemonade Stand</x:v>
+      </x:c>
+      <x:c r="B380" s="230" t="str">
+        <x:v>/images/pets/Lemonade Stand.png</x:v>
+      </x:c>
+      <x:c r="C380" s="238"/>
+      <x:c r="D380" s="234" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" ht="19" customHeight="1">
+      <x:c r="A381" s="230" t="str">
+        <x:v>Lesbian Flag</x:v>
+      </x:c>
+      <x:c r="B381" s="230" t="str">
+        <x:v>/images/pets/Lesbian Flag.png</x:v>
+      </x:c>
+      <x:c r="C381" s="238"/>
+      <x:c r="D381" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" ht="19" customHeight="1">
+      <x:c r="A382" s="230" t="str">
+        <x:v>Light Blue Pogostick</x:v>
+      </x:c>
+      <x:c r="B382" s="230" t="str">
+        <x:v>/images/pets/Light Blue Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C382" s="238"/>
+      <x:c r="D382" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" ht="19" customHeight="1">
+      <x:c r="A383" s="230" t="str">
+        <x:v>Light Spinner Throw Toy</x:v>
+      </x:c>
+      <x:c r="B383" s="230" t="str">
+        <x:v>/images/pets/Light Spinner Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C383" s="238"/>
+      <x:c r="D383" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" ht="19" customHeight="1">
+      <x:c r="A384" s="230" t="str">
+        <x:v>Lilypad Flying Disc</x:v>
+      </x:c>
+      <x:c r="B384" s="230" t="str">
+        <x:v>/images/pets/Lilypad Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C384" s="238"/>
+      <x:c r="D384" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" ht="19" customHeight="1">
+      <x:c r="A385" s="230" t="str">
+        <x:v>Lime Slice Propeller</x:v>
+      </x:c>
+      <x:c r="B385" s="230" t="str">
+        <x:v>/images/pets/Lime Slice Propeller.png</x:v>
+      </x:c>
+      <x:c r="C385" s="238"/>
+      <x:c r="D385" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" ht="19" customHeight="1">
+      <x:c r="A386" s="230" t="str">
+        <x:v>Llama Plush</x:v>
+      </x:c>
+      <x:c r="B386" s="230" t="str">
+        <x:v>/images/pets/Llama Plush.png</x:v>
+      </x:c>
+      <x:c r="C386" s="238"/>
+      <x:c r="D386" s="234" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" ht="19" customHeight="1">
+      <x:c r="A387" s="230" t="str">
+        <x:v>Llama Rattle</x:v>
+      </x:c>
+      <x:c r="B387" s="230" t="str">
+        <x:v>/images/pets/Llama Rattle.png</x:v>
+      </x:c>
+      <x:c r="C387" s="238"/>
+      <x:c r="D387" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" ht="19" customHeight="1">
+      <x:c r="A388" s="230" t="str">
+        <x:v>Long Neck Chew Toy</x:v>
+      </x:c>
+      <x:c r="B388" s="230" t="str">
+        <x:v>/images/pets/Long Neck Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C388" s="238"/>
+      <x:c r="D388" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" ht="19" customHeight="1">
+      <x:c r="A389" s="230" t="str">
+        <x:v>Long Neck Throw Toy</x:v>
+      </x:c>
+      <x:c r="B389" s="230" t="str">
+        <x:v>/images/pets/Long Neck Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C389" s="238"/>
+      <x:c r="D389" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" ht="19" customHeight="1">
+      <x:c r="A390" s="230" t="str">
+        <x:v>Love Envelope Balloon</x:v>
+      </x:c>
+      <x:c r="B390" s="230" t="str">
+        <x:v>/images/pets/Love Envelope Balloon.png</x:v>
+      </x:c>
+      <x:c r="C390" s="238"/>
+      <x:c r="D390" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" ht="19" customHeight="1">
+      <x:c r="A391" s="230" t="str">
+        <x:v>Love Perfume</x:v>
+      </x:c>
+      <x:c r="B391" s="230" t="str">
+        <x:v>/images/pets/Love Perfume.png</x:v>
+      </x:c>
+      <x:c r="C391" s="238"/>
+      <x:c r="D391" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" ht="19" customHeight="1">
+      <x:c r="A392" s="230" t="str">
+        <x:v>Lucky Coin Flying Disc</x:v>
+      </x:c>
+      <x:c r="B392" s="230" t="str">
+        <x:v>/images/pets/Lucky Coin Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C392" s="238"/>
+      <x:c r="D392" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" ht="19" customHeight="1">
+      <x:c r="A393" s="230" t="str">
+        <x:v>Lunar Lantern</x:v>
+      </x:c>
+      <x:c r="B393" s="230" t="str">
+        <x:v>/images/pets/Lunar Lantern.png</x:v>
+      </x:c>
+      <x:c r="C393" s="238"/>
+      <x:c r="D393" s="234" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" ht="19" customHeight="1">
+      <x:c r="A394" s="230" t="str">
+        <x:v>Lunar Moon Throw Toy</x:v>
+      </x:c>
+      <x:c r="B394" s="230" t="str">
+        <x:v>/images/pets/Lunar Moon Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C394" s="238"/>
+      <x:c r="D394" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" ht="19" customHeight="1">
+      <x:c r="A395" s="230" t="str">
+        <x:v>Lunar New Year Lantern</x:v>
+      </x:c>
+      <x:c r="B395" s="230" t="str">
+        <x:v>/images/pets/Lunar New Year Lantern.png</x:v>
+      </x:c>
+      <x:c r="C395" s="238"/>
+      <x:c r="D395" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" ht="19" customHeight="1">
+      <x:c r="A396" s="230" t="str">
+        <x:v>Lunar New Year Leash</x:v>
+      </x:c>
+      <x:c r="B396" s="230" t="str">
+        <x:v>/images/pets/Lunar New Year Leash.png</x:v>
+      </x:c>
+      <x:c r="C396" s="238"/>
+      <x:c r="D396" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" ht="19" customHeight="1">
+      <x:c r="A397" s="230" t="str">
+        <x:v>Lunar New Year Teapot Leash</x:v>
+      </x:c>
+      <x:c r="B397" s="230" t="str">
+        <x:v>/images/pets/Lunar New Year Teapot Leash.png</x:v>
+      </x:c>
+      <x:c r="C397" s="238"/>
+      <x:c r="D397" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" ht="19" customHeight="1">
+      <x:c r="A398" s="230" t="str">
+        <x:v>Lunar Pogo</x:v>
+      </x:c>
+      <x:c r="B398" s="230" t="str">
+        <x:v>/images/pets/Lunar Pogo.png</x:v>
+      </x:c>
+      <x:c r="C398" s="238"/>
+      <x:c r="D398" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" ht="19" customHeight="1">
+      <x:c r="A399" s="230" t="str">
+        <x:v>Lunar Rattle</x:v>
+      </x:c>
+      <x:c r="B399" s="230" t="str">
+        <x:v>/images/pets/Lunar Rattle.png</x:v>
+      </x:c>
+      <x:c r="C399" s="238"/>
+      <x:c r="D399" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" ht="19" customHeight="1">
+      <x:c r="A400" s="230" t="str">
+        <x:v>Magic Girl Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B400" s="230" t="str">
+        <x:v>/images/pets/Magic Girl Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C400" s="238"/>
+      <x:c r="D400" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" ht="19" customHeight="1">
+      <x:c r="A401" s="230" t="str">
+        <x:v>Magic Girl Tennis Racket</x:v>
+      </x:c>
+      <x:c r="B401" s="230" t="str">
+        <x:v>/images/pets/Magic Girl Tennis Racket.png</x:v>
+      </x:c>
+      <x:c r="C401" s="238"/>
+      <x:c r="D401" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" ht="19" customHeight="1">
+      <x:c r="A402" s="230" t="str">
+        <x:v>Magic House Door</x:v>
+      </x:c>
+      <x:c r="B402" s="230" t="str">
+        <x:v>/images/pets/Magic House Door.png</x:v>
+      </x:c>
+      <x:c r="C402" s="238"/>
+      <x:c r="D402" s="234" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" ht="19" customHeight="1">
+      <x:c r="A403" s="230" t="str">
+        <x:v>Magic Scroll Chew Toy</x:v>
+      </x:c>
+      <x:c r="B403" s="230" t="str">
+        <x:v>/images/pets/Magic Scroll Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C403" s="238"/>
+      <x:c r="D403" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" ht="19" customHeight="1">
+      <x:c r="A404" s="230" t="str">
+        <x:v>Magic Staff Light</x:v>
+      </x:c>
+      <x:c r="B404" s="230" t="str">
+        <x:v>/images/pets/Magic Staff Light.png</x:v>
+      </x:c>
+      <x:c r="C404" s="238"/>
+      <x:c r="D404" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" ht="19" customHeight="1">
+      <x:c r="A405" s="230" t="str">
+        <x:v>Magic Wand Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B405" s="230" t="str">
+        <x:v>/images/pets/Magic Wand Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C405" s="238"/>
+      <x:c r="D405" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" ht="19" customHeight="1">
+      <x:c r="A406" s="230" t="str">
+        <x:v>Magical Princess Chew Toy</x:v>
+      </x:c>
+      <x:c r="B406" s="230" t="str">
+        <x:v>/images/pets/Magical Princess Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C406" s="238"/>
+      <x:c r="D406" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" ht="19" customHeight="1">
+      <x:c r="A407" s="230" t="str">
+        <x:v>Magical Princess Leash</x:v>
+      </x:c>
+      <x:c r="B407" s="230" t="str">
+        <x:v>/images/pets/Magical Princess Leash.png</x:v>
+      </x:c>
+      <x:c r="C407" s="238"/>
+      <x:c r="D407" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" ht="19" customHeight="1">
+      <x:c r="A408" s="230" t="str">
+        <x:v>Magician's Wand Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B408" s="230" t="str">
+        <x:v>/images/pets/Magician's Wand Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C408" s="238"/>
+      <x:c r="D408" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" ht="19" customHeight="1">
+      <x:c r="A409" s="230" t="str">
+        <x:v>Magma Throwing Disc</x:v>
+      </x:c>
+      <x:c r="B409" s="230" t="str">
+        <x:v>/images/pets/Magma Throwing Disc.png</x:v>
+      </x:c>
+      <x:c r="C409" s="238"/>
+      <x:c r="D409" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" ht="19" customHeight="1">
+      <x:c r="A410" s="230" t="str">
+        <x:v>Marsh Balloon</x:v>
+      </x:c>
+      <x:c r="B410" s="230" t="str">
+        <x:v>/images/pets/Marsh Balloon.png</x:v>
+      </x:c>
+      <x:c r="C410" s="238"/>
+      <x:c r="D410" s="234" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" ht="19" customHeight="1">
+      <x:c r="A411" s="230" t="str">
+        <x:v>Marsh Plush</x:v>
+      </x:c>
+      <x:c r="B411" s="230" t="str">
+        <x:v>/images/pets/Marsh Plush.png</x:v>
+      </x:c>
+      <x:c r="C411" s="238"/>
+      <x:c r="D411" s="234" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" ht="19" customHeight="1">
+      <x:c r="A412" s="230" t="str">
+        <x:v>Marshmallow Stand</x:v>
+      </x:c>
+      <x:c r="B412" s="230" t="str">
+        <x:v>/images/pets/Marshmallow Stand.png</x:v>
+      </x:c>
+      <x:c r="C412" s="238"/>
+      <x:c r="D412" s="234" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" ht="19" customHeight="1">
+      <x:c r="A413" s="230" t="str">
+        <x:v>Meaty Chew Toy</x:v>
+      </x:c>
+      <x:c r="B413" s="230" t="str">
+        <x:v>/images/pets/Meaty Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C413" s="238"/>
+      <x:c r="D413" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" ht="19" customHeight="1">
+      <x:c r="A414" s="230" t="str">
+        <x:v>Mech Flying Disc</x:v>
+      </x:c>
+      <x:c r="B414" s="230" t="str">
+        <x:v>/images/pets/Mech Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C414" s="238"/>
+      <x:c r="D414" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" ht="19" customHeight="1">
+      <x:c r="A415" s="230" t="str">
+        <x:v>Medieval Grapple</x:v>
+      </x:c>
+      <x:c r="B415" s="230" t="str">
+        <x:v>/images/pets/Medieval Grapple.png</x:v>
+      </x:c>
+      <x:c r="C415" s="238"/>
+      <x:c r="D415" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" ht="19" customHeight="1">
+      <x:c r="A416" s="230" t="str">
+        <x:v>Mermaid Float</x:v>
+      </x:c>
+      <x:c r="B416" s="230" t="str">
+        <x:v>/images/pets/Mermaid Float.png</x:v>
+      </x:c>
+      <x:c r="C416" s="238"/>
+      <x:c r="D416" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" ht="19" customHeight="1">
+      <x:c r="A417" s="230" t="str">
+        <x:v>Mermaid Propeller</x:v>
+      </x:c>
+      <x:c r="B417" s="230" t="str">
+        <x:v>/images/pets/Mermaid Propeller.png</x:v>
+      </x:c>
+      <x:c r="C417" s="238"/>
+      <x:c r="D417" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" ht="19" customHeight="1">
+      <x:c r="A418" s="230" t="str">
+        <x:v>Mermaid Rattle</x:v>
+      </x:c>
+      <x:c r="B418" s="230" t="str">
+        <x:v>/images/pets/Mermaid Rattle.png</x:v>
+      </x:c>
+      <x:c r="C418" s="238"/>
+      <x:c r="D418" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" ht="19" customHeight="1">
+      <x:c r="A419" s="230" t="str">
+        <x:v>Meteor Plush</x:v>
+      </x:c>
+      <x:c r="B419" s="230" t="str">
+        <x:v>/images/pets/Meteor Plush.png</x:v>
+      </x:c>
+      <x:c r="C419" s="238"/>
+      <x:c r="D419" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" ht="19" customHeight="1">
+      <x:c r="A420" s="230" t="str">
+        <x:v>Midnight Dragon Kite</x:v>
+      </x:c>
+      <x:c r="B420" s="230" t="str">
+        <x:v>/images/pets/Midnight Dragon Kite.png</x:v>
+      </x:c>
+      <x:c r="C420" s="238"/>
+      <x:c r="D420" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" ht="19" customHeight="1">
+      <x:c r="A421" s="230" t="str">
+        <x:v>Minigame Pickaxe</x:v>
+      </x:c>
+      <x:c r="B421" s="230" t="str">
+        <x:v>/images/pets/Minigame Pickaxe.png</x:v>
+      </x:c>
+      <x:c r="C421" s="238"/>
+      <x:c r="D421" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" ht="19" customHeight="1">
+      <x:c r="A422" s="230" t="str">
+        <x:v>Mistletroll Friend Plush</x:v>
+      </x:c>
+      <x:c r="B422" s="230" t="str">
+        <x:v>/images/pets/Mistletroll Friend Plush.png</x:v>
+      </x:c>
+      <x:c r="C422" s="238"/>
+      <x:c r="D422" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" ht="19" customHeight="1">
+      <x:c r="A423" s="230" t="str">
+        <x:v>Money Rattle</x:v>
+      </x:c>
+      <x:c r="B423" s="230" t="str">
+        <x:v>/images/pets/Money Rattle.png</x:v>
+      </x:c>
+      <x:c r="C423" s="238"/>
+      <x:c r="D423" s="234" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" ht="19" customHeight="1">
+      <x:c r="A424" s="230" t="str">
+        <x:v>Monkey Pogo</x:v>
+      </x:c>
+      <x:c r="B424" s="230" t="str">
+        <x:v>/images/pets/Monkey Pogo.png</x:v>
+      </x:c>
+      <x:c r="C424" s="238"/>
+      <x:c r="D424" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" ht="19" customHeight="1">
+      <x:c r="A425" s="230" t="str">
+        <x:v>Monkey Propeller</x:v>
+      </x:c>
+      <x:c r="B425" s="230" t="str">
+        <x:v>/images/pets/Monkey Propeller.png</x:v>
+      </x:c>
+      <x:c r="C425" s="238"/>
+      <x:c r="D425" s="234" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" ht="19" customHeight="1">
+      <x:c r="A426" s="230" t="str">
+        <x:v>Moon Viewing Bench</x:v>
+      </x:c>
+      <x:c r="B426" s="230" t="str">
+        <x:v>/images/pets/Moon Viewing Bench.png</x:v>
+      </x:c>
+      <x:c r="C426" s="238"/>
+      <x:c r="D426" s="234" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" ht="19" customHeight="1">
+      <x:c r="A427" s="230" t="str">
+        <x:v>Mouse Chew Toy</x:v>
+      </x:c>
+      <x:c r="B427" s="230" t="str">
+        <x:v>/images/pets/Mouse Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C427" s="238"/>
+      <x:c r="D427" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" ht="19" customHeight="1">
+      <x:c r="A428" s="230" t="str">
+        <x:v>Mouse Leash</x:v>
+      </x:c>
+      <x:c r="B428" s="230" t="str">
+        <x:v>/images/pets/Mouse Leash.png</x:v>
+      </x:c>
+      <x:c r="C428" s="238"/>
+      <x:c r="D428" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" ht="19" customHeight="1">
+      <x:c r="A429" s="230" t="str">
+        <x:v>Mushroom Flying Disc</x:v>
+      </x:c>
+      <x:c r="B429" s="230" t="str">
+        <x:v>/images/pets/Mushroom Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C429" s="238"/>
+      <x:c r="D429" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" ht="19" customHeight="1">
+      <x:c r="A430" s="230" t="str">
+        <x:v>Mushroom Friend Plushie</x:v>
+      </x:c>
+      <x:c r="B430" s="230" t="str">
+        <x:v>/images/pets/Mushroom Friend Plushie.png</x:v>
+      </x:c>
+      <x:c r="C430" s="238"/>
+      <x:c r="D430" s="234" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" ht="19" customHeight="1">
+      <x:c r="A431" s="230" t="str">
+        <x:v>Mushroom Pogo</x:v>
+      </x:c>
+      <x:c r="B431" s="230" t="str">
+        <x:v>/images/pets/Mushroom Pogo.png</x:v>
+      </x:c>
+      <x:c r="C431" s="238"/>
+      <x:c r="D431" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" ht="19" customHeight="1">
+      <x:c r="A432" s="230" t="str">
+        <x:v>Musical Conch</x:v>
+      </x:c>
+      <x:c r="B432" s="230" t="str">
+        <x:v>/images/pets/Musical Conch.png</x:v>
+      </x:c>
+      <x:c r="C432" s="238"/>
+      <x:c r="D432" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" ht="19" customHeight="1">
+      <x:c r="A433" s="230" t="str">
+        <x:v>Nature's Crossbow</x:v>
+      </x:c>
+      <x:c r="B433" s="230" t="str">
+        <x:v>/images/pets/Nature's Crossbow.png</x:v>
+      </x:c>
+      <x:c r="C433" s="238"/>
+      <x:c r="D433" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" ht="19" customHeight="1">
+      <x:c r="A434" s="230" t="str">
+        <x:v>Netzooka</x:v>
+      </x:c>
+      <x:c r="B434" s="230" t="str">
+        <x:v>/images/pets/Netzooka.png</x:v>
+      </x:c>
+      <x:c r="C434" s="238"/>
+      <x:c r="D434" s="234" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" ht="19" customHeight="1">
+      <x:c r="A435" s="230" t="str">
+        <x:v>Newspaper Chew Toy</x:v>
+      </x:c>
+      <x:c r="B435" s="230" t="str">
+        <x:v>/images/pets/Newspaper Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C435" s="238"/>
+      <x:c r="D435" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" ht="19" customHeight="1">
+      <x:c r="A436" s="230" t="str">
+        <x:v>Noob Balloon</x:v>
+      </x:c>
+      <x:c r="B436" s="230" t="str">
+        <x:v>/images/pets/Noob Balloon.png</x:v>
+      </x:c>
+      <x:c r="C436" s="238"/>
+      <x:c r="D436" s="234" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" ht="19" customHeight="1">
+      <x:c r="A437" s="230" t="str">
+        <x:v>Noob Doll DIY Chew Toy</x:v>
+      </x:c>
+      <x:c r="B437" s="230" t="str">
+        <x:v>/images/pets/Noob Doll DIY Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C437" s="238"/>
+      <x:c r="D437" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" ht="19" customHeight="1">
+      <x:c r="A438" s="230" t="str">
+        <x:v>Noodle Cup Throw Toy</x:v>
+      </x:c>
+      <x:c r="B438" s="230" t="str">
+        <x:v>/images/pets/Noodle Cup Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C438" s="238"/>
+      <x:c r="D438" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" ht="19" customHeight="1">
+      <x:c r="A439" s="230" t="str">
+        <x:v>Octopus Plush</x:v>
+      </x:c>
+      <x:c r="B439" s="230" t="str">
+        <x:v>/images/pets/Octopus Plush.png</x:v>
+      </x:c>
+      <x:c r="C439" s="238"/>
+      <x:c r="D439" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" ht="19" customHeight="1">
+      <x:c r="A440" s="230" t="str">
+        <x:v>Olympian Rattle</x:v>
+      </x:c>
+      <x:c r="B440" s="230" t="str">
+        <x:v>/images/pets/Olympian Rattle.png</x:v>
+      </x:c>
+      <x:c r="C440" s="238"/>
+      <x:c r="D440" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" ht="19" customHeight="1">
+      <x:c r="A441" s="230" t="str">
+        <x:v>Omnisex Flag</x:v>
+      </x:c>
+      <x:c r="B441" s="230" t="str">
+        <x:v>/images/pets/Omnisex Flag.png</x:v>
+      </x:c>
+      <x:c r="C441" s="238"/>
+      <x:c r="D441" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" ht="19" customHeight="1">
+      <x:c r="A442" s="230" t="str">
+        <x:v>Orange Pogostick</x:v>
+      </x:c>
+      <x:c r="B442" s="230" t="str">
+        <x:v>/images/pets/Orange Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C442" s="238"/>
+      <x:c r="D442" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443" ht="19" customHeight="1">
+      <x:c r="A443" s="230" t="str">
+        <x:v>Ornament Balloon</x:v>
+      </x:c>
+      <x:c r="B443" s="230" t="str">
+        <x:v>/images/pets/Ornament Balloon.png</x:v>
+      </x:c>
+      <x:c r="C443" s="238"/>
+      <x:c r="D443" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" ht="19" customHeight="1">
+      <x:c r="A444" s="230" t="str">
+        <x:v>Ornament Throw Toy</x:v>
+      </x:c>
+      <x:c r="B444" s="230" t="str">
+        <x:v>/images/pets/Ornament Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C444" s="238"/>
+      <x:c r="D444" s="234" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445" ht="19" customHeight="1">
+      <x:c r="A445" s="230" t="str">
+        <x:v>Paddle Ball Rattle</x:v>
+      </x:c>
+      <x:c r="B445" s="230" t="str">
+        <x:v>/images/pets/Paddle Ball Rattle.png</x:v>
+      </x:c>
+      <x:c r="C445" s="238"/>
+      <x:c r="D445" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" ht="19" customHeight="1">
+      <x:c r="A446" s="230" t="str">
+        <x:v>Paint Sealer</x:v>
+      </x:c>
+      <x:c r="B446" s="230" t="str">
+        <x:v>/images/pets/Paint Sealer.png</x:v>
+      </x:c>
+      <x:c r="C446" s="238"/>
+      <x:c r="D446" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447" ht="19" customHeight="1">
+      <x:c r="A447" s="230" t="str">
+        <x:v>Paintbrush Leash</x:v>
+      </x:c>
+      <x:c r="B447" s="230" t="str">
+        <x:v>/images/pets/Paintbrush Leash.png</x:v>
+      </x:c>
+      <x:c r="C447" s="238"/>
+      <x:c r="D447" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448" ht="19" customHeight="1">
+      <x:c r="A448" s="230" t="str">
+        <x:v>Pan Flag</x:v>
+      </x:c>
+      <x:c r="B448" s="230" t="str">
+        <x:v>/images/pets/Pan Flag.png</x:v>
+      </x:c>
+      <x:c r="C448" s="238"/>
+      <x:c r="D448" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449" ht="19" customHeight="1">
+      <x:c r="A449" s="230" t="str">
+        <x:v>Pancake Throwing Disc</x:v>
+      </x:c>
+      <x:c r="B449" s="230" t="str">
+        <x:v>/images/pets/Pancake Throwing Disc.png</x:v>
+      </x:c>
+      <x:c r="C449" s="238"/>
+      <x:c r="D449" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450" ht="19" customHeight="1">
+      <x:c r="A450" s="230" t="str">
+        <x:v>Panda Flying Disc</x:v>
+      </x:c>
+      <x:c r="B450" s="230" t="str">
+        <x:v>/images/pets/Panda Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C450" s="238"/>
+      <x:c r="D450" s="234" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451" ht="19" customHeight="1">
+      <x:c r="A451" s="230" t="str">
+        <x:v>Panda Frisbee</x:v>
+      </x:c>
+      <x:c r="B451" s="230" t="str">
+        <x:v>/images/pets/Panda Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C451" s="238"/>
+      <x:c r="D451" s="234" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452" ht="19" customHeight="1">
+      <x:c r="A452" s="230" t="str">
+        <x:v>Panda Pal</x:v>
+      </x:c>
+      <x:c r="B452" s="230" t="str">
+        <x:v>/images/pets/Panda Pal.png</x:v>
+      </x:c>
+      <x:c r="C452" s="238"/>
+      <x:c r="D452" s="234" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453" ht="19" customHeight="1">
+      <x:c r="A453" s="230" t="str">
+        <x:v>Paper Plane Launcher Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B453" s="230" t="str">
+        <x:v>/images/pets/Paper Plane Launcher Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C453" s="238"/>
+      <x:c r="D453" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454" ht="19" customHeight="1">
+      <x:c r="A454" s="230" t="str">
+        <x:v>Paper Plane Throw Toy</x:v>
+      </x:c>
+      <x:c r="B454" s="230" t="str">
+        <x:v>/images/pets/Paper Plane Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C454" s="238"/>
+      <x:c r="D454" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455" ht="19" customHeight="1">
+      <x:c r="A455" s="230" t="str">
+        <x:v>Paper Towel Chew Toy</x:v>
+      </x:c>
+      <x:c r="B455" s="230" t="str">
+        <x:v>/images/pets/Paper Towel Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C455" s="238"/>
+      <x:c r="D455" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456" ht="19" customHeight="1">
+      <x:c r="A456" s="230" t="str">
+        <x:v>Party Innertube</x:v>
+      </x:c>
+      <x:c r="B456" s="230" t="str">
+        <x:v>/images/pets/Party Innertube.png</x:v>
+      </x:c>
+      <x:c r="C456" s="238"/>
+      <x:c r="D456" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457" ht="19" customHeight="1">
+      <x:c r="A457" s="230" t="str">
+        <x:v>Party Mermaid Float</x:v>
+      </x:c>
+      <x:c r="B457" s="230" t="str">
+        <x:v>/images/pets/Party Mermaid Float.png</x:v>
+      </x:c>
+      <x:c r="C457" s="238"/>
+      <x:c r="D457" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458" ht="19" customHeight="1">
+      <x:c r="A458" s="230" t="str">
+        <x:v>Party Pizza Float</x:v>
+      </x:c>
+      <x:c r="B458" s="230" t="str">
+        <x:v>/images/pets/Party Pizza Float.png</x:v>
+      </x:c>
+      <x:c r="C458" s="238"/>
+      <x:c r="D458" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459" ht="19" customHeight="1">
+      <x:c r="A459" s="230" t="str">
+        <x:v>Party Pool Noodle</x:v>
+      </x:c>
+      <x:c r="B459" s="230" t="str">
+        <x:v>/images/pets/Party Pool Noodle.png</x:v>
+      </x:c>
+      <x:c r="C459" s="238"/>
+      <x:c r="D459" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460" ht="19" customHeight="1">
+      <x:c r="A460" s="230" t="str">
+        <x:v>Peanut Balloon</x:v>
+      </x:c>
+      <x:c r="B460" s="230" t="str">
+        <x:v>/images/pets/Peanut Balloon.png</x:v>
+      </x:c>
+      <x:c r="C460" s="238"/>
+      <x:c r="D460" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461" ht="19" customHeight="1">
+      <x:c r="A461" s="230" t="str">
+        <x:v>Peanut Friend Chewtoy</x:v>
+      </x:c>
+      <x:c r="B461" s="230" t="str">
+        <x:v>/images/pets/Peanut Friend Chewtoy.png</x:v>
+      </x:c>
+      <x:c r="C461" s="238"/>
+      <x:c r="D461" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462" ht="19" customHeight="1">
+      <x:c r="A462" s="230" t="str">
+        <x:v>Pegleg Pogostick</x:v>
+      </x:c>
+      <x:c r="B462" s="230" t="str">
+        <x:v>/images/pets/Pegleg Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C462" s="238"/>
+      <x:c r="D462" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463" ht="19" customHeight="1">
+      <x:c r="A463" s="230" t="str">
+        <x:v>Pellet Drum Rattle</x:v>
+      </x:c>
+      <x:c r="B463" s="230" t="str">
+        <x:v>/images/pets/Pellet Drum Rattle.png</x:v>
+      </x:c>
+      <x:c r="C463" s="238"/>
+      <x:c r="D463" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464" ht="19" customHeight="1">
+      <x:c r="A464" s="230" t="str">
+        <x:v>Peppermint Disc</x:v>
+      </x:c>
+      <x:c r="B464" s="230" t="str">
+        <x:v>/images/pets/Peppermint Disc.png</x:v>
+      </x:c>
+      <x:c r="C464" s="238"/>
+      <x:c r="D464" s="234" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465" ht="19" customHeight="1">
+      <x:c r="A465" s="230" t="str">
+        <x:v>Phoenix Plush</x:v>
+      </x:c>
+      <x:c r="B465" s="230" t="str">
+        <x:v>/images/pets/Phoenix Plush.png</x:v>
+      </x:c>
+      <x:c r="C465" s="238"/>
+      <x:c r="D465" s="234" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466" ht="19" customHeight="1">
+      <x:c r="A466" s="230" t="str">
+        <x:v>Pickle Elf Chew Toy</x:v>
+      </x:c>
+      <x:c r="B466" s="230" t="str">
+        <x:v>/images/pets/Pickle Elf Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C466" s="238"/>
+      <x:c r="D466" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467" ht="19" customHeight="1">
+      <x:c r="A467" s="230" t="str">
+        <x:v>Pineapple Plush</x:v>
+      </x:c>
+      <x:c r="B467" s="230" t="str">
+        <x:v>/images/pets/Pineapple Plush.png</x:v>
+      </x:c>
+      <x:c r="C467" s="238"/>
+      <x:c r="D467" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468" ht="19" customHeight="1">
+      <x:c r="A468" s="230" t="str">
+        <x:v>Pink Bowling Ball</x:v>
+      </x:c>
+      <x:c r="B468" s="230" t="str">
+        <x:v>/images/pets/Pink Bowling Ball.png</x:v>
+      </x:c>
+      <x:c r="C468" s="238"/>
+      <x:c r="D468" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469" ht="19" customHeight="1">
+      <x:c r="A469" s="230" t="str">
+        <x:v>Pink Cat Balloon</x:v>
+      </x:c>
+      <x:c r="B469" s="230" t="str">
+        <x:v>/images/pets/Pink Cat Balloon.png</x:v>
+      </x:c>
+      <x:c r="C469" s="238"/>
+      <x:c r="D469" s="234" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470" ht="19" customHeight="1">
+      <x:c r="A470" s="230" t="str">
+        <x:v>Pink Lemonade Chew Toy</x:v>
+      </x:c>
+      <x:c r="B470" s="230" t="str">
+        <x:v>/images/pets/Pink Lemonade Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C470" s="238"/>
+      <x:c r="D470" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471" ht="19" customHeight="1">
+      <x:c r="A471" s="230" t="str">
+        <x:v>Pink Pogostick</x:v>
+      </x:c>
+      <x:c r="B471" s="230" t="str">
+        <x:v>/images/pets/Pink Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C471" s="238"/>
+      <x:c r="D471" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472" ht="19" customHeight="1">
+      <x:c r="A472" s="230" t="str">
+        <x:v>Pinwheel Propeller</x:v>
+      </x:c>
+      <x:c r="B472" s="230" t="str">
+        <x:v>/images/pets/Pinwheel Propeller.png</x:v>
+      </x:c>
+      <x:c r="C472" s="238"/>
+      <x:c r="D472" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473" ht="19" customHeight="1">
+      <x:c r="A473" s="230" t="str">
+        <x:v>Pirate Cutlass</x:v>
+      </x:c>
+      <x:c r="B473" s="230" t="str">
+        <x:v>/images/pets/Pirate Cutlass.png</x:v>
+      </x:c>
+      <x:c r="C473" s="238"/>
+      <x:c r="D473" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474" ht="19" customHeight="1">
+      <x:c r="A474" s="230" t="str">
+        <x:v>Pirate Plushie</x:v>
+      </x:c>
+      <x:c r="B474" s="230" t="str">
+        <x:v>/images/pets/Pirate Plushie.png</x:v>
+      </x:c>
+      <x:c r="C474" s="238"/>
+      <x:c r="D474" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475" ht="19" customHeight="1">
+      <x:c r="A475" s="230" t="str">
+        <x:v>Pizza Float</x:v>
+      </x:c>
+      <x:c r="B475" s="230" t="str">
+        <x:v>/images/pets/Pizza Float.png</x:v>
+      </x:c>
+      <x:c r="C475" s="238"/>
+      <x:c r="D475" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476" ht="19" customHeight="1">
+      <x:c r="A476" s="230" t="str">
+        <x:v>Pizza Throwing Disc</x:v>
+      </x:c>
+      <x:c r="B476" s="230" t="str">
+        <x:v>/images/pets/Pizza Throwing Disc.png</x:v>
+      </x:c>
+      <x:c r="C476" s="238"/>
+      <x:c r="D476" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477" ht="19" customHeight="1">
+      <x:c r="A477" s="230" t="str">
+        <x:v>Placeable Snowperson</x:v>
+      </x:c>
+      <x:c r="B477" s="230" t="str">
+        <x:v>/images/pets/Placeable Snowperson.png</x:v>
+      </x:c>
+      <x:c r="C477" s="238"/>
+      <x:c r="D477" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478" ht="19" customHeight="1">
+      <x:c r="A478" s="230" t="str">
+        <x:v>Plate of Food Disc</x:v>
+      </x:c>
+      <x:c r="B478" s="230" t="str">
+        <x:v>/images/pets/Plate of Food Disc.png</x:v>
+      </x:c>
+      <x:c r="C478" s="238"/>
+      <x:c r="D478" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479" ht="19" customHeight="1">
+      <x:c r="A479" s="230" t="str">
+        <x:v>Pluboneium Chew Toy</x:v>
+      </x:c>
+      <x:c r="B479" s="230" t="str">
+        <x:v>/images/pets/Pluboneium Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C479" s="238"/>
+      <x:c r="D479" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480" ht="19" customHeight="1">
+      <x:c r="A480" s="230" t="str">
+        <x:v>Plunger Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B480" s="230" t="str">
+        <x:v>/images/pets/Plunger Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C480" s="238"/>
+      <x:c r="D480" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481" ht="19" customHeight="1">
+      <x:c r="A481" s="230" t="str">
+        <x:v>Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B481" s="230" t="str">
+        <x:v>/images/pets/Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C481" s="238"/>
+      <x:c r="D481" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482" ht="19" customHeight="1">
+      <x:c r="A482" s="230" t="str">
+        <x:v>Poinsettia Leash</x:v>
+      </x:c>
+      <x:c r="B482" s="230" t="str">
+        <x:v>/images/pets/Poinsettia Leash.png</x:v>
+      </x:c>
+      <x:c r="C482" s="238"/>
+      <x:c r="D482" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483" ht="19" customHeight="1">
+      <x:c r="A483" s="230" t="str">
+        <x:v>Polar Bear Plush</x:v>
+      </x:c>
+      <x:c r="B483" s="230" t="str">
+        <x:v>/images/pets/Polar Bear Plush.png</x:v>
+      </x:c>
+      <x:c r="C483" s="238"/>
+      <x:c r="D483" s="234" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484" ht="19" customHeight="1">
+      <x:c r="A484" s="230" t="str">
+        <x:v>Pool Noodle</x:v>
+      </x:c>
+      <x:c r="B484" s="230" t="str">
+        <x:v>/images/pets/Pool Noodle.png</x:v>
+      </x:c>
+      <x:c r="C484" s="238"/>
+      <x:c r="D484" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485" ht="19" customHeight="1">
+      <x:c r="A485" s="230" t="str">
+        <x:v>Popcorn Plush</x:v>
+      </x:c>
+      <x:c r="B485" s="230" t="str">
+        <x:v>/images/pets/Popcorn Plush.png</x:v>
+      </x:c>
+      <x:c r="C485" s="238"/>
+      <x:c r="D485" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486" ht="19" customHeight="1">
+      <x:c r="A486" s="230" t="str">
+        <x:v>Potato Chew Toy</x:v>
+      </x:c>
+      <x:c r="B486" s="230" t="str">
+        <x:v>/images/pets/Potato Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C486" s="238"/>
+      <x:c r="D486" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487" ht="19" customHeight="1">
+      <x:c r="A487" s="230" t="str">
+        <x:v>Potion Bottle Balloon</x:v>
+      </x:c>
+      <x:c r="B487" s="230" t="str">
+        <x:v>/images/pets/Potion Bottle Balloon.png</x:v>
+      </x:c>
+      <x:c r="C487" s="238"/>
+      <x:c r="D487" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488" ht="19" customHeight="1">
+      <x:c r="A488" s="230" t="str">
+        <x:v>Premium Camping Tent</x:v>
+      </x:c>
+      <x:c r="B488" s="230" t="str">
+        <x:v>/images/pets/Premium Camping Tent.png</x:v>
+      </x:c>
+      <x:c r="C488" s="238"/>
+      <x:c r="D488" s="234" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489" ht="19" customHeight="1">
+      <x:c r="A489" s="230" t="str">
+        <x:v>Premium Fire Pit</x:v>
+      </x:c>
+      <x:c r="B489" s="230" t="str">
+        <x:v>/images/pets/Premium Fire Pit.png</x:v>
+      </x:c>
+      <x:c r="C489" s="238"/>
+      <x:c r="D489" s="234" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490" ht="19" customHeight="1">
+      <x:c r="A490" s="230" t="str">
+        <x:v>Premium Log Bench</x:v>
+      </x:c>
+      <x:c r="B490" s="230" t="str">
+        <x:v>/images/pets/Premium Log Bench.png</x:v>
+      </x:c>
+      <x:c r="C490" s="238"/>
+      <x:c r="D490" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491" ht="19" customHeight="1">
+      <x:c r="A491" s="230" t="str">
+        <x:v>Priceless Jewel</x:v>
+      </x:c>
+      <x:c r="B491" s="230" t="str">
+        <x:v>/images/pets/Priceless Jewel.png</x:v>
+      </x:c>
+      <x:c r="C491" s="238"/>
+      <x:c r="D491" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492" ht="19" customHeight="1">
+      <x:c r="A492" s="230" t="str">
+        <x:v>Pride Balloons</x:v>
+      </x:c>
+      <x:c r="B492" s="230" t="str">
+        <x:v>/images/pets/Pride Balloons.png</x:v>
+      </x:c>
+      <x:c r="C492" s="238"/>
+      <x:c r="D492" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493" ht="19" customHeight="1">
+      <x:c r="A493" s="230" t="str">
+        <x:v>Pride Flag</x:v>
+      </x:c>
+      <x:c r="B493" s="230" t="str">
+        <x:v>/images/pets/Pride Flag.png</x:v>
+      </x:c>
+      <x:c r="C493" s="238"/>
+      <x:c r="D493" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494" ht="19" customHeight="1">
+      <x:c r="A494" s="230" t="str">
+        <x:v>Pride Paw Flying Disc</x:v>
+      </x:c>
+      <x:c r="B494" s="230" t="str">
+        <x:v>/images/pets/Pride Paw Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C494" s="238"/>
+      <x:c r="D494" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495" ht="19" customHeight="1">
+      <x:c r="A495" s="230" t="str">
+        <x:v>Pride Wand Rattle</x:v>
+      </x:c>
+      <x:c r="B495" s="230" t="str">
+        <x:v>/images/pets/Pride Wand Rattle.png</x:v>
+      </x:c>
+      <x:c r="C495" s="238"/>
+      <x:c r="D495" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" ht="19" customHeight="1">
+      <x:c r="A496" s="230" t="str">
+        <x:v>Princess Rattle</x:v>
+      </x:c>
+      <x:c r="B496" s="230" t="str">
+        <x:v>/images/pets/Princess Rattle.png</x:v>
+      </x:c>
+      <x:c r="C496" s="238"/>
+      <x:c r="D496" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497" ht="19" customHeight="1">
+      <x:c r="A497" s="230" t="str">
+        <x:v>Propeller</x:v>
+      </x:c>
+      <x:c r="B497" s="230" t="str">
+        <x:v>/images/pets/Propeller.png</x:v>
+      </x:c>
+      <x:c r="C497" s="238"/>
+      <x:c r="D497" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498" ht="19" customHeight="1">
+      <x:c r="A498" s="230" t="str">
+        <x:v>Protein Bottle Rattle</x:v>
+      </x:c>
+      <x:c r="B498" s="230" t="str">
+        <x:v>/images/pets/Protein Bottle Rattle.png</x:v>
+      </x:c>
+      <x:c r="C498" s="238"/>
+      <x:c r="D498" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499" ht="19" customHeight="1">
+      <x:c r="A499" s="230" t="str">
+        <x:v>Psionic Magic Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B499" s="230" t="str">
+        <x:v>/images/pets/Psionic Magic Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C499" s="238"/>
+      <x:c r="D499" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" ht="19" customHeight="1">
+      <x:c r="A500" s="230" t="str">
+        <x:v>Pumpkin</x:v>
+      </x:c>
+      <x:c r="B500" s="230" t="str">
+        <x:v>/images/pets/Pumpkin.png</x:v>
+      </x:c>
+      <x:c r="C500" s="238"/>
+      <x:c r="D500" s="234" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501" ht="19" customHeight="1">
+      <x:c r="A501" s="230" t="str">
+        <x:v>Pumpkin Basket Plushie</x:v>
+      </x:c>
+      <x:c r="B501" s="230" t="str">
+        <x:v>/images/pets/Pumpkin Basket Plushie.png</x:v>
+      </x:c>
+      <x:c r="C501" s="238"/>
+      <x:c r="D501" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" ht="19" customHeight="1">
+      <x:c r="A502" s="230" t="str">
+        <x:v>Pumpkin Rattle</x:v>
+      </x:c>
+      <x:c r="B502" s="230" t="str">
+        <x:v>/images/pets/Pumpkin Rattle.png</x:v>
+      </x:c>
+      <x:c r="C502" s="238"/>
+      <x:c r="D502" s="234" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503" ht="19" customHeight="1">
+      <x:c r="A503" s="230" t="str">
+        <x:v>Puppy Plush</x:v>
+      </x:c>
+      <x:c r="B503" s="230" t="str">
+        <x:v>/images/pets/Puppy Plush.png</x:v>
+      </x:c>
+      <x:c r="C503" s="238"/>
+      <x:c r="D503" s="234" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504" ht="19" customHeight="1">
+      <x:c r="A504" s="230" t="str">
+        <x:v>Rabbit Rattle</x:v>
+      </x:c>
+      <x:c r="B504" s="230" t="str">
+        <x:v>/images/pets/Rabbit Rattle.png</x:v>
+      </x:c>
+      <x:c r="C504" s="238"/>
+      <x:c r="D504" s="234" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505" ht="19" customHeight="1">
+      <x:c r="A505" s="230" t="str">
+        <x:v>Rain Stick</x:v>
+      </x:c>
+      <x:c r="B505" s="230" t="str">
+        <x:v>/images/pets/Rain Stick.png</x:v>
+      </x:c>
+      <x:c r="C505" s="238"/>
+      <x:c r="D505" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506" ht="19" customHeight="1">
+      <x:c r="A506" s="230" t="str">
+        <x:v>Rainbow Cake Chew Toy</x:v>
+      </x:c>
+      <x:c r="B506" s="230" t="str">
+        <x:v>/images/pets/Rainbow Cake Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C506" s="238"/>
+      <x:c r="D506" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507" ht="19" customHeight="1">
+      <x:c r="A507" s="230" t="str">
+        <x:v>Rainbow Dragon Kite</x:v>
+      </x:c>
+      <x:c r="B507" s="230" t="str">
+        <x:v>/images/pets/Rainbow Dragon Kite.png</x:v>
+      </x:c>
+      <x:c r="C507" s="238"/>
+      <x:c r="D507" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" ht="19" customHeight="1">
+      <x:c r="A508" s="230" t="str">
+        <x:v>Rainbow Leash</x:v>
+      </x:c>
+      <x:c r="B508" s="230" t="str">
+        <x:v>/images/pets/Rainbow Leash.png</x:v>
+      </x:c>
+      <x:c r="C508" s="238"/>
+      <x:c r="D508" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509" ht="19" customHeight="1">
+      <x:c r="A509" s="230" t="str">
+        <x:v>Rainbow Popsicle Friend</x:v>
+      </x:c>
+      <x:c r="B509" s="230" t="str">
+        <x:v>/images/pets/Rainbow Popsicle Friend.png</x:v>
+      </x:c>
+      <x:c r="C509" s="238"/>
+      <x:c r="D509" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510" ht="19" customHeight="1">
+      <x:c r="A510" s="230" t="str">
+        <x:v>Rainbow Rattle</x:v>
+      </x:c>
+      <x:c r="B510" s="230" t="str">
+        <x:v>/images/pets/Rainbow Rattle.png</x:v>
+      </x:c>
+      <x:c r="C510" s="238"/>
+      <x:c r="D510" s="234" t="n">
+        <x:v>1750</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511" ht="19" customHeight="1">
+      <x:c r="A511" s="230" t="str">
+        <x:v>Rainbow Sword</x:v>
+      </x:c>
+      <x:c r="B511" s="230" t="str">
+        <x:v>/images/pets/Rainbow Sword.png</x:v>
+      </x:c>
+      <x:c r="C511" s="238"/>
+      <x:c r="D511" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512" ht="19" customHeight="1">
+      <x:c r="A512" s="230" t="str">
+        <x:v>Rainbow Wand</x:v>
+      </x:c>
+      <x:c r="B512" s="230" t="str">
+        <x:v>/images/pets/Rainbow Wand.png</x:v>
+      </x:c>
+      <x:c r="C512" s="238"/>
+      <x:c r="D512" s="234" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513" ht="19" customHeight="1">
+      <x:c r="A513" s="230" t="str">
+        <x:v>Rattle</x:v>
+      </x:c>
+      <x:c r="B513" s="230" t="str">
+        <x:v>/images/pets/Rattle.png</x:v>
+      </x:c>
+      <x:c r="C513" s="238"/>
+      <x:c r="D513" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514" ht="19" customHeight="1">
+      <x:c r="A514" s="230" t="str">
+        <x:v>Raw Bone</x:v>
+      </x:c>
+      <x:c r="B514" s="230" t="str">
+        <x:v>/images/pets/Raw Bone.png</x:v>
+      </x:c>
+      <x:c r="C514" s="238"/>
+      <x:c r="D514" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515" ht="19" customHeight="1">
+      <x:c r="A515" s="230" t="str">
+        <x:v>Ray Gun Leash</x:v>
+      </x:c>
+      <x:c r="B515" s="230" t="str">
+        <x:v>/images/pets/Ray Gun Leash.png</x:v>
+      </x:c>
+      <x:c r="C515" s="238"/>
+      <x:c r="D515" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516" ht="19" customHeight="1">
+      <x:c r="A516" s="230" t="str">
+        <x:v>RBG Leash</x:v>
+      </x:c>
+      <x:c r="B516" s="230" t="str">
+        <x:v>/images/pets/RBG Leash.png</x:v>
+      </x:c>
+      <x:c r="C516" s="238"/>
+      <x:c r="D516" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517" ht="19" customHeight="1">
+      <x:c r="A517" s="230" t="str">
+        <x:v>Recycled Banjo</x:v>
+      </x:c>
+      <x:c r="B517" s="230" t="str">
+        <x:v>/images/pets/Recycled Banjo.png</x:v>
+      </x:c>
+      <x:c r="C517" s="238"/>
+      <x:c r="D517" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518" ht="19" customHeight="1">
+      <x:c r="A518" s="230" t="str">
+        <x:v>Red Panda Cupcake Chew Toy</x:v>
+      </x:c>
+      <x:c r="B518" s="230" t="str">
+        <x:v>/images/pets/Red Panda Cupcake Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C518" s="238"/>
+      <x:c r="D518" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519" ht="19" customHeight="1">
+      <x:c r="A519" s="230" t="str">
+        <x:v>Red Pogostick</x:v>
+      </x:c>
+      <x:c r="B519" s="230" t="str">
+        <x:v>/images/pets/Red Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C519" s="238"/>
+      <x:c r="D519" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520" ht="19" customHeight="1">
+      <x:c r="A520" s="230" t="str">
+        <x:v>Reindeer Leash</x:v>
+      </x:c>
+      <x:c r="B520" s="230" t="str">
+        <x:v>/images/pets/Reindeer Leash.png</x:v>
+      </x:c>
+      <x:c r="C520" s="238"/>
+      <x:c r="D520" s="234" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521" ht="19" customHeight="1">
+      <x:c r="A521" s="230" t="str">
+        <x:v>Reindeer Plush</x:v>
+      </x:c>
+      <x:c r="B521" s="230" t="str">
+        <x:v>/images/pets/Reindeer Plush.png</x:v>
+      </x:c>
+      <x:c r="C521" s="238"/>
+      <x:c r="D521" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522" ht="19" customHeight="1">
+      <x:c r="A522" s="230" t="str">
+        <x:v>Reindeer Rattle</x:v>
+      </x:c>
+      <x:c r="B522" s="230" t="str">
+        <x:v>/images/pets/Reindeer Rattle.png</x:v>
+      </x:c>
+      <x:c r="C522" s="238"/>
+      <x:c r="D522" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523" ht="19" customHeight="1">
+      <x:c r="A523" s="230" t="str">
+        <x:v>RGB Friend</x:v>
+      </x:c>
+      <x:c r="B523" s="230" t="str">
+        <x:v>/images/pets/RGB Friend.png</x:v>
+      </x:c>
+      <x:c r="C523" s="238"/>
+      <x:c r="D523" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524" ht="19" customHeight="1">
+      <x:c r="A524" s="230" t="str">
+        <x:v>RGB Leash</x:v>
+      </x:c>
+      <x:c r="B524" s="230" t="str">
+        <x:v>/images/pets/RGB Leash.png</x:v>
+      </x:c>
+      <x:c r="C524" s="238"/>
+      <x:c r="D524" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525" ht="19" customHeight="1">
+      <x:c r="A525" s="230" t="str">
+        <x:v>RGB Phone Throw Toy</x:v>
+      </x:c>
+      <x:c r="B525" s="230" t="str">
+        <x:v>/images/pets/RGB Phone Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C525" s="238"/>
+      <x:c r="D525" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526" ht="19" customHeight="1">
+      <x:c r="A526" s="230" t="str">
+        <x:v>RGB Propeller</x:v>
+      </x:c>
+      <x:c r="B526" s="230" t="str">
+        <x:v>/images/pets/RGB Propeller.png</x:v>
+      </x:c>
+      <x:c r="C526" s="238"/>
+      <x:c r="D526" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527" ht="19" customHeight="1">
+      <x:c r="A527" s="230" t="str">
+        <x:v>RGB Sword Rattle</x:v>
+      </x:c>
+      <x:c r="B527" s="230" t="str">
+        <x:v>/images/pets/RGB Sword Rattle.png</x:v>
+      </x:c>
+      <x:c r="C527" s="238"/>
+      <x:c r="D527" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528" ht="19" customHeight="1">
+      <x:c r="A528" s="230" t="str">
+        <x:v>Rib Guitar</x:v>
+      </x:c>
+      <x:c r="B528" s="230" t="str">
+        <x:v>/images/pets/Rib Guitar.png</x:v>
+      </x:c>
+      <x:c r="C528" s="238"/>
+      <x:c r="D528" s="234" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529" ht="19" customHeight="1">
+      <x:c r="A529" s="230" t="str">
+        <x:v>Rice Cake Rabbit Kite</x:v>
+      </x:c>
+      <x:c r="B529" s="230" t="str">
+        <x:v>/images/pets/Rice Cake Rabbit Kite.png</x:v>
+      </x:c>
+      <x:c r="C529" s="238"/>
+      <x:c r="D529" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530" ht="19" customHeight="1">
+      <x:c r="A530" s="230" t="str">
+        <x:v>Ring of Fire Throwing Disc</x:v>
+      </x:c>
+      <x:c r="B530" s="230" t="str">
+        <x:v>/images/pets/Ring of Fire Throwing Disc.png</x:v>
+      </x:c>
+      <x:c r="C530" s="238"/>
+      <x:c r="D530" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531" ht="19" customHeight="1">
+      <x:c r="A531" s="230" t="str">
+        <x:v>Robo Balloon</x:v>
+      </x:c>
+      <x:c r="B531" s="230" t="str">
+        <x:v>/images/pets/Robo Balloon.png</x:v>
+      </x:c>
+      <x:c r="C531" s="238"/>
+      <x:c r="D531" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532" ht="19" customHeight="1">
+      <x:c r="A532" s="230" t="str">
+        <x:v>Robo Plush</x:v>
+      </x:c>
+      <x:c r="B532" s="230" t="str">
+        <x:v>/images/pets/Robo Plush.png</x:v>
+      </x:c>
+      <x:c r="C532" s="238"/>
+      <x:c r="D532" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533" ht="19" customHeight="1">
+      <x:c r="A533" s="230" t="str">
+        <x:v>Robo Plush 3000</x:v>
+      </x:c>
+      <x:c r="B533" s="230" t="str">
+        <x:v>/images/pets/Robo Plush 3000.png</x:v>
+      </x:c>
+      <x:c r="C533" s="238"/>
+      <x:c r="D533" s="234" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534" ht="19" customHeight="1">
+      <x:c r="A534" s="230" t="str">
+        <x:v>Rocket Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B534" s="230" t="str">
+        <x:v>/images/pets/Rocket Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C534" s="238"/>
+      <x:c r="D534" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535" ht="19" customHeight="1">
+      <x:c r="A535" s="230" t="str">
+        <x:v>Rocket Pogo</x:v>
+      </x:c>
+      <x:c r="B535" s="230" t="str">
+        <x:v>/images/pets/Rocket Pogo.png</x:v>
+      </x:c>
+      <x:c r="C535" s="238"/>
+      <x:c r="D535" s="234" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536" ht="19" customHeight="1">
+      <x:c r="A536" s="230" t="str">
+        <x:v>Rolling Pin</x:v>
+      </x:c>
+      <x:c r="B536" s="230" t="str">
+        <x:v>/images/pets/Rolling Pin.png</x:v>
+      </x:c>
+      <x:c r="C536" s="238"/>
+      <x:c r="D536" s="234" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537" ht="19" customHeight="1">
+      <x:c r="A537" s="230" t="str">
+        <x:v>Rope Chew Toy</x:v>
+      </x:c>
+      <x:c r="B537" s="230" t="str">
+        <x:v>/images/pets/Rope Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C537" s="238"/>
+      <x:c r="D537" s="234" t="n">
+        <x:v>0.015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538" ht="19" customHeight="1">
+      <x:c r="A538" s="230" t="str">
+        <x:v>Rose Pogo</x:v>
+      </x:c>
+      <x:c r="B538" s="230" t="str">
+        <x:v>/images/pets/Rose Pogo.png</x:v>
+      </x:c>
+      <x:c r="C538" s="238"/>
+      <x:c r="D538" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539" ht="19" customHeight="1">
+      <x:c r="A539" s="230" t="str">
+        <x:v>Rose Quartz Glow Mega Neon Paint</x:v>
+      </x:c>
+      <x:c r="B539" s="230" t="str">
+        <x:v>/images/pets/Rose Quartz Glow Mega Neon Paint.png</x:v>
+      </x:c>
+      <x:c r="C539" s="238"/>
+      <x:c r="D539" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540" ht="19" customHeight="1">
+      <x:c r="A540" s="230" t="str">
+        <x:v>Rose Quartz Glow Mega Neon Pet Paint</x:v>
+      </x:c>
+      <x:c r="B540" s="230" t="str">
+        <x:v>/images/pets/Rose Quartz Glow Mega Neon Pet Paint.png</x:v>
+      </x:c>
+      <x:c r="C540" s="238"/>
+      <x:c r="D540" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541" ht="19" customHeight="1">
+      <x:c r="A541" s="230" t="str">
+        <x:v>Rose Rattle</x:v>
+      </x:c>
+      <x:c r="B541" s="230" t="str">
+        <x:v>/images/pets/Rose Rattle.png</x:v>
+      </x:c>
+      <x:c r="C541" s="238"/>
+      <x:c r="D541" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542" ht="19" customHeight="1">
+      <x:c r="A542" s="230" t="str">
+        <x:v>Rose Throw Toy</x:v>
+      </x:c>
+      <x:c r="B542" s="230" t="str">
+        <x:v>/images/pets/Rose Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C542" s="238"/>
+      <x:c r="D542" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543" ht="19" customHeight="1">
+      <x:c r="A543" s="230" t="str">
+        <x:v>Rubber Bone Throw Toy</x:v>
+      </x:c>
+      <x:c r="B543" s="230" t="str">
+        <x:v>/images/pets/Rubber Bone Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C543" s="238"/>
+      <x:c r="D543" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544" ht="19" customHeight="1">
+      <x:c r="A544" s="230" t="str">
+        <x:v>Rubber Chicken Rattle</x:v>
+      </x:c>
+      <x:c r="B544" s="230" t="str">
+        <x:v>/images/pets/Rubber Chicken Rattle.png</x:v>
+      </x:c>
+      <x:c r="C544" s="238"/>
+      <x:c r="D544" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545" ht="19" customHeight="1">
+      <x:c r="A545" s="230" t="str">
+        <x:v>Rubber Dog Balloon</x:v>
+      </x:c>
+      <x:c r="B545" s="230" t="str">
+        <x:v>/images/pets/Rubber Dog Balloon.png</x:v>
+      </x:c>
+      <x:c r="C545" s="238"/>
+      <x:c r="D545" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546" ht="19" customHeight="1">
+      <x:c r="A546" s="230" t="str">
+        <x:v>Sai</x:v>
+      </x:c>
+      <x:c r="B546" s="230" t="str">
+        <x:v>/images/pets/Sai.png</x:v>
+      </x:c>
+      <x:c r="C546" s="238"/>
+      <x:c r="D546" s="234" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547" ht="19" customHeight="1">
+      <x:c r="A547" s="230" t="str">
+        <x:v>Sandcastle Rattle</x:v>
+      </x:c>
+      <x:c r="B547" s="230" t="str">
+        <x:v>/images/pets/Sandcastle Rattle.png</x:v>
+      </x:c>
+      <x:c r="C547" s="238"/>
+      <x:c r="D547" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548" ht="19" customHeight="1">
+      <x:c r="A548" s="230" t="str">
+        <x:v>Santa Leash</x:v>
+      </x:c>
+      <x:c r="B548" s="230" t="str">
+        <x:v>/images/pets/Santa Leash.png</x:v>
+      </x:c>
+      <x:c r="C548" s="238"/>
+      <x:c r="D548" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549" ht="19" customHeight="1">
+      <x:c r="A549" s="230" t="str">
+        <x:v>Santa Rattle</x:v>
+      </x:c>
+      <x:c r="B549" s="230" t="str">
+        <x:v>/images/pets/Santa Rattle.png</x:v>
+      </x:c>
+      <x:c r="C549" s="238"/>
+      <x:c r="D549" s="234" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550" ht="19" customHeight="1">
+      <x:c r="A550" s="230" t="str">
+        <x:v>Santa Throne</x:v>
+      </x:c>
+      <x:c r="B550" s="230" t="str">
+        <x:v>/images/pets/Santa Throne.png</x:v>
+      </x:c>
+      <x:c r="C550" s="238"/>
+      <x:c r="D550" s="234" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551" ht="19" customHeight="1">
+      <x:c r="A551" s="230" t="str">
+        <x:v>Satellite Balloon</x:v>
+      </x:c>
+      <x:c r="B551" s="230" t="str">
+        <x:v>/images/pets/Satellite Balloon.png</x:v>
+      </x:c>
+      <x:c r="C551" s="238"/>
+      <x:c r="D551" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552" ht="19" customHeight="1">
+      <x:c r="A552" s="230" t="str">
+        <x:v>Saturn Balloon</x:v>
+      </x:c>
+      <x:c r="B552" s="230" t="str">
+        <x:v>/images/pets/Saturn Balloon.png</x:v>
+      </x:c>
+      <x:c r="C552" s="238"/>
+      <x:c r="D552" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553" ht="19" customHeight="1">
+      <x:c r="A553" s="230" t="str">
+        <x:v>Scarab Crossbow Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B553" s="230" t="str">
+        <x:v>/images/pets/Scarab Crossbow Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C553" s="238"/>
+      <x:c r="D553" s="234" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554" ht="19" customHeight="1">
+      <x:c r="A554" s="230" t="str">
+        <x:v>Scroll Ingredient</x:v>
+      </x:c>
+      <x:c r="B554" s="230" t="str">
+        <x:v>/images/pets/Scroll Ingredient.png</x:v>
+      </x:c>
+      <x:c r="C554" s="238"/>
+      <x:c r="D554" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555" ht="19" customHeight="1">
+      <x:c r="A555" s="230" t="str">
+        <x:v>Seal Pogo</x:v>
+      </x:c>
+      <x:c r="B555" s="230" t="str">
+        <x:v>/images/pets/Seal Pogo.png</x:v>
+      </x:c>
+      <x:c r="C555" s="238"/>
+      <x:c r="D555" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556" ht="19" customHeight="1">
+      <x:c r="A556" s="230" t="str">
+        <x:v>Selfie Stick</x:v>
+      </x:c>
+      <x:c r="B556" s="230" t="str">
+        <x:v>/images/pets/Selfie Stick.png</x:v>
+      </x:c>
+      <x:c r="C556" s="238"/>
+      <x:c r="D556" s="234" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557" ht="19" customHeight="1">
+      <x:c r="A557" s="230" t="str">
+        <x:v>Shadow Dragon Sabre</x:v>
+      </x:c>
+      <x:c r="B557" s="230" t="str">
+        <x:v>/images/pets/Shadow Dragon Sabre.png</x:v>
+      </x:c>
+      <x:c r="C557" s="238"/>
+      <x:c r="D557" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558" ht="19" customHeight="1">
+      <x:c r="A558" s="230" t="str">
+        <x:v>Ship Wheel Flying Disc</x:v>
+      </x:c>
+      <x:c r="B558" s="230" t="str">
+        <x:v>/images/pets/Ship Wheel Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C558" s="238"/>
+      <x:c r="D558" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559" ht="19" customHeight="1">
+      <x:c r="A559" s="230" t="str">
+        <x:v>Ship's Mast Pogo</x:v>
+      </x:c>
+      <x:c r="B559" s="230" t="str">
+        <x:v>/images/pets/Ship's Mast Pogo.png</x:v>
+      </x:c>
+      <x:c r="C559" s="238"/>
+      <x:c r="D559" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560" ht="19" customHeight="1">
+      <x:c r="A560" s="230" t="str">
+        <x:v>Shoe Chew Toy</x:v>
+      </x:c>
+      <x:c r="B560" s="230" t="str">
+        <x:v>/images/pets/Shoe Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C560" s="238"/>
+      <x:c r="D560" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561" ht="19" customHeight="1">
+      <x:c r="A561" s="230" t="str">
+        <x:v>Shooting Star Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B561" s="230" t="str">
+        <x:v>/images/pets/Shooting Star Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C561" s="238"/>
+      <x:c r="D561" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562" ht="19" customHeight="1">
+      <x:c r="A562" s="230" t="str">
+        <x:v>Shuttle Pogo</x:v>
+      </x:c>
+      <x:c r="B562" s="230" t="str">
+        <x:v>/images/pets/Shuttle Pogo.png</x:v>
+      </x:c>
+      <x:c r="C562" s="238"/>
+      <x:c r="D562" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563" ht="19" customHeight="1">
+      <x:c r="A563" s="230" t="str">
+        <x:v>Skeleton Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B563" s="230" t="str">
+        <x:v>/images/pets/Skeleton Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C563" s="238"/>
+      <x:c r="D563" s="234" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564" ht="19" customHeight="1">
+      <x:c r="A564" s="230" t="str">
+        <x:v>Skeleton Wing Glider</x:v>
+      </x:c>
+      <x:c r="B564" s="230" t="str">
+        <x:v>/images/pets/Skeleton Wing Glider.png</x:v>
+      </x:c>
+      <x:c r="C564" s="238"/>
+      <x:c r="D564" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565" ht="19" customHeight="1">
+      <x:c r="A565" s="230" t="str">
+        <x:v>Skeleton Winged Glider</x:v>
+      </x:c>
+      <x:c r="B565" s="230" t="str">
+        <x:v>/images/pets/Skeleton Winged Glider.png</x:v>
+      </x:c>
+      <x:c r="C565" s="238"/>
+      <x:c r="D565" s="234" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566" ht="19" customHeight="1">
+      <x:c r="A566" s="230" t="str">
+        <x:v>Ski Pole Pogo</x:v>
+      </x:c>
+      <x:c r="B566" s="230" t="str">
+        <x:v>/images/pets/Ski Pole Pogo.png</x:v>
+      </x:c>
+      <x:c r="C566" s="238"/>
+      <x:c r="D566" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567" ht="19" customHeight="1">
+      <x:c r="A567" s="230" t="str">
+        <x:v>Skull Drum</x:v>
+      </x:c>
+      <x:c r="B567" s="230" t="str">
+        <x:v>/images/pets/Skull Drum.png</x:v>
+      </x:c>
+      <x:c r="C567" s="238"/>
+      <x:c r="D567" s="234" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568" ht="19" customHeight="1">
+      <x:c r="A568" s="230" t="str">
+        <x:v>Skull Propeller</x:v>
+      </x:c>
+      <x:c r="B568" s="230" t="str">
+        <x:v>/images/pets/Skull Propeller.png</x:v>
+      </x:c>
+      <x:c r="C568" s="238"/>
+      <x:c r="D568" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569" ht="19" customHeight="1">
+      <x:c r="A569" s="230" t="str">
+        <x:v>Sleeping Bag</x:v>
+      </x:c>
+      <x:c r="B569" s="230" t="str">
+        <x:v>/images/pets/Sleeping Bag.png</x:v>
+      </x:c>
+      <x:c r="C569" s="238"/>
+      <x:c r="D569" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570" ht="19" customHeight="1">
+      <x:c r="A570" s="230" t="str">
+        <x:v>Sleigh Bell Throw Toy</x:v>
+      </x:c>
+      <x:c r="B570" s="230" t="str">
+        <x:v>/images/pets/Sleigh Bell Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C570" s="238"/>
+      <x:c r="D570" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571" ht="19" customHeight="1">
+      <x:c r="A571" s="230" t="str">
+        <x:v>Sleigh Bells Rattle</x:v>
+      </x:c>
+      <x:c r="B571" s="230" t="str">
+        <x:v>/images/pets/Sleigh Bells Rattle.png</x:v>
+      </x:c>
+      <x:c r="C571" s="238"/>
+      <x:c r="D571" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572" ht="19" customHeight="1">
+      <x:c r="A572" s="230" t="str">
+        <x:v>Slimingo Feather Teleporter</x:v>
+      </x:c>
+      <x:c r="B572" s="230" t="str">
+        <x:v>/images/pets/Slimingo Feather Teleporter.png</x:v>
+      </x:c>
+      <x:c r="C572" s="238"/>
+      <x:c r="D572" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573" ht="19" customHeight="1">
+      <x:c r="A573" s="230" t="str">
+        <x:v>Small Mushroom</x:v>
+      </x:c>
+      <x:c r="B573" s="230" t="str">
+        <x:v>/images/pets/Small Mushroom.png</x:v>
+      </x:c>
+      <x:c r="C573" s="238"/>
+      <x:c r="D573" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="574" ht="19" customHeight="1">
+      <x:c r="A574" s="230" t="str">
+        <x:v>Snow Balloon</x:v>
+      </x:c>
+      <x:c r="B574" s="230" t="str">
+        <x:v>/images/pets/Snow Balloon.png</x:v>
+      </x:c>
+      <x:c r="C574" s="238"/>
+      <x:c r="D574" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575" ht="19" customHeight="1">
+      <x:c r="A575" s="230" t="str">
+        <x:v>Snow Cone Stand</x:v>
+      </x:c>
+      <x:c r="B575" s="230" t="str">
+        <x:v>/images/pets/Snow Cone Stand.png</x:v>
+      </x:c>
+      <x:c r="C575" s="238"/>
+      <x:c r="D575" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="576" ht="19" customHeight="1">
+      <x:c r="A576" s="230" t="str">
+        <x:v>Snowball Launcher</x:v>
+      </x:c>
+      <x:c r="B576" s="230" t="str">
+        <x:v>/images/pets/Snowball Launcher.png</x:v>
+      </x:c>
+      <x:c r="C576" s="238"/>
+      <x:c r="D576" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="577" ht="19" customHeight="1">
+      <x:c r="A577" s="230" t="str">
+        <x:v>Snowflake Flying Disc</x:v>
+      </x:c>
+      <x:c r="B577" s="230" t="str">
+        <x:v>/images/pets/Snowflake Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C577" s="238"/>
+      <x:c r="D577" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="578" ht="19" customHeight="1">
+      <x:c r="A578" s="230" t="str">
+        <x:v>Snowflake Frisbee</x:v>
+      </x:c>
+      <x:c r="B578" s="230" t="str">
+        <x:v>/images/pets/Snowflake Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C578" s="238"/>
+      <x:c r="D578" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579" ht="19" customHeight="1">
+      <x:c r="A579" s="230" t="str">
+        <x:v>Snowflake Plush</x:v>
+      </x:c>
+      <x:c r="B579" s="230" t="str">
+        <x:v>/images/pets/Snowflake Plush.png</x:v>
+      </x:c>
+      <x:c r="C579" s="238"/>
+      <x:c r="D579" s="234" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="580" ht="19" customHeight="1">
+      <x:c r="A580" s="230" t="str">
+        <x:v>Snowflake Propeller</x:v>
+      </x:c>
+      <x:c r="B580" s="230" t="str">
+        <x:v>/images/pets/Snowflake Propeller.png</x:v>
+      </x:c>
+      <x:c r="C580" s="238"/>
+      <x:c r="D580" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581" ht="19" customHeight="1">
+      <x:c r="A581" s="230" t="str">
+        <x:v>Snowflake Throwing Disc</x:v>
+      </x:c>
+      <x:c r="B581" s="230" t="str">
+        <x:v>/images/pets/Snowflake Throwing Disc.png</x:v>
+      </x:c>
+      <x:c r="C581" s="238"/>
+      <x:c r="D581" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582" ht="19" customHeight="1">
+      <x:c r="A582" s="230" t="str">
+        <x:v>Snowman Plush</x:v>
+      </x:c>
+      <x:c r="B582" s="230" t="str">
+        <x:v>/images/pets/Snowman Plush.png</x:v>
+      </x:c>
+      <x:c r="C582" s="238"/>
+      <x:c r="D582" s="234" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="583" ht="19" customHeight="1">
+      <x:c r="A583" s="230" t="str">
+        <x:v>Snowman Plushie Friend</x:v>
+      </x:c>
+      <x:c r="B583" s="230" t="str">
+        <x:v>/images/pets/Snowman Plushie Friend.png</x:v>
+      </x:c>
+      <x:c r="C583" s="238"/>
+      <x:c r="D583" s="234" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584" ht="19" customHeight="1">
+      <x:c r="A584" s="230" t="str">
+        <x:v>Snowman Rattle</x:v>
+      </x:c>
+      <x:c r="B584" s="230" t="str">
+        <x:v>/images/pets/Snowman Rattle.png</x:v>
+      </x:c>
+      <x:c r="C584" s="238"/>
+      <x:c r="D584" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="585" ht="19" customHeight="1">
+      <x:c r="A585" s="230" t="str">
+        <x:v>Soccer Ball Throw Toy</x:v>
+      </x:c>
+      <x:c r="B585" s="230" t="str">
+        <x:v>/images/pets/Soccer Ball Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C585" s="238"/>
+      <x:c r="D585" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586" ht="19" customHeight="1">
+      <x:c r="A586" s="230" t="str">
+        <x:v>Sock Chew Toy</x:v>
+      </x:c>
+      <x:c r="B586" s="230" t="str">
+        <x:v>/images/pets/Sock Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C586" s="238"/>
+      <x:c r="D586" s="234" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587" ht="19" customHeight="1">
+      <x:c r="A587" s="230" t="str">
+        <x:v>Soda Chew Toy</x:v>
+      </x:c>
+      <x:c r="B587" s="230" t="str">
+        <x:v>/images/pets/Soda Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C587" s="238"/>
+      <x:c r="D587" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="588" ht="19" customHeight="1">
+      <x:c r="A588" s="230" t="str">
+        <x:v>Sour Glider</x:v>
+      </x:c>
+      <x:c r="B588" s="230" t="str">
+        <x:v>/images/pets/Sour Glider.png</x:v>
+      </x:c>
+      <x:c r="C588" s="238"/>
+      <x:c r="D588" s="234" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589" ht="19" customHeight="1">
+      <x:c r="A589" s="230" t="str">
+        <x:v>Space Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B589" s="230" t="str">
+        <x:v>/images/pets/Space Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C589" s="238"/>
+      <x:c r="D589" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="590" ht="19" customHeight="1">
+      <x:c r="A590" s="230" t="str">
+        <x:v>Sparkler</x:v>
+      </x:c>
+      <x:c r="B590" s="230" t="str">
+        <x:v>/images/pets/Sparkler.png</x:v>
+      </x:c>
+      <x:c r="C590" s="238"/>
+      <x:c r="D590" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591" ht="19" customHeight="1">
+      <x:c r="A591" s="230" t="str">
+        <x:v>Spellbook Throw Toy</x:v>
+      </x:c>
+      <x:c r="B591" s="230" t="str">
+        <x:v>/images/pets/Spellbook Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C591" s="238"/>
+      <x:c r="D591" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="592" ht="19" customHeight="1">
+      <x:c r="A592" s="230" t="str">
+        <x:v>Spider Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B592" s="230" t="str">
+        <x:v>/images/pets/Spider Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C592" s="238"/>
+      <x:c r="D592" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593" ht="19" customHeight="1">
+      <x:c r="A593" s="230" t="str">
+        <x:v>Spider Web Flying Disc</x:v>
+      </x:c>
+      <x:c r="B593" s="230" t="str">
+        <x:v>/images/pets/Spider Web Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C593" s="238"/>
+      <x:c r="D593" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594" ht="19" customHeight="1">
+      <x:c r="A594" s="230" t="str">
+        <x:v>Spinning Propeller</x:v>
+      </x:c>
+      <x:c r="B594" s="230" t="str">
+        <x:v>/images/pets/Spinning Propeller.png</x:v>
+      </x:c>
+      <x:c r="C594" s="238"/>
+      <x:c r="D594" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="595" ht="19" customHeight="1">
+      <x:c r="A595" s="230" t="str">
+        <x:v>Spinning Top Flying Disc</x:v>
+      </x:c>
+      <x:c r="B595" s="230" t="str">
+        <x:v>/images/pets/Spinning Top Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C595" s="238"/>
+      <x:c r="D595" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596" ht="19" customHeight="1">
+      <x:c r="A596" s="230" t="str">
+        <x:v>Spirit Chew Toy</x:v>
+      </x:c>
+      <x:c r="B596" s="230" t="str">
+        <x:v>/images/pets/Spirit Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C596" s="238"/>
+      <x:c r="D596" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="597" ht="19" customHeight="1">
+      <x:c r="A597" s="230" t="str">
+        <x:v>Spring Bunny Leash</x:v>
+      </x:c>
+      <x:c r="B597" s="230" t="str">
+        <x:v>/images/pets/Spring Bunny Leash.png</x:v>
+      </x:c>
+      <x:c r="C597" s="238"/>
+      <x:c r="D597" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598" ht="19" customHeight="1">
+      <x:c r="A598" s="230" t="str">
+        <x:v>Sprinkler Propeller</x:v>
+      </x:c>
+      <x:c r="B598" s="230" t="str">
+        <x:v>/images/pets/Sprinkler Propeller.png</x:v>
+      </x:c>
+      <x:c r="C598" s="238"/>
+      <x:c r="D598" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="599" ht="19" customHeight="1">
+      <x:c r="A599" s="230" t="str">
+        <x:v>Sprout Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B599" s="230" t="str">
+        <x:v>/images/pets/Sprout Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C599" s="238"/>
+      <x:c r="D599" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600" ht="19" customHeight="1">
+      <x:c r="A600" s="230" t="str">
+        <x:v>Squeaky Bone</x:v>
+      </x:c>
+      <x:c r="B600" s="230" t="str">
+        <x:v>/images/pets/Squeaky Bone.png</x:v>
+      </x:c>
+      <x:c r="C600" s="238"/>
+      <x:c r="D600" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601" ht="19" customHeight="1">
+      <x:c r="A601" s="230" t="str">
+        <x:v>Squeaky Spikey</x:v>
+      </x:c>
+      <x:c r="B601" s="230" t="str">
+        <x:v>/images/pets/Squeaky Spikey.png</x:v>
+      </x:c>
+      <x:c r="C601" s="238"/>
+      <x:c r="D601" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="602" ht="19" customHeight="1">
+      <x:c r="A602" s="230" t="str">
+        <x:v>Squid Plush</x:v>
+      </x:c>
+      <x:c r="B602" s="230" t="str">
+        <x:v>/images/pets/Squid Plush.png</x:v>
+      </x:c>
+      <x:c r="C602" s="238"/>
+      <x:c r="D602" s="234" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603" ht="19" customHeight="1">
+      <x:c r="A603" s="230" t="str">
+        <x:v>Squid Rattle</x:v>
+      </x:c>
+      <x:c r="B603" s="230" t="str">
+        <x:v>/images/pets/Squid Rattle.png</x:v>
+      </x:c>
+      <x:c r="C603" s="238"/>
+      <x:c r="D603" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604" ht="19" customHeight="1">
+      <x:c r="A604" s="230" t="str">
+        <x:v>Squirty Flower</x:v>
+      </x:c>
+      <x:c r="B604" s="230" t="str">
+        <x:v>/images/pets/Squirty Flower.png</x:v>
+      </x:c>
+      <x:c r="C604" s="238"/>
+      <x:c r="D604" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605" ht="19" customHeight="1">
+      <x:c r="A605" s="230" t="str">
+        <x:v>Stable Token</x:v>
+      </x:c>
+      <x:c r="B605" s="230" t="str">
+        <x:v>/images/pets/Stable Token.png</x:v>
+      </x:c>
+      <x:c r="C605" s="238"/>
+      <x:c r="D605" s="234" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606" ht="19" customHeight="1">
+      <x:c r="A606" s="230" t="str">
+        <x:v>Staff Ingredient</x:v>
+      </x:c>
+      <x:c r="B606" s="230" t="str">
+        <x:v>/images/pets/Staff Ingredient.png</x:v>
+      </x:c>
+      <x:c r="C606" s="238"/>
+      <x:c r="D606" s="234" t="n">
+        <x:v>2.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607" ht="19" customHeight="1">
+      <x:c r="A607" s="230" t="str">
+        <x:v>Standard Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B607" s="230" t="str">
+        <x:v>/images/pets/Standard Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C607" s="238"/>
+      <x:c r="D607" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608" ht="19" customHeight="1">
+      <x:c r="A608" s="230" t="str">
+        <x:v>Standard Pogo</x:v>
+      </x:c>
+      <x:c r="B608" s="230" t="str">
+        <x:v>/images/pets/Standard Pogo.png</x:v>
+      </x:c>
+      <x:c r="C608" s="238"/>
+      <x:c r="D608" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609" ht="19" customHeight="1">
+      <x:c r="A609" s="230" t="str">
+        <x:v>Star &amp; Moon Propeller</x:v>
+      </x:c>
+      <x:c r="B609" s="230" t="str">
+        <x:v>/images/pets/Star &amp; Moon Propeller.png</x:v>
+      </x:c>
+      <x:c r="C609" s="238"/>
+      <x:c r="D609" s="234" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610" ht="19" customHeight="1">
+      <x:c r="A610" s="230" t="str">
+        <x:v>Star Ball</x:v>
+      </x:c>
+      <x:c r="B610" s="230" t="str">
+        <x:v>/images/pets/Star Ball.png</x:v>
+      </x:c>
+      <x:c r="C610" s="238"/>
+      <x:c r="D610" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611" ht="19" customHeight="1">
+      <x:c r="A611" s="230" t="str">
+        <x:v>Star Balloon</x:v>
+      </x:c>
+      <x:c r="B611" s="230" t="str">
+        <x:v>/images/pets/Star Balloon.png</x:v>
+      </x:c>
+      <x:c r="C611" s="238"/>
+      <x:c r="D611" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612" ht="19" customHeight="1">
+      <x:c r="A612" s="230" t="str">
+        <x:v>Star Throwing Disc</x:v>
+      </x:c>
+      <x:c r="B612" s="230" t="str">
+        <x:v>/images/pets/Star Throwing Disc.png</x:v>
+      </x:c>
+      <x:c r="C612" s="238"/>
+      <x:c r="D612" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613" ht="19" customHeight="1">
+      <x:c r="A613" s="230" t="str">
+        <x:v>Star Topper Plush</x:v>
+      </x:c>
+      <x:c r="B613" s="230" t="str">
+        <x:v>/images/pets/Star Topper Plush.png</x:v>
+      </x:c>
+      <x:c r="C613" s="238"/>
+      <x:c r="D613" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614" ht="19" customHeight="1">
+      <x:c r="A614" s="230" t="str">
+        <x:v>Starpower Wand</x:v>
+      </x:c>
+      <x:c r="B614" s="230" t="str">
+        <x:v>/images/pets/Starpower Wand.png</x:v>
+      </x:c>
+      <x:c r="C614" s="238"/>
+      <x:c r="D614" s="234" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615" ht="19" customHeight="1">
+      <x:c r="A615" s="230" t="str">
+        <x:v>Steel Drum</x:v>
+      </x:c>
+      <x:c r="B615" s="230" t="str">
+        <x:v>/images/pets/Steel Drum.png</x:v>
+      </x:c>
+      <x:c r="C615" s="238"/>
+      <x:c r="D615" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616" ht="19" customHeight="1">
+      <x:c r="A616" s="230" t="str">
+        <x:v>Stegosaurus Chew Toy</x:v>
+      </x:c>
+      <x:c r="B616" s="230" t="str">
+        <x:v>/images/pets/Stegosaurus Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C616" s="238"/>
+      <x:c r="D616" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617" ht="19" customHeight="1">
+      <x:c r="A617" s="230" t="str">
+        <x:v>Stegosaurus Throw Toy</x:v>
+      </x:c>
+      <x:c r="B617" s="230" t="str">
+        <x:v>/images/pets/Stegosaurus Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C617" s="238"/>
+      <x:c r="D617" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618" ht="19" customHeight="1">
+      <x:c r="A618" s="230" t="str">
+        <x:v>Stick Throw Toy</x:v>
+      </x:c>
+      <x:c r="B618" s="230" t="str">
+        <x:v>/images/pets/Stick Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C618" s="238"/>
+      <x:c r="D618" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619" ht="19" customHeight="1">
+      <x:c r="A619" s="230" t="str">
+        <x:v>Strawberry Cake Roll Flying Disc</x:v>
+      </x:c>
+      <x:c r="B619" s="230" t="str">
+        <x:v>/images/pets/Strawberry Cake Roll Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C619" s="238"/>
+      <x:c r="D619" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620" ht="19" customHeight="1">
+      <x:c r="A620" s="230" t="str">
+        <x:v>Strawberry Cakeroll Plush</x:v>
+      </x:c>
+      <x:c r="B620" s="230" t="str">
+        <x:v>/images/pets/Strawberry Cakeroll Plush.png</x:v>
+      </x:c>
+      <x:c r="C620" s="238"/>
+      <x:c r="D620" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621" ht="19" customHeight="1">
+      <x:c r="A621" s="230" t="str">
+        <x:v>Strawberry Jam Rattle</x:v>
+      </x:c>
+      <x:c r="B621" s="230" t="str">
+        <x:v>/images/pets/Strawberry Jam Rattle.png</x:v>
+      </x:c>
+      <x:c r="C621" s="238"/>
+      <x:c r="D621" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622" ht="19" customHeight="1">
+      <x:c r="A622" s="230" t="str">
+        <x:v>Strawberry Kitty Throw Toy</x:v>
+      </x:c>
+      <x:c r="B622" s="230" t="str">
+        <x:v>/images/pets/Strawberry Kitty Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C622" s="238"/>
+      <x:c r="D622" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623" ht="19" customHeight="1">
+      <x:c r="A623" s="230" t="str">
+        <x:v>Strawberry Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B623" s="230" t="str">
+        <x:v>/images/pets/Strawberry Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C623" s="238"/>
+      <x:c r="D623" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624" ht="19" customHeight="1">
+      <x:c r="A624" s="230" t="str">
+        <x:v>Strawberry Rattle</x:v>
+      </x:c>
+      <x:c r="B624" s="230" t="str">
+        <x:v>/images/pets/Strawberry Rattle.png</x:v>
+      </x:c>
+      <x:c r="C624" s="238"/>
+      <x:c r="D624" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625" ht="19" customHeight="1">
+      <x:c r="A625" s="230" t="str">
+        <x:v>Strawberry Sandwich Chew Toy</x:v>
+      </x:c>
+      <x:c r="B625" s="230" t="str">
+        <x:v>/images/pets/Strawberry Sandwich Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C625" s="238"/>
+      <x:c r="D625" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="626" ht="19" customHeight="1">
+      <x:c r="A626" s="230" t="str">
+        <x:v>Strawberry Teapot Leash</x:v>
+      </x:c>
+      <x:c r="B626" s="230" t="str">
+        <x:v>/images/pets/Strawberry Teapot Leash.png</x:v>
+      </x:c>
+      <x:c r="C626" s="238"/>
+      <x:c r="D626" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="627" ht="19" customHeight="1">
+      <x:c r="A627" s="230" t="str">
+        <x:v>Strawberry Toast Flying Disc</x:v>
+      </x:c>
+      <x:c r="B627" s="230" t="str">
+        <x:v>/images/pets/Strawberry Toast Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C627" s="238"/>
+      <x:c r="D627" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="628" ht="19" customHeight="1">
+      <x:c r="A628" s="230" t="str">
+        <x:v>Succulent Plush</x:v>
+      </x:c>
+      <x:c r="B628" s="230" t="str">
+        <x:v>/images/pets/Succulent Plush.png</x:v>
+      </x:c>
+      <x:c r="C628" s="238"/>
+      <x:c r="D628" s="234" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="629" ht="19" customHeight="1">
+      <x:c r="A629" s="230" t="str">
+        <x:v>Sun Balloon</x:v>
+      </x:c>
+      <x:c r="B629" s="230" t="str">
+        <x:v>/images/pets/Sun Balloon.png</x:v>
+      </x:c>
+      <x:c r="C629" s="238"/>
+      <x:c r="D629" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="630" ht="19" customHeight="1">
+      <x:c r="A630" s="230" t="str">
+        <x:v>Sunflower Rattle</x:v>
+      </x:c>
+      <x:c r="B630" s="230" t="str">
+        <x:v>/images/pets/Sunflower Rattle.png</x:v>
+      </x:c>
+      <x:c r="C630" s="238"/>
+      <x:c r="D630" s="234" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="631" ht="19" customHeight="1">
+      <x:c r="A631" s="230" t="str">
+        <x:v>Sunrise Hang Glider</x:v>
+      </x:c>
+      <x:c r="B631" s="230" t="str">
+        <x:v>/images/pets/Sunrise Hang Glider.png</x:v>
+      </x:c>
+      <x:c r="C631" s="238"/>
+      <x:c r="D631" s="234" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="632" ht="19" customHeight="1">
+      <x:c r="A632" s="230" t="str">
+        <x:v>Sunshine Token</x:v>
+      </x:c>
+      <x:c r="B632" s="230" t="str">
+        <x:v>/images/pets/Sunshine Token.png</x:v>
+      </x:c>
+      <x:c r="C632" s="238"/>
+      <x:c r="D632" s="234" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="633" ht="19" customHeight="1">
+      <x:c r="A633" s="230" t="str">
+        <x:v>Sushi Plushie</x:v>
+      </x:c>
+      <x:c r="B633" s="230" t="str">
+        <x:v>/images/pets/Sushi Plushie.png</x:v>
+      </x:c>
+      <x:c r="C633" s="238"/>
+      <x:c r="D633" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="634" ht="19" customHeight="1">
+      <x:c r="A634" s="230" t="str">
+        <x:v>T-Rex Chew Toy</x:v>
+      </x:c>
+      <x:c r="B634" s="230" t="str">
+        <x:v>/images/pets/T-Rex Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C634" s="238"/>
+      <x:c r="D634" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="635" ht="19" customHeight="1">
+      <x:c r="A635" s="230" t="str">
+        <x:v>T-Rex Rattle</x:v>
+      </x:c>
+      <x:c r="B635" s="230" t="str">
+        <x:v>/images/pets/T-Rex Rattle.png</x:v>
+      </x:c>
+      <x:c r="C635" s="238"/>
+      <x:c r="D635" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="636" ht="19" customHeight="1">
+      <x:c r="A636" s="230" t="str">
+        <x:v>T-Rex Throw Toy</x:v>
+      </x:c>
+      <x:c r="B636" s="230" t="str">
+        <x:v>/images/pets/T-Rex Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C636" s="238"/>
+      <x:c r="D636" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="637" ht="19" customHeight="1">
+      <x:c r="A637" s="230" t="str">
+        <x:v>Taiyaki Chew Toy</x:v>
+      </x:c>
+      <x:c r="B637" s="230" t="str">
+        <x:v>/images/pets/Taiyaki Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C637" s="238"/>
+      <x:c r="D637" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="638" ht="19" customHeight="1">
+      <x:c r="A638" s="230" t="str">
+        <x:v>Tall Glow Mushroom</x:v>
+      </x:c>
+      <x:c r="B638" s="230" t="str">
+        <x:v>/images/pets/Tall Glow Mushroom.png</x:v>
+      </x:c>
+      <x:c r="C638" s="238"/>
+      <x:c r="D638" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="639" ht="19" customHeight="1">
+      <x:c r="A639" s="230" t="str">
+        <x:v>Tall Mushroom</x:v>
+      </x:c>
+      <x:c r="B639" s="230" t="str">
+        <x:v>/images/pets/Tall Mushroom.png</x:v>
+      </x:c>
+      <x:c r="C639" s="238"/>
+      <x:c r="D639" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="640" ht="19" customHeight="1">
+      <x:c r="A640" s="230" t="str">
+        <x:v>Tangerine Chew Toy</x:v>
+      </x:c>
+      <x:c r="B640" s="230" t="str">
+        <x:v>/images/pets/Tangerine Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C640" s="238"/>
+      <x:c r="D640" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="641" ht="19" customHeight="1">
+      <x:c r="A641" s="230" t="str">
+        <x:v>Tape Measure Leash</x:v>
+      </x:c>
+      <x:c r="B641" s="230" t="str">
+        <x:v>/images/pets/Tape Measure Leash.png</x:v>
+      </x:c>
+      <x:c r="C641" s="238"/>
+      <x:c r="D641" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="642" ht="19" customHeight="1">
+      <x:c r="A642" s="230" t="str">
+        <x:v>Tea Party Chair</x:v>
+      </x:c>
+      <x:c r="B642" s="230" t="str">
+        <x:v>/images/pets/Tea Party Chair.png</x:v>
+      </x:c>
+      <x:c r="C642" s="238"/>
+      <x:c r="D642" s="234" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="643" ht="19" customHeight="1">
+      <x:c r="A643" s="230" t="str">
+        <x:v>Tea Party Set</x:v>
+      </x:c>
+      <x:c r="B643" s="230" t="str">
+        <x:v>/images/pets/Tea Party Set.png</x:v>
+      </x:c>
+      <x:c r="C643" s="238"/>
+      <x:c r="D643" s="234" t="n">
+        <x:v>3.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="644" ht="19" customHeight="1">
+      <x:c r="A644" s="230" t="str">
+        <x:v>Teddy Bear</x:v>
+      </x:c>
+      <x:c r="B644" s="230" t="str">
+        <x:v>/images/pets/Teddy Bear.png</x:v>
+      </x:c>
+      <x:c r="C644" s="238"/>
+      <x:c r="D644" s="234" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="645" ht="19" customHeight="1">
+      <x:c r="A645" s="230" t="str">
+        <x:v>Teddy Skele</x:v>
+      </x:c>
+      <x:c r="B645" s="230" t="str">
+        <x:v>/images/pets/Teddy Skele.png</x:v>
+      </x:c>
+      <x:c r="C645" s="238"/>
+      <x:c r="D645" s="234" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="646" ht="19" customHeight="1">
+      <x:c r="A646" s="230" t="str">
+        <x:v>Telescope Pogo</x:v>
+      </x:c>
+      <x:c r="B646" s="230" t="str">
+        <x:v>/images/pets/Telescope Pogo.png</x:v>
+      </x:c>
+      <x:c r="C646" s="238"/>
+      <x:c r="D646" s="234" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="647" ht="19" customHeight="1">
+      <x:c r="A647" s="230" t="str">
+        <x:v>Tennis Ball</x:v>
+      </x:c>
+      <x:c r="B647" s="230" t="str">
+        <x:v>/images/pets/Tennis Ball.png</x:v>
+      </x:c>
+      <x:c r="C647" s="238"/>
+      <x:c r="D647" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="648" ht="19" customHeight="1">
+      <x:c r="A648" s="230" t="str">
+        <x:v>Tennis Racket Toy</x:v>
+      </x:c>
+      <x:c r="B648" s="230" t="str">
+        <x:v>/images/pets/Tennis Racket Toy.png</x:v>
+      </x:c>
+      <x:c r="C648" s="238"/>
+      <x:c r="D648" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="649" ht="19" customHeight="1">
+      <x:c r="A649" s="230" t="str">
+        <x:v>Thor's Grappling Hammer</x:v>
+      </x:c>
+      <x:c r="B649" s="230" t="str">
+        <x:v>/images/pets/Thor's Grappling Hammer.png</x:v>
+      </x:c>
+      <x:c r="C649" s="238"/>
+      <x:c r="D649" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="650" ht="19" customHeight="1">
+      <x:c r="A650" s="230" t="str">
+        <x:v>Throwing Pumpkin</x:v>
+      </x:c>
+      <x:c r="B650" s="230" t="str">
+        <x:v>/images/pets/Throwing Pumpkin.png</x:v>
+      </x:c>
+      <x:c r="C650" s="238"/>
+      <x:c r="D650" s="234" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="651" ht="19" customHeight="1">
+      <x:c r="A651" s="230" t="str">
+        <x:v>Tombstone Ghostify</x:v>
+      </x:c>
+      <x:c r="B651" s="230" t="str">
+        <x:v>/images/pets/Tombstone Ghostify.png</x:v>
+      </x:c>
+      <x:c r="C651" s="238"/>
+      <x:c r="D651" s="234" t="n">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="652" ht="19" customHeight="1">
+      <x:c r="A652" s="230" t="str">
+        <x:v>Top Hat Flying Disc</x:v>
+      </x:c>
+      <x:c r="B652" s="230" t="str">
+        <x:v>/images/pets/Top Hat Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C652" s="238"/>
+      <x:c r="D652" s="234" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="653" ht="19" customHeight="1">
+      <x:c r="A653" s="230" t="str">
+        <x:v>Top Hat Frisbee</x:v>
+      </x:c>
+      <x:c r="B653" s="230" t="str">
+        <x:v>/images/pets/Top Hat Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C653" s="238"/>
+      <x:c r="D653" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="654" ht="19" customHeight="1">
+      <x:c r="A654" s="230" t="str">
+        <x:v>Toy Drum Flying Disc</x:v>
+      </x:c>
+      <x:c r="B654" s="230" t="str">
+        <x:v>/images/pets/Toy Drum Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C654" s="238"/>
+      <x:c r="D654" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="655" ht="19" customHeight="1">
+      <x:c r="A655" s="230" t="str">
+        <x:v>Toy Handcuffs</x:v>
+      </x:c>
+      <x:c r="B655" s="230" t="str">
+        <x:v>/images/pets/Toy Handcuffs.png</x:v>
+      </x:c>
+      <x:c r="C655" s="238"/>
+      <x:c r="D655" s="234" t="n">
+        <x:v>0.015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="656" ht="19" customHeight="1">
+      <x:c r="A656" s="230" t="str">
+        <x:v>Toy Sword</x:v>
+      </x:c>
+      <x:c r="B656" s="230" t="str">
+        <x:v>/images/pets/Toy Sword.png</x:v>
+      </x:c>
+      <x:c r="C656" s="238"/>
+      <x:c r="D656" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="657" ht="19" customHeight="1">
+      <x:c r="A657" s="230" t="str">
+        <x:v>Transgender Flag</x:v>
+      </x:c>
+      <x:c r="B657" s="230" t="str">
+        <x:v>/images/pets/Transgender Flag.png</x:v>
+      </x:c>
+      <x:c r="C657" s="238"/>
+      <x:c r="D657" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="658" ht="19" customHeight="1">
+      <x:c r="A658" s="230" t="str">
+        <x:v>Treasure Key</x:v>
+      </x:c>
+      <x:c r="B658" s="230" t="str">
+        <x:v>/images/pets/Treasure Key.png</x:v>
+      </x:c>
+      <x:c r="C658" s="238"/>
+      <x:c r="D658" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="659" ht="19" customHeight="1">
+      <x:c r="A659" s="230" t="str">
+        <x:v>Treble Clef Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B659" s="230" t="str">
+        <x:v>/images/pets/Treble Clef Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C659" s="238"/>
+      <x:c r="D659" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="660" ht="19" customHeight="1">
+      <x:c r="A660" s="230" t="str">
+        <x:v>Tree Plush</x:v>
+      </x:c>
+      <x:c r="B660" s="230" t="str">
+        <x:v>/images/pets/Tree Plush.png</x:v>
+      </x:c>
+      <x:c r="C660" s="238"/>
+      <x:c r="D660" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="661" ht="19" customHeight="1">
+      <x:c r="A661" s="230" t="str">
+        <x:v>Trident Throw Toy</x:v>
+      </x:c>
+      <x:c r="B661" s="230" t="str">
+        <x:v>/images/pets/Trident Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C661" s="238"/>
+      <x:c r="D661" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="662" ht="19" customHeight="1">
+      <x:c r="A662" s="230" t="str">
+        <x:v>Tripod Camera</x:v>
+      </x:c>
+      <x:c r="B662" s="230" t="str">
+        <x:v>/images/pets/Tripod Camera.png</x:v>
+      </x:c>
+      <x:c r="C662" s="238"/>
+      <x:c r="D662" s="234" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="663" ht="19" customHeight="1">
+      <x:c r="A663" s="230" t="str">
+        <x:v>Tropical Surge Mega Neon Paint</x:v>
+      </x:c>
+      <x:c r="B663" s="230" t="str">
+        <x:v>/images/pets/Tropical Surge Mega Neon Paint.png</x:v>
+      </x:c>
+      <x:c r="C663" s="238"/>
+      <x:c r="D663" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="664" ht="19" customHeight="1">
+      <x:c r="A664" s="230" t="str">
+        <x:v>Tropical Surge Mega Neon Pet Paint</x:v>
+      </x:c>
+      <x:c r="B664" s="230" t="str">
+        <x:v>/images/pets/Tropical Surge Mega Neon Pet Paint.png</x:v>
+      </x:c>
+      <x:c r="C664" s="238"/>
+      <x:c r="D664" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="665" ht="19" customHeight="1">
+      <x:c r="A665" s="230" t="str">
+        <x:v>Trumpet</x:v>
+      </x:c>
+      <x:c r="B665" s="230" t="str">
+        <x:v>/images/pets/Trumpet.png</x:v>
+      </x:c>
+      <x:c r="C665" s="238"/>
+      <x:c r="D665" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="666" ht="19" customHeight="1">
+      <x:c r="A666" s="230" t="str">
+        <x:v>Tundra Violin</x:v>
+      </x:c>
+      <x:c r="B666" s="230" t="str">
+        <x:v>/images/pets/Tundra Violin.png</x:v>
+      </x:c>
+      <x:c r="C666" s="238"/>
+      <x:c r="D666" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="667" ht="19" customHeight="1">
+      <x:c r="A667" s="230" t="str">
+        <x:v>Turkey Leg</x:v>
+      </x:c>
+      <x:c r="B667" s="230" t="str">
+        <x:v>/images/pets/Turkey Leg.png</x:v>
+      </x:c>
+      <x:c r="C667" s="238"/>
+      <x:c r="D667" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="668" ht="19" customHeight="1">
+      <x:c r="A668" s="230" t="str">
+        <x:v>Turkey Plush</x:v>
+      </x:c>
+      <x:c r="B668" s="230" t="str">
+        <x:v>/images/pets/Turkey Plush.png</x:v>
+      </x:c>
+      <x:c r="C668" s="238"/>
+      <x:c r="D668" s="234" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="669" ht="19" customHeight="1">
+      <x:c r="A669" s="230" t="str">
+        <x:v>Twisty Marshmallow Chew Toy</x:v>
+      </x:c>
+      <x:c r="B669" s="230" t="str">
+        <x:v>/images/pets/Twisty Marshmallow Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C669" s="238"/>
+      <x:c r="D669" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="670" ht="19" customHeight="1">
+      <x:c r="A670" s="230" t="str">
+        <x:v>Ukulele</x:v>
+      </x:c>
+      <x:c r="B670" s="230" t="str">
+        <x:v>/images/pets/Ukulele.png</x:v>
+      </x:c>
+      <x:c r="C670" s="238"/>
+      <x:c r="D670" s="234" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="671" ht="19" customHeight="1">
+      <x:c r="A671" s="230" t="str">
+        <x:v>Umbrella Propeller</x:v>
+      </x:c>
+      <x:c r="B671" s="230" t="str">
+        <x:v>/images/pets/Umbrella Propeller.png</x:v>
+      </x:c>
+      <x:c r="C671" s="238"/>
+      <x:c r="D671" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="672" ht="19" customHeight="1">
+      <x:c r="A672" s="230" t="str">
+        <x:v>Unicorn Leash</x:v>
+      </x:c>
+      <x:c r="B672" s="230" t="str">
+        <x:v>/images/pets/Unicorn Leash.png</x:v>
+      </x:c>
+      <x:c r="C672" s="238"/>
+      <x:c r="D672" s="234" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="673" ht="19" customHeight="1">
+      <x:c r="A673" s="230" t="str">
+        <x:v>Unicorn Plush</x:v>
+      </x:c>
+      <x:c r="B673" s="230" t="str">
+        <x:v>/images/pets/Unicorn Plush.png</x:v>
+      </x:c>
+      <x:c r="C673" s="238"/>
+      <x:c r="D673" s="234" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="674" ht="19" customHeight="1">
+      <x:c r="A674" s="230" t="str">
+        <x:v>Unicorn Rattle</x:v>
+      </x:c>
+      <x:c r="B674" s="230" t="str">
+        <x:v>/images/pets/Unicorn Rattle.png</x:v>
+      </x:c>
+      <x:c r="C674" s="238"/>
+      <x:c r="D674" s="234" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="675" ht="19" customHeight="1">
+      <x:c r="A675" s="230" t="str">
+        <x:v>Unpoppable Bubble</x:v>
+      </x:c>
+      <x:c r="B675" s="230" t="str">
+        <x:v>/images/pets/Unpoppable Bubble.png</x:v>
+      </x:c>
+      <x:c r="C675" s="238"/>
+      <x:c r="D675" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="676" ht="19" customHeight="1">
+      <x:c r="A676" s="230" t="str">
+        <x:v>Vampire Chew Toy</x:v>
+      </x:c>
+      <x:c r="B676" s="230" t="str">
+        <x:v>/images/pets/Vampire Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C676" s="238"/>
+      <x:c r="D676" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="677" ht="19" customHeight="1">
+      <x:c r="A677" s="230" t="str">
+        <x:v>Vampire Skull Rattle</x:v>
+      </x:c>
+      <x:c r="B677" s="230" t="str">
+        <x:v>/images/pets/Vampire Skull Rattle.png</x:v>
+      </x:c>
+      <x:c r="C677" s="238"/>
+      <x:c r="D677" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="678" ht="19" customHeight="1">
+      <x:c r="A678" s="230" t="str">
+        <x:v>Vampire Teeth Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B678" s="230" t="str">
+        <x:v>/images/pets/Vampire Teeth Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C678" s="238"/>
+      <x:c r="D678" s="234" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="679" ht="19" customHeight="1">
+      <x:c r="A679" s="230" t="str">
+        <x:v>Velociraptor Fossil</x:v>
+      </x:c>
+      <x:c r="B679" s="230" t="str">
+        <x:v>/images/pets/Velociraptor Fossil.png</x:v>
+      </x:c>
+      <x:c r="C679" s="238"/>
+      <x:c r="D679" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="680" ht="19" customHeight="1">
+      <x:c r="A680" s="230" t="str">
+        <x:v>Velvet Fuschia Mega Neon Paint</x:v>
+      </x:c>
+      <x:c r="B680" s="230" t="str">
+        <x:v>/images/pets/Velvet Fuschia Mega Neon Paint.png</x:v>
+      </x:c>
+      <x:c r="C680" s="238"/>
+      <x:c r="D680" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="681" ht="19" customHeight="1">
+      <x:c r="A681" s="230" t="str">
+        <x:v>Velvet Fuschia Mega Neon Pet Paint</x:v>
+      </x:c>
+      <x:c r="B681" s="230" t="str">
+        <x:v>/images/pets/Velvet Fuschia Mega Neon Pet Paint.png</x:v>
+      </x:c>
+      <x:c r="C681" s="238"/>
+      <x:c r="D681" s="234" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="682" ht="19" customHeight="1">
+      <x:c r="A682" s="230" t="str">
+        <x:v>Venus Fly Trap Rattle</x:v>
+      </x:c>
+      <x:c r="B682" s="230" t="str">
+        <x:v>/images/pets/Venus Fly Trap Rattle.png</x:v>
+      </x:c>
+      <x:c r="C682" s="238"/>
+      <x:c r="D682" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="683" ht="19" customHeight="1">
+      <x:c r="A683" s="230" t="str">
+        <x:v>Viking Shield Throw Toy</x:v>
+      </x:c>
+      <x:c r="B683" s="230" t="str">
+        <x:v>/images/pets/Viking Shield Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C683" s="238"/>
+      <x:c r="D683" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="684" ht="19" customHeight="1">
+      <x:c r="A684" s="230" t="str">
+        <x:v>Vine Leash</x:v>
+      </x:c>
+      <x:c r="B684" s="230" t="str">
+        <x:v>/images/pets/Vine Leash.png</x:v>
+      </x:c>
+      <x:c r="C684" s="238"/>
+      <x:c r="D684" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="685" ht="19" customHeight="1">
+      <x:c r="A685" s="230" t="str">
+        <x:v>Violet Pogostick</x:v>
+      </x:c>
+      <x:c r="B685" s="230" t="str">
+        <x:v>/images/pets/Violet Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C685" s="238"/>
+      <x:c r="D685" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="686" ht="19" customHeight="1">
+      <x:c r="A686" s="230" t="str">
+        <x:v>Voting Paddle</x:v>
+      </x:c>
+      <x:c r="B686" s="230" t="str">
+        <x:v>/images/pets/Voting Paddle.png</x:v>
+      </x:c>
+      <x:c r="C686" s="238"/>
+      <x:c r="D686" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="687" ht="19" customHeight="1">
+      <x:c r="A687" s="230" t="str">
+        <x:v>Wallet Chew Toy</x:v>
+      </x:c>
+      <x:c r="B687" s="230" t="str">
+        <x:v>/images/pets/Wallet Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C687" s="238"/>
+      <x:c r="D687" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="688" ht="19" customHeight="1">
+      <x:c r="A688" s="230" t="str">
+        <x:v>Water Drop Plush</x:v>
+      </x:c>
+      <x:c r="B688" s="230" t="str">
+        <x:v>/images/pets/Water Drop Plush.png</x:v>
+      </x:c>
+      <x:c r="C688" s="238"/>
+      <x:c r="D688" s="234" t="n">
+        <x:v>0.005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="689" ht="19" customHeight="1">
+      <x:c r="A689" s="230" t="str">
+        <x:v>Water Pail Leash</x:v>
+      </x:c>
+      <x:c r="B689" s="230" t="str">
+        <x:v>/images/pets/Water Pail Leash.png</x:v>
+      </x:c>
+      <x:c r="C689" s="238"/>
+      <x:c r="D689" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="690" ht="19" customHeight="1">
+      <x:c r="A690" s="230" t="str">
+        <x:v>Water Soaker Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B690" s="230" t="str">
+        <x:v>/images/pets/Water Soaker Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C690" s="238"/>
+      <x:c r="D690" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="691" ht="19" customHeight="1">
+      <x:c r="A691" s="230" t="str">
+        <x:v>Water Wings</x:v>
+      </x:c>
+      <x:c r="B691" s="230" t="str">
+        <x:v>/images/pets/Water Wings.png</x:v>
+      </x:c>
+      <x:c r="C691" s="238"/>
+      <x:c r="D691" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="692" ht="19" customHeight="1">
+      <x:c r="A692" s="230" t="str">
+        <x:v>Whip Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B692" s="230" t="str">
+        <x:v>/images/pets/Whip Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C692" s="238"/>
+      <x:c r="D692" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="693" ht="19" customHeight="1">
+      <x:c r="A693" s="230" t="str">
+        <x:v>White Fern</x:v>
+      </x:c>
+      <x:c r="B693" s="230" t="str">
+        <x:v>/images/pets/White Fern.png</x:v>
+      </x:c>
+      <x:c r="C693" s="238"/>
+      <x:c r="D693" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="694" ht="19" customHeight="1">
+      <x:c r="A694" s="230" t="str">
+        <x:v>White Pogostick</x:v>
+      </x:c>
+      <x:c r="B694" s="230" t="str">
+        <x:v>/images/pets/White Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C694" s="238"/>
+      <x:c r="D694" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="695" ht="19" customHeight="1">
+      <x:c r="A695" s="230" t="str">
+        <x:v>Whoopee Cushion</x:v>
+      </x:c>
+      <x:c r="B695" s="230" t="str">
+        <x:v>/images/pets/Whoopee Cushion.png</x:v>
+      </x:c>
+      <x:c r="C695" s="238"/>
+      <x:c r="D695" s="234" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="696" ht="19" customHeight="1">
+      <x:c r="A696" s="230" t="str">
+        <x:v>Wing Hang Glider</x:v>
+      </x:c>
+      <x:c r="B696" s="230" t="str">
+        <x:v>/images/pets/Wing Hang Glider.png</x:v>
+      </x:c>
+      <x:c r="C696" s="238"/>
+      <x:c r="D696" s="234" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="697" ht="19" customHeight="1">
+      <x:c r="A697" s="230" t="str">
+        <x:v>Winged Flying Disc</x:v>
+      </x:c>
+      <x:c r="B697" s="230" t="str">
+        <x:v>/images/pets/Winged Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C697" s="238"/>
+      <x:c r="D697" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="698" ht="19" customHeight="1">
+      <x:c r="A698" s="230" t="str">
+        <x:v>Winter Lantern</x:v>
+      </x:c>
+      <x:c r="B698" s="230" t="str">
+        <x:v>/images/pets/Winter Lantern.png</x:v>
+      </x:c>
+      <x:c r="C698" s="238"/>
+      <x:c r="D698" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="699" ht="19" customHeight="1">
+      <x:c r="A699" s="230" t="str">
+        <x:v>Wishing Star</x:v>
+      </x:c>
+      <x:c r="B699" s="230" t="str">
+        <x:v>/images/pets/Wishing Star.png</x:v>
+      </x:c>
+      <x:c r="C699" s="238"/>
+      <x:c r="D699" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="700" ht="19" customHeight="1">
+      <x:c r="A700" s="230" t="str">
+        <x:v>Witch Claw Grapple</x:v>
+      </x:c>
+      <x:c r="B700" s="230" t="str">
+        <x:v>/images/pets/Witch Claw Grapple.png</x:v>
+      </x:c>
+      <x:c r="C700" s="238"/>
+      <x:c r="D700" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="701" ht="19" customHeight="1">
+      <x:c r="A701" s="230" t="str">
+        <x:v>Witch Propeller</x:v>
+      </x:c>
+      <x:c r="B701" s="230" t="str">
+        <x:v>/images/pets/Witch Propeller.png</x:v>
+      </x:c>
+      <x:c r="C701" s="238"/>
+      <x:c r="D701" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="702" ht="19" customHeight="1">
+      <x:c r="A702" s="230" t="str">
+        <x:v>Witches Wand</x:v>
+      </x:c>
+      <x:c r="B702" s="230" t="str">
+        <x:v>/images/pets/Witches Wand.png</x:v>
+      </x:c>
+      <x:c r="C702" s="238"/>
+      <x:c r="D702" s="234" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="703" ht="19" customHeight="1">
+      <x:c r="A703" s="230" t="str">
+        <x:v>Wooden Pan Flute</x:v>
+      </x:c>
+      <x:c r="B703" s="230" t="str">
+        <x:v>/images/pets/Wooden Pan Flute.png</x:v>
+      </x:c>
+      <x:c r="C703" s="238"/>
+      <x:c r="D703" s="234" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="704" ht="19" customHeight="1">
+      <x:c r="A704" s="230" t="str">
+        <x:v>Wooden Pogo</x:v>
+      </x:c>
+      <x:c r="B704" s="230" t="str">
+        <x:v>/images/pets/Wooden Pogo.png</x:v>
+      </x:c>
+      <x:c r="C704" s="238"/>
+      <x:c r="D704" s="234" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="705" ht="19" customHeight="1">
+      <x:c r="A705" s="230" t="str">
+        <x:v>Wooden Spoon Toy</x:v>
+      </x:c>
+      <x:c r="B705" s="230" t="str">
+        <x:v>/images/pets/Wooden Spoon Toy.png</x:v>
+      </x:c>
+      <x:c r="C705" s="238"/>
+      <x:c r="D705" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="706" ht="19" customHeight="1">
+      <x:c r="A706" s="230" t="str">
+        <x:v>Wooden Sword</x:v>
+      </x:c>
+      <x:c r="B706" s="230" t="str">
+        <x:v>/images/pets/Wooden Sword.png</x:v>
+      </x:c>
+      <x:c r="C706" s="238"/>
+      <x:c r="D706" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="707" ht="19" customHeight="1">
+      <x:c r="A707" s="230" t="str">
+        <x:v>Worm Farm Grappling Hook</x:v>
+      </x:c>
+      <x:c r="B707" s="230" t="str">
+        <x:v>/images/pets/Worm Farm Grappling Hook.png</x:v>
+      </x:c>
+      <x:c r="C707" s="238"/>
+      <x:c r="D707" s="234" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="708" ht="19" customHeight="1">
+      <x:c r="A708" s="230" t="str">
+        <x:v>Wrapping Paper Throw Toy</x:v>
+      </x:c>
+      <x:c r="B708" s="230" t="str">
+        <x:v>/images/pets/Wrapping Paper Throw Toy.png</x:v>
+      </x:c>
+      <x:c r="C708" s="238"/>
+      <x:c r="D708" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="709" ht="19" customHeight="1">
+      <x:c r="A709" s="230" t="str">
+        <x:v>Wreath Flying Disc</x:v>
+      </x:c>
+      <x:c r="B709" s="230" t="str">
+        <x:v>/images/pets/Wreath Flying Disc.png</x:v>
+      </x:c>
+      <x:c r="C709" s="238"/>
+      <x:c r="D709" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="710" ht="19" customHeight="1">
+      <x:c r="A710" s="230" t="str">
+        <x:v>Wreath Frisbee</x:v>
+      </x:c>
+      <x:c r="B710" s="230" t="str">
+        <x:v>/images/pets/Wreath Frisbee.png</x:v>
+      </x:c>
+      <x:c r="C710" s="238"/>
+      <x:c r="D710" s="234" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="711" ht="19" customHeight="1">
+      <x:c r="A711" s="230" t="str">
+        <x:v>Wrench Chew Toy</x:v>
+      </x:c>
+      <x:c r="B711" s="230" t="str">
+        <x:v>/images/pets/Wrench Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C711" s="238"/>
+      <x:c r="D711" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="712" ht="19" customHeight="1">
+      <x:c r="A712" s="230" t="str">
+        <x:v>Xmas Carousel Propeller</x:v>
+      </x:c>
+      <x:c r="B712" s="230" t="str">
+        <x:v>/images/pets/Xmas Carousel Propeller.png</x:v>
+      </x:c>
+      <x:c r="C712" s="238"/>
+      <x:c r="D712" s="234" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="713" ht="19" customHeight="1">
+      <x:c r="A713" s="230" t="str">
+        <x:v>Xmas Tree Rattle</x:v>
+      </x:c>
+      <x:c r="B713" s="230" t="str">
+        <x:v>/images/pets/Xmas Tree Rattle.png</x:v>
+      </x:c>
+      <x:c r="C713" s="238"/>
+      <x:c r="D713" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="714" ht="19" customHeight="1">
+      <x:c r="A714" s="230" t="str">
+        <x:v>Yarn Apple</x:v>
+      </x:c>
+      <x:c r="B714" s="230" t="str">
+        <x:v>/images/pets/Yarn Apple.png</x:v>
+      </x:c>
+      <x:c r="C714" s="238"/>
+      <x:c r="D714" s="234" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="715" ht="19" customHeight="1">
+      <x:c r="A715" s="230" t="str">
+        <x:v>Yellow Pogostick</x:v>
+      </x:c>
+      <x:c r="B715" s="230" t="str">
+        <x:v>/images/pets/Yellow Pogostick.png</x:v>
+      </x:c>
+      <x:c r="C715" s="238"/>
+      <x:c r="D715" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="716" ht="19" customHeight="1">
+      <x:c r="A716" s="230" t="str">
+        <x:v>Yule Log Chew Toy</x:v>
+      </x:c>
+      <x:c r="B716" s="230" t="str">
+        <x:v>/images/pets/Yule Log Chew Toy.png</x:v>
+      </x:c>
+      <x:c r="C716" s="238"/>
+      <x:c r="D716" s="234" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="717" ht="19" customHeight="1">
+      <x:c r="A717" s="230" t="str">
+        <x:v>Yule Log Pogo Stick</x:v>
+      </x:c>
+      <x:c r="B717" s="230" t="str">
+        <x:v>/images/pets/Yule Log Pogo Stick.png</x:v>
+      </x:c>
+      <x:c r="C717" s="238"/>
+      <x:c r="D717" s="234" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="718" ht="19" customHeight="1">
+      <x:c r="A718" s="230" t="str">
+        <x:v>Zombie Buffalo Plush</x:v>
+      </x:c>
+      <x:c r="B718" s="230" t="str">
+        <x:v>/images/pets/Zombie Buffalo Plush.png</x:v>
+      </x:c>
+      <x:c r="C718" s="238"/>
+      <x:c r="D718" s="234" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="719" ht="19" customHeight="1">
+      <x:c r="A719" s="231" t="str">
+        <x:v>Zombie Finger Rattle</x:v>
+      </x:c>
+      <x:c r="B719" s="231" t="str">
+        <x:v>/images/pets/Zombie Finger Rattle.png</x:v>
+      </x:c>
+      <x:c r="C719" s="239"/>
+      <x:c r="D719" s="235" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:conditionalFormatting sqref="A2:B719">
+    <x:cfRule type="expression" dxfId="21" priority="1">
+      <x:formula>MOD(ROW(),2)=0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="D2:D719">
+    <x:cfRule type="expression" dxfId="22" priority="2">
+      <x:formula>MOD(ROW(),2)=0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/source-data/trading-data.xlsx
+++ b/source-data/trading-data.xlsx
@@ -16083,13 +16083,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Pet Wear-style" pivot="0" count="4" xr9:uid="{A5C48195-EEC2-4DCA-85EE-B76662872FC8}">
+    <tableStyle name="Pet Wear-style" pivot="0" count="4" xr9:uid="{65EE2102-1BC9-4F26-9CE3-F450E931A68D}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
       <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
-    <tableStyle name="Pets-style" pivot="0" count="4" xr9:uid="{8FA0FFCC-A7A6-4E1F-9ECE-535FC510435C}">
+    <tableStyle name="Pets-style" pivot="0" count="4" xr9:uid="{D96CA825-2139-492E-94AF-1EEDB8536D38}">
       <tableStyleElement type="wholeTable" dxfId="20"/>
       <tableStyleElement type="headerRow" dxfId="19"/>
       <tableStyleElement type="firstRowStripe" dxfId="18"/>
@@ -19427,7 +19427,7 @@
         <v>1700</v>
       </c>
       <c r="D75" s="17">
-        <v>60000</v>
+        <v>6000</v>
       </c>
       <c r="E75" s="17">
         <v>21750</v>

--- a/source-data/trading-data.xlsx
+++ b/source-data/trading-data.xlsx
@@ -16083,13 +16083,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Pet Wear-style" pivot="0" count="4" xr9:uid="{65EE2102-1BC9-4F26-9CE3-F450E931A68D}">
+    <tableStyle name="Pet Wear-style" pivot="0" count="4" xr9:uid="{11A85394-7F82-4D01-ADF2-1710DFF2DF7A}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
       <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
-    <tableStyle name="Pets-style" pivot="0" count="4" xr9:uid="{D96CA825-2139-492E-94AF-1EEDB8536D38}">
+    <tableStyle name="Pets-style" pivot="0" count="4" xr9:uid="{7132FCCB-6DB9-477E-9613-B4701EABD6C7}">
       <tableStyleElement type="wholeTable" dxfId="20"/>
       <tableStyleElement type="headerRow" dxfId="19"/>
       <tableStyleElement type="firstRowStripe" dxfId="18"/>

--- a/source-data/trading-data.xlsx
+++ b/source-data/trading-data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26400" windowHeight="10830" activeTab="1"/>
+    <workbookView windowWidth="26400" windowHeight="10230" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -16083,13 +16083,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Pet Wear-style" pivot="0" count="4" xr9:uid="{11A85394-7F82-4D01-ADF2-1710DFF2DF7A}">
+    <tableStyle name="Pet Wear-style" pivot="0" count="4" xr9:uid="{2ED320A1-2B76-48EC-8783-B9ADB58CD970}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
       <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
-    <tableStyle name="Pets-style" pivot="0" count="4" xr9:uid="{7132FCCB-6DB9-477E-9613-B4701EABD6C7}">
+    <tableStyle name="Pets-style" pivot="0" count="4" xr9:uid="{C297F3A3-FC7E-4870-B188-E4019F5315EE}">
       <tableStyleElement type="wholeTable" dxfId="20"/>
       <tableStyleElement type="headerRow" dxfId="19"/>
       <tableStyleElement type="firstRowStripe" dxfId="18"/>
@@ -27008,13 +27008,13 @@
         <v>774</v>
       </c>
       <c r="C367" s="17">
-        <v>640</v>
+        <v>60</v>
       </c>
       <c r="D367" s="17">
-        <v>2180</v>
+        <v>210</v>
       </c>
       <c r="E367" s="17">
-        <v>8745</v>
+        <v>800</v>
       </c>
       <c r="F367" s="17">
         <v>4</v>

--- a/source-data/trading-data.xlsx
+++ b/source-data/trading-data.xlsx
@@ -16083,13 +16083,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Pet Wear-style" pivot="0" count="4" xr9:uid="{2ED320A1-2B76-48EC-8783-B9ADB58CD970}">
+    <tableStyle name="Pet Wear-style" pivot="0" count="4" xr9:uid="{FA53F96C-9E60-4D19-A842-4A09B8608D35}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
       <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
-    <tableStyle name="Pets-style" pivot="0" count="4" xr9:uid="{C297F3A3-FC7E-4870-B188-E4019F5315EE}">
+    <tableStyle name="Pets-style" pivot="0" count="4" xr9:uid="{0279F8A0-0F6D-4E62-97FA-E004D47284A7}">
       <tableStyleElement type="wholeTable" dxfId="20"/>
       <tableStyleElement type="headerRow" dxfId="19"/>
       <tableStyleElement type="firstRowStripe" dxfId="18"/>
@@ -25295,10 +25295,10 @@
         <v>400</v>
       </c>
       <c r="D301" s="17">
-        <v>3560</v>
+        <v>1100</v>
       </c>
       <c r="E301" s="17">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="F301" s="17">
         <v>36.5</v>

--- a/source-data/trading-data.xlsx
+++ b/source-data/trading-data.xlsx
@@ -5202,7 +5202,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1007"/>
+  <dimension ref="A1:I1009"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="24.4416666666667"/>
     <col min="2" max="2" customWidth="1" width="49"/>
@@ -5376,10 +5376,10 @@
         <v>7</v>
       </c>
       <c r="G6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H6">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I6" t="str">
         <v>2D Doggy</v>
@@ -5495,7 +5495,7 @@
         <v>530</v>
       </c>
       <c r="H10">
-        <v>1925</v>
+        <v>1930</v>
       </c>
       <c r="I10" t="str">
         <v>African Wild Dog</v>
@@ -5692,13 +5692,13 @@
         <v>2520</v>
       </c>
       <c r="F17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H17">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="I17" t="str">
         <v>Alpaca</v>
@@ -6243,13 +6243,13 @@
         <v>330</v>
       </c>
       <c r="F36">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="G36">
-        <v>6.79</v>
+        <v>6.86</v>
       </c>
       <c r="H36">
-        <v>27.5</v>
+        <v>27.8</v>
       </c>
       <c r="I36" t="str">
         <v>Astronaut Gorilla</v>
@@ -6475,13 +6475,13 @@
         <v>1800</v>
       </c>
       <c r="F44">
-        <v>9.5</v>
+        <v>10.75</v>
       </c>
       <c r="G44">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H44">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="I44" t="str">
         <v>Bald Eagle</v>
@@ -6536,10 +6536,10 @@
         <v>167</v>
       </c>
       <c r="G46">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H46">
-        <v>1980</v>
+        <v>2000</v>
       </c>
       <c r="I46" t="str">
         <v>Balloon Unicorn</v>
@@ -6684,7 +6684,7 @@
         <v>2170</v>
       </c>
       <c r="H51">
-        <v>6950</v>
+        <v>7000</v>
       </c>
       <c r="I51" t="str">
         <v>Bat Dragon</v>
@@ -7374,13 +7374,13 @@
         <v>24120</v>
       </c>
       <c r="F75">
-        <v>148</v>
+        <v>148.5</v>
       </c>
       <c r="G75">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="H75">
-        <v>2050</v>
+        <v>2100</v>
       </c>
       <c r="I75" t="str">
         <v>Blazing Lion</v>
@@ -7983,13 +7983,13 @@
         <v>110</v>
       </c>
       <c r="F96">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="G96">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="H96">
-        <v>10.25</v>
+        <v>10.75</v>
       </c>
       <c r="I96" t="str">
         <v>Burning Bunny</v>
@@ -8012,13 +8012,13 @@
         <v>3090</v>
       </c>
       <c r="F97">
-        <v>18.75</v>
+        <v>19.75</v>
       </c>
       <c r="G97">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H97">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="I97" t="str">
         <v>Bush Elephant</v>
@@ -8041,13 +8041,13 @@
         <v>190</v>
       </c>
       <c r="F98">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="G98">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="H98">
-        <v>17.6</v>
+        <v>18</v>
       </c>
       <c r="I98" t="str">
         <v>Business Monkey</v>
@@ -8070,13 +8070,13 @@
         <v>2640</v>
       </c>
       <c r="F99">
-        <v>26.25</v>
+        <v>26.5</v>
       </c>
       <c r="G99">
         <v>58</v>
       </c>
       <c r="H99">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="I99" t="str">
         <v>Cabbit</v>
@@ -8273,13 +8273,13 @@
         <v>100</v>
       </c>
       <c r="F106">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="G106">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="H106">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="I106" t="str">
         <v>Candy Cane Snail</v>
@@ -8670,13 +8670,13 @@
         <v>260</v>
       </c>
       <c r="F120">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="G120">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="H120">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="I120" t="str">
         <v>Chef Gorilla</v>
@@ -9691,7 +9691,7 @@
         <v>397</v>
       </c>
       <c r="H155">
-        <v>1275</v>
+        <v>1210</v>
       </c>
       <c r="I155" t="str">
         <v>Crow</v>
@@ -9714,13 +9714,13 @@
         <v>14040</v>
       </c>
       <c r="F156">
-        <v>134</v>
+        <v>134.5</v>
       </c>
       <c r="G156">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="H156">
-        <v>1250</v>
+        <v>1350</v>
       </c>
       <c r="I156" t="str">
         <v>Cryptid</v>
@@ -9830,7 +9830,7 @@
         <v>9420</v>
       </c>
       <c r="F160">
-        <v>58.75</v>
+        <v>59</v>
       </c>
       <c r="G160">
         <v>198</v>
@@ -11132,13 +11132,13 @@
         <v>2000</v>
       </c>
       <c r="F205">
-        <v>15</v>
+        <v>16.25</v>
       </c>
       <c r="G205">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H205">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="I205" t="str">
         <v>Emperor Gorilla</v>
@@ -11399,7 +11399,7 @@
         <v>200</v>
       </c>
       <c r="H214">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="I214" t="str">
         <v>Evil Unicorn</v>
@@ -11422,10 +11422,10 @@
         <v>2000</v>
       </c>
       <c r="F215">
-        <v>15.75</v>
+        <v>16.5</v>
       </c>
       <c r="G215">
-        <v>44</v>
+        <v>44.5</v>
       </c>
       <c r="H215">
         <v>172</v>
@@ -11741,13 +11741,13 @@
         <v>450</v>
       </c>
       <c r="F226">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="G226">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="H226">
-        <v>44.6</v>
+        <v>48</v>
       </c>
       <c r="I226" t="str">
         <v>Flaming Fox</v>
@@ -12124,7 +12124,7 @@
         <v>550</v>
       </c>
       <c r="H239">
-        <v>1465</v>
+        <v>1400</v>
       </c>
       <c r="I239" t="str">
         <v>Frost Dragon</v>
@@ -12205,13 +12205,13 @@
         <v>2300</v>
       </c>
       <c r="F242">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G242">
-        <v>56</v>
+        <v>59.5</v>
       </c>
       <c r="H242">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="I242" t="str">
         <v>Frost Unicorn</v>
@@ -12234,13 +12234,13 @@
         <v>2800</v>
       </c>
       <c r="F243">
-        <v>26.5</v>
+        <v>30</v>
       </c>
       <c r="G243">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="H243">
-        <v>442</v>
+        <v>500</v>
       </c>
       <c r="I243" t="str">
         <v>Frostbite Bear</v>
@@ -12521,13 +12521,13 @@
         <v>230</v>
       </c>
       <c r="F253">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="G253">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="H253">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I253" t="str">
         <v>General Sheepdog</v>
@@ -12608,13 +12608,13 @@
         <v>300</v>
       </c>
       <c r="F256">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="G256">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="H256">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="I256" t="str">
         <v>Ghost Bunny</v>
@@ -12869,13 +12869,13 @@
         <v>30000</v>
       </c>
       <c r="F265">
-        <v>194</v>
+        <v>194.5</v>
       </c>
       <c r="G265">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="H265">
-        <v>2930</v>
+        <v>2960</v>
       </c>
       <c r="I265" t="str">
         <v>Giant Panda</v>
@@ -13107,7 +13107,7 @@
         <v>915</v>
       </c>
       <c r="H273">
-        <v>3100</v>
+        <v>2960</v>
       </c>
       <c r="I273" t="str">
         <v>Giraffe</v>
@@ -13159,13 +13159,13 @@
         <v>810</v>
       </c>
       <c r="F275">
-        <v>3.75</v>
+        <v>7.75</v>
       </c>
       <c r="G275">
-        <v>16.5</v>
+        <v>35</v>
       </c>
       <c r="H275">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="I275" t="str">
         <v>Glacier Moth</v>
@@ -14116,13 +14116,13 @@
         <v>3930</v>
       </c>
       <c r="F308">
-        <v>23</v>
+        <v>23.25</v>
       </c>
       <c r="G308">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H308">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="I308" t="str">
         <v>Grim Dragon</v>
@@ -14319,13 +14319,13 @@
         <v>18500</v>
       </c>
       <c r="F315">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G315">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="H315">
-        <v>1660</v>
+        <v>1725</v>
       </c>
       <c r="I315" t="str">
         <v>Haetae</v>
@@ -14464,13 +14464,13 @@
         <v>870</v>
       </c>
       <c r="F320">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="G320">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H320">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I320" t="str">
         <v>Halloween White Ghost Dragon</v>
@@ -14580,13 +14580,13 @@
         <v>100</v>
       </c>
       <c r="F324">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="G324">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="H324">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="I324" t="str">
         <v>Hamster</v>
@@ -14783,7 +14783,7 @@
         <v>12000</v>
       </c>
       <c r="F331">
-        <v>66.5</v>
+        <v>66.75</v>
       </c>
       <c r="G331">
         <v>250</v>
@@ -14841,13 +14841,13 @@
         <v>1080</v>
       </c>
       <c r="F333">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
       <c r="G333">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H333">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="I333" t="str">
         <v>Hero Gibbon</v>
@@ -14957,13 +14957,13 @@
         <v>960</v>
       </c>
       <c r="F337">
-        <v>4.25</v>
+        <v>6.25</v>
       </c>
       <c r="G337">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H337">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="I337" t="str">
         <v>Honey Badger</v>
@@ -15624,13 +15624,13 @@
         <v>1720</v>
       </c>
       <c r="F360">
-        <v>8.25</v>
+        <v>9.75</v>
       </c>
       <c r="G360">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H360">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="I360" t="str">
         <v>Irish Water Spaniel</v>
@@ -15711,13 +15711,13 @@
         <v>8220</v>
       </c>
       <c r="F363">
-        <v>57.5</v>
+        <v>58</v>
       </c>
       <c r="G363">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H363">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="I363" t="str">
         <v>Jekyll Hydra</v>
@@ -15740,13 +15740,13 @@
         <v>1940</v>
       </c>
       <c r="F364">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="G364">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H364">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="I364" t="str">
         <v>Jellyfish</v>
@@ -15798,13 +15798,13 @@
         <v>980</v>
       </c>
       <c r="F366">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="G366">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H366">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="I366" t="str">
         <v>Jousting Horse</v>
@@ -16001,13 +16001,13 @@
         <v>200</v>
       </c>
       <c r="F373">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="G373">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="H373">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="I373" t="str">
         <v>Karate Gorilla</v>
@@ -16030,13 +16030,13 @@
         <v>280</v>
       </c>
       <c r="F374">
-        <v>0.95</v>
+        <v>3.5</v>
       </c>
       <c r="G374">
-        <v>6.65</v>
+        <v>17</v>
       </c>
       <c r="H374">
-        <v>26.9</v>
+        <v>70</v>
       </c>
       <c r="I374" t="str">
         <v>Kelp Captain</v>
@@ -16059,13 +16059,13 @@
         <v>45</v>
       </c>
       <c r="F375">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="G375">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="H375">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="I375" t="str">
         <v>Kelp Crewmate</v>
@@ -16088,13 +16088,13 @@
         <v>65</v>
       </c>
       <c r="F376">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="G376">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="H376">
-        <v>5.75</v>
+        <v>7.75</v>
       </c>
       <c r="I376" t="str">
         <v>Kelp Hunter</v>
@@ -16117,13 +16117,13 @@
         <v>50</v>
       </c>
       <c r="F377">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="G377">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="H377">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="I377" t="str">
         <v>Kelp Raider</v>
@@ -16204,13 +16204,13 @@
         <v>100</v>
       </c>
       <c r="F380">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G380">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="H380">
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="I380" t="str">
         <v>King Penguin</v>
@@ -16610,13 +16610,13 @@
         <v>945</v>
       </c>
       <c r="F394">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="G394">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H394">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I394" t="str">
         <v>Lava Dragon</v>
@@ -16639,13 +16639,13 @@
         <v>320</v>
       </c>
       <c r="F395">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="G395">
-        <v>7.25</v>
+        <v>6.79</v>
       </c>
       <c r="H395">
-        <v>30</v>
+        <v>27.5</v>
       </c>
       <c r="I395" t="str">
         <v>Lava Wolf</v>
@@ -17680,7 +17680,7 @@
         <v>88</v>
       </c>
       <c r="H431">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="I431" t="str">
         <v>Mermicorn</v>
@@ -17787,13 +17787,13 @@
         <v>850</v>
       </c>
       <c r="F435">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="G435">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H435">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I435" t="str">
         <v>Midnight Dragon</v>
@@ -18013,13 +18013,13 @@
         <v>65</v>
       </c>
       <c r="F443">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G443">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="H443">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="I443" t="str">
         <v>Momma Moose</v>
@@ -18103,10 +18103,10 @@
         <v>34.5</v>
       </c>
       <c r="G446">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H446">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="I446" t="str">
         <v>Monkey King</v>
@@ -18187,13 +18187,13 @@
         <v>3250</v>
       </c>
       <c r="F449">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="G449">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H449">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="I449" t="str">
         <v>Moonbeam Peacock</v>
@@ -19323,7 +19323,7 @@
         <v>601</v>
       </c>
       <c r="H489">
-        <v>1980</v>
+        <v>1860</v>
       </c>
       <c r="I489" t="str">
         <v>Owl</v>
@@ -19404,13 +19404,13 @@
         <v>240</v>
       </c>
       <c r="F492">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="G492">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H492">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="I492" t="str">
         <v>Panda</v>
@@ -19526,7 +19526,7 @@
         <v>394</v>
       </c>
       <c r="H496">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="I496" t="str">
         <v>Parrot</v>
@@ -19691,13 +19691,13 @@
         <v>540</v>
       </c>
       <c r="F502">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="G502">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="H502">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I502" t="str">
         <v>Peahen</v>
@@ -19778,10 +19778,10 @@
         <v>3000</v>
       </c>
       <c r="F505">
-        <v>26.5</v>
+        <v>26.75</v>
       </c>
       <c r="G505">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H505">
         <v>380</v>
@@ -19873,13 +19873,13 @@
         <v>1320</v>
       </c>
       <c r="F509">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="G509">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H509">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="I509" t="str">
         <v>Phantom Dragon</v>
@@ -20134,13 +20134,13 @@
         <v>2640</v>
       </c>
       <c r="F518">
-        <v>14.75</v>
+        <v>15.75</v>
       </c>
       <c r="G518">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H518">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="I518" t="str">
         <v>Pirate Ghost Capuchin Monkey</v>
@@ -21172,13 +21172,13 @@
         <v>210</v>
       </c>
       <c r="F554">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="G554">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="H554">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="I554" t="str">
         <v>Ranger Beaver</v>
@@ -22642,13 +22642,13 @@
         <v>390</v>
       </c>
       <c r="F605">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="G605">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="H605">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I605" t="str">
         <v>Scorching Kaijunior</v>
@@ -22909,7 +22909,7 @@
         <v>1343</v>
       </c>
       <c r="H614">
-        <v>3415</v>
+        <v>3320</v>
       </c>
       <c r="I614" t="str">
         <v>Shadow Dragon</v>
@@ -23367,13 +23367,13 @@
         <v>2000</v>
       </c>
       <c r="F630">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G630">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="H630">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="I630" t="str">
         <v>Silverback Gorilla</v>
@@ -24382,13 +24382,13 @@
         <v>980</v>
       </c>
       <c r="F665">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="G665">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H665">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I665" t="str">
         <v>Strawberry Penguin</v>
@@ -24417,7 +24417,7 @@
         <v>108</v>
       </c>
       <c r="H666">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="I666" t="str">
         <v>Strawberry Shortcake Bat Dragon</v>
@@ -24556,13 +24556,13 @@
         <v>1655</v>
       </c>
       <c r="F671">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="G671">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H671">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="I671" t="str">
         <v>Sugar Axolotl</v>
@@ -25281,13 +25281,13 @@
         <v>1680</v>
       </c>
       <c r="F696">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G696">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H696">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="I696" t="str">
         <v>Tió De Nadal</v>
@@ -25310,13 +25310,13 @@
         <v>130</v>
       </c>
       <c r="F697">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="G697">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H697">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="I697" t="str">
         <v>Toasty Red Panda</v>
@@ -25455,13 +25455,13 @@
         <v>265</v>
       </c>
       <c r="F702">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="G702">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="H702">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="I702" t="str">
         <v>Toy Monkey</v>
@@ -25629,13 +25629,13 @@
         <v>930</v>
       </c>
       <c r="F708">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G708">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="H708">
-        <v>128</v>
+        <v>376</v>
       </c>
       <c r="I708" t="str">
         <v>Tri-Horned Treehopper</v>
@@ -25803,13 +25803,13 @@
         <v>9180</v>
       </c>
       <c r="F714">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G714">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H714">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="I714" t="str">
         <v>Undead Jousting Horse</v>
@@ -25919,13 +25919,13 @@
         <v>1700</v>
       </c>
       <c r="F718">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="G718">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H718">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="I718" t="str">
         <v>Vampire Dragon</v>
@@ -26006,13 +26006,13 @@
         <v>1440</v>
       </c>
       <c r="F721">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="G721">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H721">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I721" t="str">
         <v>Velocirooster</v>
@@ -26093,13 +26093,13 @@
         <v>330</v>
       </c>
       <c r="F724">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="G724">
-        <v>6.86</v>
+        <v>7.25</v>
       </c>
       <c r="H724">
-        <v>27.8</v>
+        <v>30</v>
       </c>
       <c r="I724" t="str">
         <v>Violet Butterfly</v>
@@ -26415,10 +26415,10 @@
         <v>23</v>
       </c>
       <c r="G735">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H735">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="I735" t="str">
         <v>Werewolf</v>
@@ -26557,13 +26557,13 @@
         <v>210</v>
       </c>
       <c r="F740">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="G740">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="H740">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="I740" t="str">
         <v>Wildfire Hawk</v>
@@ -26615,13 +26615,13 @@
         <v>2520</v>
       </c>
       <c r="F742">
-        <v>12.25</v>
+        <v>13.75</v>
       </c>
       <c r="G742">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H742">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="I742" t="str">
         <v>Winged Tiger</v>
@@ -26789,13 +26789,13 @@
         <v>520</v>
       </c>
       <c r="F748">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G748">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="H748">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I748" t="str">
         <v>Wood Pigeon</v>
@@ -27012,13 +27012,13 @@
         <v>190</v>
       </c>
       <c r="F756">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="G756">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H756">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="I756" t="str">
         <v>Yeti</v>
@@ -27157,13 +27157,13 @@
         <v>1920</v>
       </c>
       <c r="F761">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="G761">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H761">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="I761" t="str">
         <v>Zombie Buffalo</v>
@@ -27215,13 +27215,13 @@
         <v>300</v>
       </c>
       <c r="F763">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="G763">
-        <v>6.05</v>
+        <v>6.15</v>
       </c>
       <c r="H763">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
       <c r="I763" t="str">
         <v>Zombie Wolf</v>
@@ -27455,13 +27455,13 @@
         <v>/images/pets/Cake Friend.png</v>
       </c>
       <c r="F1001">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="G1001">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="H1001">
-        <v>25.6</v>
+        <v>25</v>
       </c>
       <c r="I1001" t="str">
         <v>Cake Friend</v>
@@ -27569,21 +27569,55 @@
         <v>/images/pets/Wooly Rhino.png</v>
       </c>
       <c r="F1007">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="G1007">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="H1007">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="I1007" t="str">
         <v>Wooly Rhino</v>
       </c>
     </row>
+    <row r="1008">
+      <c r="A1008" t="str">
+        <v>Chihuaha</v>
+      </c>
+      <c r="B1008" t="str">
+        <v>/images/pets/Chihuaha.png</v>
+      </c>
+      <c r="F1008">
+        <v>1.27</v>
+      </c>
+      <c r="G1008">
+        <v>7.25</v>
+      </c>
+      <c r="H1008">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="str">
+        <v>Tuxedo Cat</v>
+      </c>
+      <c r="B1009" t="str">
+        <v>/images/pets/Tuxedo Cat.png</v>
+      </c>
+      <c r="F1009">
+        <v>2</v>
+      </c>
+      <c r="G1009">
+        <v>11</v>
+      </c>
+      <c r="H1009">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I1007"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1009"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -32893,7 +32927,7 @@
         <v>670</v>
       </c>
       <c r="F379">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="380" ht="19.5" customHeight="1">
@@ -32921,7 +32955,7 @@
         <v>450</v>
       </c>
       <c r="F381">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="382" ht="19.5" customHeight="1">
@@ -38772,7 +38806,7 @@
         <v>860</v>
       </c>
       <c r="F800">
-        <v>150</v>
+        <v>180</v>
       </c>
     </row>
     <row r="801" ht="19.5" customHeight="1">
@@ -38954,7 +38988,7 @@
         <v>940</v>
       </c>
       <c r="F813">
-        <v>151</v>
+        <v>190</v>
       </c>
     </row>
     <row r="814" ht="19.5" customHeight="1">
@@ -38982,7 +39016,7 @@
         <v>970</v>
       </c>
       <c r="F815">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="816" ht="19.5" customHeight="1">
@@ -40807,7 +40841,7 @@
         <v>/images/pets/Buzzing Honeypot Hat.png</v>
       </c>
       <c r="F1001">
-        <v>270</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1002">
@@ -40818,7 +40852,7 @@
         <v>/images/pets/Hive Backpack.png</v>
       </c>
       <c r="F1002">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="1003">
@@ -40848,7 +40882,7 @@
         <v>/images/pets/Panda Cap.png</v>
       </c>
       <c r="F1005">
-        <v>1250</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="1006">
@@ -40859,7 +40893,7 @@
         <v>/images/pets/Queen Bee Slippers.png</v>
       </c>
       <c r="F1006">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1007">
@@ -41324,7 +41358,7 @@
         <v>2500</v>
       </c>
       <c r="D33">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" ht="18.75" customHeight="1">
@@ -42957,7 +42991,7 @@
         <v>3445</v>
       </c>
       <c r="D96">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" ht="18.75" customHeight="1">

--- a/source-data/trading-data.xlsx
+++ b/source-data/trading-data.xlsx
@@ -5202,7 +5202,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1008"/>
+  <dimension ref="A1:I1010"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="28"/>
     <col min="2" max="2" customWidth="1" width="42"/>
@@ -5379,13 +5379,13 @@
         <v>1450</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I7">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -5483,13 +5483,13 @@
         <v>23100</v>
       </c>
       <c r="G11">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H11">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="I11">
-        <v>1940</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -5665,13 +5665,13 @@
         <v>2520</v>
       </c>
       <c r="G18">
-        <v>20.25</v>
+        <v>21</v>
       </c>
       <c r="H18">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I18">
-        <v>322</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -5977,13 +5977,13 @@
         <v>700</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H30">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I30">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -6055,7 +6055,7 @@
         <v>4220</v>
       </c>
       <c r="G33">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H33">
         <v>99</v>
@@ -6159,13 +6159,13 @@
         <v>330</v>
       </c>
       <c r="G37">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="I37">
-        <v>27.8</v>
+        <v>28.45</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -6422,10 +6422,10 @@
         <v>167</v>
       </c>
       <c r="H47">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I47">
-        <v>2000</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -6549,13 +6549,13 @@
         <v>83400</v>
       </c>
       <c r="G52">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="H52">
-        <v>2170</v>
+        <v>2185</v>
       </c>
       <c r="I52">
-        <v>6900</v>
+        <v>6760</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -6731,13 +6731,13 @@
         <v>230</v>
       </c>
       <c r="G59">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="H59">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="I59">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -6887,13 +6887,13 @@
         <v>75</v>
       </c>
       <c r="G65">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H65">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I65">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -7121,13 +7121,13 @@
         <v>2440</v>
       </c>
       <c r="G74">
-        <v>12.5</v>
+        <v>13.75</v>
       </c>
       <c r="H74">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="I74">
-        <v>220</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -7173,13 +7173,13 @@
         <v>24120</v>
       </c>
       <c r="G76">
-        <v>148.5</v>
+        <v>198</v>
       </c>
       <c r="H76">
-        <v>590</v>
+        <v>760</v>
       </c>
       <c r="I76">
-        <v>2200</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -7745,13 +7745,13 @@
         <v>3090</v>
       </c>
       <c r="G98">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="H98">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I98">
-        <v>306</v>
+        <v>334</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -7797,13 +7797,13 @@
         <v>2640</v>
       </c>
       <c r="G100">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H100">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I100">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -7849,13 +7849,13 @@
         <v>980</v>
       </c>
       <c r="G102">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="H102">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="I102">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -7866,13 +7866,13 @@
         <v>/images/pets/Cake Friend.png</v>
       </c>
       <c r="G103">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="H103">
-        <v>5.95</v>
+        <v>5.85</v>
       </c>
       <c r="I103">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -7976,7 +7976,7 @@
         <v>35</v>
       </c>
       <c r="I107">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -8247,13 +8247,13 @@
         <v>645</v>
       </c>
       <c r="G118">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="H118">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I118">
-        <v>54</v>
+        <v>78</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -8628,10 +8628,10 @@
         <v>5500</v>
       </c>
       <c r="G133">
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
       <c r="H133">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I133">
         <v>510</v>
@@ -8732,13 +8732,13 @@
         <v>850</v>
       </c>
       <c r="G137">
-        <v>4.25</v>
+        <v>7</v>
       </c>
       <c r="H137">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I137">
-        <v>83</v>
+        <v>120</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -9278,10 +9278,10 @@
         <v>15900</v>
       </c>
       <c r="G158">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H158">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I158">
         <v>1210</v>
@@ -9304,13 +9304,13 @@
         <v>14040</v>
       </c>
       <c r="G159">
-        <v>134.5</v>
+        <v>136</v>
       </c>
       <c r="H159">
-        <v>345</v>
+        <v>390</v>
       </c>
       <c r="I159">
-        <v>1360</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -9356,13 +9356,13 @@
         <v>1250</v>
       </c>
       <c r="G161">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="H161">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I161">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -9408,7 +9408,7 @@
         <v>9500</v>
       </c>
       <c r="G163">
-        <v>59</v>
+        <v>59.5</v>
       </c>
       <c r="H163">
         <v>198</v>
@@ -9434,13 +9434,13 @@
         <v>780</v>
       </c>
       <c r="G164">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="H164">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I164">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -9451,13 +9451,13 @@
         <v>/images/pets/Dango Penguins.png</v>
       </c>
       <c r="G165">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="H165">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="I165">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -9555,13 +9555,13 @@
         <v>635</v>
       </c>
       <c r="G169">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="H169">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I169">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -9581,13 +9581,13 @@
         <v>880</v>
       </c>
       <c r="G170">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="H170">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I170">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -9607,13 +9607,13 @@
         <v>10800</v>
       </c>
       <c r="G171">
-        <v>62.5</v>
+        <v>65</v>
       </c>
       <c r="H171">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="I171">
-        <v>925</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -9711,13 +9711,13 @@
         <v>620</v>
       </c>
       <c r="G175">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="H175">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I175">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -10283,13 +10283,13 @@
         <v>580</v>
       </c>
       <c r="G197">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="H197">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="I197">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -10554,13 +10554,13 @@
         <v>1000</v>
       </c>
       <c r="G208">
-        <v>1.65</v>
+        <v>1.05</v>
       </c>
       <c r="H208">
-        <v>9.5</v>
+        <v>7.25</v>
       </c>
       <c r="I208">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
@@ -10580,13 +10580,13 @@
         <v>2900</v>
       </c>
       <c r="G209">
-        <v>17.5</v>
+        <v>27</v>
       </c>
       <c r="H209">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="I209">
-        <v>294</v>
+        <v>450</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
@@ -10710,13 +10710,13 @@
         <v>100</v>
       </c>
       <c r="G214">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="H214">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="I214">
-        <v>11.6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
@@ -10762,13 +10762,13 @@
         <v>90</v>
       </c>
       <c r="G216">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H216">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I216">
-        <v>10.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
@@ -10788,13 +10788,13 @@
         <v>210</v>
       </c>
       <c r="G217">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="H217">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="I217">
-        <v>21.6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1">
@@ -10814,7 +10814,7 @@
         <v>7700</v>
       </c>
       <c r="G218">
-        <v>108</v>
+        <v>108.5</v>
       </c>
       <c r="H218">
         <v>200</v>
@@ -10840,13 +10840,13 @@
         <v>2000</v>
       </c>
       <c r="G219">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="H219">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I219">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="220" ht="20" customHeight="1">
@@ -11464,10 +11464,10 @@
         <v>17000</v>
       </c>
       <c r="G243">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H243">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I243">
         <v>1400</v>
@@ -11516,13 +11516,13 @@
         <v>360</v>
       </c>
       <c r="G245">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="H245">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="I245">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1">
@@ -11542,13 +11542,13 @@
         <v>2600</v>
       </c>
       <c r="G246">
-        <v>14</v>
+        <v>14.75</v>
       </c>
       <c r="H246">
-        <v>59.5</v>
+        <v>63</v>
       </c>
       <c r="I246">
-        <v>240</v>
+        <v>256</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1">
@@ -11568,13 +11568,13 @@
         <v>5500</v>
       </c>
       <c r="G247">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H247">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="I247">
-        <v>620</v>
+        <v>590</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1">
@@ -11646,13 +11646,13 @@
         <v>70</v>
       </c>
       <c r="G250">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H250">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="I250">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1">
@@ -11672,13 +11672,13 @@
         <v>260</v>
       </c>
       <c r="G251">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="H251">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I251">
-        <v>21.8</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1">
@@ -11897,13 +11897,13 @@
         <v>285</v>
       </c>
       <c r="G260">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="H260">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="I260">
-        <v>25</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1">
@@ -11920,13 +11920,13 @@
         <v>80</v>
       </c>
       <c r="G261">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H261">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I261">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1">
@@ -11946,13 +11946,13 @@
         <v>240</v>
       </c>
       <c r="G262">
-        <v>0.8</v>
+        <v>1.45</v>
       </c>
       <c r="H262">
-        <v>4.75</v>
+        <v>8.1</v>
       </c>
       <c r="I262">
-        <v>20</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1">
@@ -12024,13 +12024,13 @@
         <v>1290</v>
       </c>
       <c r="G265">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="H265">
-        <v>26.5</v>
+        <v>28</v>
       </c>
       <c r="I265">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1">
@@ -12102,13 +12102,13 @@
         <v>763</v>
       </c>
       <c r="G268">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="H268">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="I268">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1">
@@ -12128,13 +12128,13 @@
         <v>30000</v>
       </c>
       <c r="G269">
-        <v>194.5</v>
+        <v>220</v>
       </c>
       <c r="H269">
-        <v>750</v>
+        <v>870</v>
       </c>
       <c r="I269">
-        <v>2980</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1">
@@ -12318,13 +12318,13 @@
         <v>34000</v>
       </c>
       <c r="G277">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="H277">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="I277">
-        <v>3000</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1">
@@ -12370,13 +12370,13 @@
         <v>810</v>
       </c>
       <c r="G279">
-        <v>7.75</v>
+        <v>5.5</v>
       </c>
       <c r="H279">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I279">
-        <v>148</v>
+        <v>104</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1">
@@ -12445,13 +12445,13 @@
         <v>525</v>
       </c>
       <c r="G282">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="H282">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I282">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1">
@@ -12471,13 +12471,13 @@
         <v>740</v>
       </c>
       <c r="G283">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="H283">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I283">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1">
@@ -12543,13 +12543,13 @@
         <v>1440</v>
       </c>
       <c r="G286">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H286">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I286">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1">
@@ -13219,13 +13219,13 @@
         <v>4300</v>
       </c>
       <c r="G312">
-        <v>23.25</v>
+        <v>29</v>
       </c>
       <c r="H312">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="I312">
-        <v>370</v>
+        <v>460</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1">
@@ -13404,10 +13404,10 @@
         <v>119</v>
       </c>
       <c r="H319">
-        <v>434</v>
+        <v>463</v>
       </c>
       <c r="I319">
-        <v>1750</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1">
@@ -13531,13 +13531,13 @@
         <v>870</v>
       </c>
       <c r="G324">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="H324">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I324">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1">
@@ -13791,13 +13791,13 @@
         <v>160</v>
       </c>
       <c r="G334">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
       <c r="H334">
-        <v>3.35</v>
+        <v>4.55</v>
       </c>
       <c r="I334">
-        <v>14.4</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1">
@@ -13817,7 +13817,7 @@
         <v>12000</v>
       </c>
       <c r="G335">
-        <v>66.75</v>
+        <v>67.25</v>
       </c>
       <c r="H335">
         <v>250</v>
@@ -13869,13 +13869,13 @@
         <v>1080</v>
       </c>
       <c r="G337">
-        <v>7.5</v>
+        <v>8.75</v>
       </c>
       <c r="H337">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I337">
-        <v>140</v>
+        <v>156</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1">
@@ -13973,13 +13973,13 @@
         <v>960</v>
       </c>
       <c r="G341">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="H341">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I341">
-        <v>124</v>
+        <v>96</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1">
@@ -14311,13 +14311,13 @@
         <v>480</v>
       </c>
       <c r="G354">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="H354">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I354">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="355" ht="20" customHeight="1">
@@ -14363,13 +14363,13 @@
         <v>400</v>
       </c>
       <c r="G356">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="H356">
-        <v>8.1</v>
+        <v>9.85</v>
       </c>
       <c r="I356">
-        <v>33.4</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="357" ht="20" customHeight="1">
@@ -14389,13 +14389,13 @@
         <v>80</v>
       </c>
       <c r="G357">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H357">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="I357">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="358" ht="20" customHeight="1">
@@ -14571,13 +14571,13 @@
         <v>1750</v>
       </c>
       <c r="G364">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="H364">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I364">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="365" ht="20" customHeight="1">
@@ -14649,13 +14649,13 @@
         <v>7000</v>
       </c>
       <c r="G367">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H367">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="I367">
-        <v>740</v>
+        <v>855</v>
       </c>
     </row>
     <row r="368" ht="20" customHeight="1">
@@ -14675,13 +14675,13 @@
         <v>2050</v>
       </c>
       <c r="G368">
-        <v>9.75</v>
+        <v>9.5</v>
       </c>
       <c r="H368">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I368">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="369" ht="20" customHeight="1">
@@ -14727,13 +14727,13 @@
         <v>980</v>
       </c>
       <c r="G370">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H370">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I370">
-        <v>110</v>
+        <v>158</v>
       </c>
     </row>
     <row r="371" ht="20" customHeight="1">
@@ -14863,7 +14863,7 @@
         <v>39</v>
       </c>
       <c r="I375">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="376" ht="20" customHeight="1">
@@ -14909,13 +14909,13 @@
         <v>200</v>
       </c>
       <c r="G377">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H377">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="I377">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="378" ht="20" customHeight="1">
@@ -14935,13 +14935,13 @@
         <v>280</v>
       </c>
       <c r="G378">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="H378">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I378">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="379" ht="20" customHeight="1">
@@ -15299,13 +15299,13 @@
         <v>500</v>
       </c>
       <c r="G392">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="H392">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="I392">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="393" ht="20" customHeight="1">
@@ -15429,13 +15429,13 @@
         <v>480</v>
       </c>
       <c r="G397">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="H397">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I397">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="398" ht="20" customHeight="1">
@@ -15455,13 +15455,13 @@
         <v>1150</v>
       </c>
       <c r="G398">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="H398">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I398">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="399" ht="20" customHeight="1">
@@ -15481,13 +15481,13 @@
         <v>320</v>
       </c>
       <c r="G399">
-        <v>0.97</v>
+        <v>1.15</v>
       </c>
       <c r="H399">
-        <v>6.79</v>
+        <v>7.5</v>
       </c>
       <c r="I399">
-        <v>27.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="400" ht="20" customHeight="1">
@@ -15510,10 +15510,10 @@
         <v>2</v>
       </c>
       <c r="H400">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I400">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="401" ht="20" customHeight="1">
@@ -16321,13 +16321,13 @@
         <v>1520</v>
       </c>
       <c r="G432">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="H432">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I432">
-        <v>260</v>
+        <v>300</v>
       </c>
     </row>
     <row r="433" ht="20" customHeight="1">
@@ -16500,13 +16500,13 @@
         <v>850</v>
       </c>
       <c r="G439">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="H439">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I439">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="440" ht="20" customHeight="1">
@@ -16780,13 +16780,13 @@
         <v>6520</v>
       </c>
       <c r="G450">
-        <v>34.5</v>
+        <v>37</v>
       </c>
       <c r="H450">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="I450">
-        <v>550</v>
+        <v>590</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -16832,13 +16832,13 @@
         <v>360</v>
       </c>
       <c r="G452">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="H452">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="I452">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="453" ht="20" customHeight="1">
@@ -16858,13 +16858,13 @@
         <v>3250</v>
       </c>
       <c r="G453">
-        <v>16.75</v>
+        <v>16.25</v>
       </c>
       <c r="H453">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I453">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="454" ht="20" customHeight="1">
@@ -17481,13 +17481,13 @@
         <v>65</v>
       </c>
       <c r="G478">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H478">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="I478">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="479" ht="20" customHeight="1">
@@ -17744,10 +17744,10 @@
         <v>105</v>
       </c>
       <c r="H488">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="I488">
-        <v>1500</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="489" ht="20" customHeight="1">
@@ -17868,10 +17868,10 @@
         <v>24300</v>
       </c>
       <c r="G493">
-        <v>242</v>
+        <v>243.5</v>
       </c>
       <c r="H493">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="I493">
         <v>1860</v>
@@ -18050,10 +18050,10 @@
         <v>12300</v>
       </c>
       <c r="G500">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H500">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I500">
         <v>1025</v>
@@ -18284,13 +18284,13 @@
         <v>2800</v>
       </c>
       <c r="G509">
-        <v>26.75</v>
+        <v>27</v>
       </c>
       <c r="H509">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I509">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="510" ht="20" customHeight="1">
@@ -18370,13 +18370,13 @@
         <v>1320</v>
       </c>
       <c r="G513">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="H513">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I513">
-        <v>144</v>
+        <v>160</v>
       </c>
     </row>
     <row r="514" ht="20" customHeight="1">
@@ -18604,13 +18604,13 @@
         <v>3000</v>
       </c>
       <c r="G522">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H522">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="I522">
-        <v>286</v>
+        <v>400</v>
       </c>
     </row>
     <row r="523" ht="20" customHeight="1">
@@ -18884,13 +18884,13 @@
         <v>230</v>
       </c>
       <c r="G533">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H533">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="I533">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="534" ht="20" customHeight="1">
@@ -19248,13 +19248,13 @@
         <v>70</v>
       </c>
       <c r="G547">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H547">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I547">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="548" ht="20" customHeight="1">
@@ -19274,13 +19274,13 @@
         <v>420</v>
       </c>
       <c r="G548">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="H548">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I548">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="549" ht="20" customHeight="1">
@@ -19326,13 +19326,13 @@
         <v>440</v>
       </c>
       <c r="G550">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="H550">
-        <v>9.25</v>
+        <v>11</v>
       </c>
       <c r="I550">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="551" ht="20" customHeight="1">
@@ -19690,13 +19690,13 @@
         <v>2730</v>
       </c>
       <c r="G564">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="H564">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="I564">
-        <v>210</v>
+        <v>142</v>
       </c>
     </row>
     <row r="565" ht="20" customHeight="1">
@@ -19794,13 +19794,13 @@
         <v>280</v>
       </c>
       <c r="G568">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="H568">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="I568">
-        <v>24</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="569" ht="20" customHeight="1">
@@ -20282,13 +20282,13 @@
         <v>640</v>
       </c>
       <c r="G587">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="H587">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I587">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="588" ht="20" customHeight="1">
@@ -20386,13 +20386,13 @@
         <v>2300</v>
       </c>
       <c r="G591">
-        <v>11.25</v>
+        <v>15</v>
       </c>
       <c r="H591">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="I591">
-        <v>200</v>
+        <v>260</v>
       </c>
     </row>
     <row r="592" ht="20" customHeight="1">
@@ -20695,13 +20695,13 @@
         <v>300</v>
       </c>
       <c r="G603">
-        <v>0.97</v>
+        <v>1.05</v>
       </c>
       <c r="H603">
-        <v>6.79</v>
+        <v>7.25</v>
       </c>
       <c r="I603">
-        <v>27.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="604" ht="20" customHeight="1">
@@ -21085,13 +21085,13 @@
         <v>37000</v>
       </c>
       <c r="G618">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="H618">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="I618">
-        <v>3380</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="619" ht="20" customHeight="1">
@@ -21501,13 +21501,13 @@
         <v>10500</v>
       </c>
       <c r="G634">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="H634">
-        <v>225</v>
+        <v>83</v>
       </c>
       <c r="I634">
-        <v>908</v>
+        <v>300</v>
       </c>
     </row>
     <row r="635" ht="20" customHeight="1">
@@ -21579,13 +21579,13 @@
         <v>360</v>
       </c>
       <c r="G637">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="H637">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="I637">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="638" ht="20" customHeight="1">
@@ -21657,13 +21657,13 @@
         <v>560</v>
       </c>
       <c r="G640">
-        <v>2.25</v>
+        <v>3.85</v>
       </c>
       <c r="H640">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="I640">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="641" ht="20" customHeight="1">
@@ -22021,13 +22021,13 @@
         <v>80</v>
       </c>
       <c r="G654">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H654">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="I654">
-        <v>7</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="655" ht="20" customHeight="1">
@@ -22411,13 +22411,13 @@
         <v>980</v>
       </c>
       <c r="G669">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="H669">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I669">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="670" ht="20" customHeight="1">
@@ -22437,10 +22437,10 @@
         <v>4800</v>
       </c>
       <c r="G670">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="H670">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I670">
         <v>428</v>
@@ -22567,13 +22567,13 @@
         <v>1655</v>
       </c>
       <c r="G675">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="H675">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I675">
-        <v>170</v>
+        <v>220</v>
       </c>
     </row>
     <row r="676" ht="20" customHeight="1">
@@ -23217,13 +23217,13 @@
         <v>2000</v>
       </c>
       <c r="G700">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H700">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="I700">
-        <v>216</v>
+        <v>310</v>
       </c>
     </row>
     <row r="701" ht="20" customHeight="1">
@@ -23269,13 +23269,13 @@
         <v>6500</v>
       </c>
       <c r="G702">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H702">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="I702">
-        <v>630</v>
+        <v>450</v>
       </c>
     </row>
     <row r="703" ht="20" customHeight="1">
@@ -23529,13 +23529,13 @@
         <v>5100</v>
       </c>
       <c r="G712">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H712">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="I712">
-        <v>340</v>
+        <v>250</v>
       </c>
     </row>
     <row r="713" ht="20" customHeight="1">
@@ -23607,13 +23607,13 @@
         <v>1500</v>
       </c>
       <c r="G715">
-        <v>25.25</v>
+        <v>25.5</v>
       </c>
       <c r="H715">
         <v>51.5</v>
       </c>
       <c r="I715">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="716" ht="20" customHeight="1">
@@ -23702,13 +23702,13 @@
         <v>9500</v>
       </c>
       <c r="G719">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H719">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="I719">
-        <v>828</v>
+        <v>999</v>
       </c>
     </row>
     <row r="720" ht="20" customHeight="1">
@@ -23806,13 +23806,13 @@
         <v>1700</v>
       </c>
       <c r="G723">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="H723">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I723">
-        <v>164</v>
+        <v>200</v>
       </c>
     </row>
     <row r="724" ht="20" customHeight="1">
@@ -23884,13 +23884,13 @@
         <v>1600</v>
       </c>
       <c r="G726">
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="H726">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="I726">
-        <v>136</v>
+        <v>232</v>
       </c>
     </row>
     <row r="727" ht="20" customHeight="1">
@@ -23962,13 +23962,13 @@
         <v>330</v>
       </c>
       <c r="G729">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="H729">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="I729">
-        <v>72</v>
+        <v>44</v>
       </c>
     </row>
     <row r="730" ht="20" customHeight="1">
@@ -24248,13 +24248,13 @@
         <v>3500</v>
       </c>
       <c r="G740">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H740">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="I740">
-        <v>326</v>
+        <v>385</v>
       </c>
     </row>
     <row r="741" ht="20" customHeight="1">
@@ -24326,13 +24326,13 @@
         <v>290</v>
       </c>
       <c r="G743">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="H743">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="I743">
-        <v>24</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="744" ht="20" customHeight="1">
@@ -24430,13 +24430,13 @@
         <v>2800</v>
       </c>
       <c r="G747">
-        <v>13.75</v>
+        <v>14.25</v>
       </c>
       <c r="H747">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I747">
-        <v>240</v>
+        <v>252</v>
       </c>
     </row>
     <row r="748" ht="20" customHeight="1">
@@ -24586,13 +24586,13 @@
         <v>520</v>
       </c>
       <c r="G753">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="H753">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="I753">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="754" ht="20" customHeight="1">
@@ -24655,13 +24655,13 @@
         <v>/images/pets/Wooly Rhino.png</v>
       </c>
       <c r="G756">
-        <v>0.67</v>
+        <v>1.35</v>
       </c>
       <c r="H756">
-        <v>4.15</v>
+        <v>7.6</v>
       </c>
       <c r="I756">
-        <v>17.6</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="757" ht="20" customHeight="1">
@@ -24817,7 +24817,7 @@
         <v>7.25</v>
       </c>
       <c r="I762">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="763" ht="20" customHeight="1">
@@ -24915,13 +24915,13 @@
         <v>1920</v>
       </c>
       <c r="G766">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H766">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I766">
-        <v>188</v>
+        <v>204</v>
       </c>
     </row>
     <row r="767" ht="20" customHeight="1">
@@ -24967,13 +24967,13 @@
         <v>300</v>
       </c>
       <c r="G768">
-        <v>1.05</v>
+        <v>1.73</v>
       </c>
       <c r="H768">
-        <v>6.1</v>
+        <v>9.5</v>
       </c>
       <c r="I768">
-        <v>25.4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="769" ht="20" customHeight="1"/>
@@ -25223,18 +25223,52 @@
         <v>/images/pets/Chihuahua.png</v>
       </c>
       <c r="G1008">
-        <v>1.33</v>
+        <v>0.51</v>
       </c>
       <c r="H1008">
-        <v>7.5</v>
+        <v>3.35</v>
       </c>
       <c r="I1008">
-        <v>31</v>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="str">
+        <v>Kiwi Kiwi</v>
+      </c>
+      <c r="B1009" t="str">
+        <v>/images/pets/Kiwi Kiwi.png</v>
+      </c>
+      <c r="G1009">
+        <v>3</v>
+      </c>
+      <c r="H1009">
+        <v>15</v>
+      </c>
+      <c r="I1009">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="str">
+        <v>Strawberry Tortle</v>
+      </c>
+      <c r="B1010" t="str">
+        <v>/images/pets/Strawberry Tortle.png</v>
+      </c>
+      <c r="G1010">
+        <v>29</v>
+      </c>
+      <c r="H1010">
+        <v>125</v>
+      </c>
+      <c r="I1010">
+        <v>515</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I1008"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1010"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -26897,7 +26931,7 @@
         <v>/images/pets/Buzzing Honeypot Hat.png</v>
       </c>
       <c r="F117">
-        <v>190</v>
+        <v>140</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -31538,7 +31572,7 @@
         <v>/images/pets/Hive Backpack.png</v>
       </c>
       <c r="F450">
-        <v>90</v>
+        <v>67</v>
       </c>
     </row>
     <row r="451" ht="20" customHeight="1">
@@ -33612,7 +33646,7 @@
         <v>/images/pets/Panda Cap.png</v>
       </c>
       <c r="F599">
-        <v>1100</v>
+        <v>800</v>
       </c>
     </row>
     <row r="600" ht="20" customHeight="1">
@@ -34429,7 +34463,7 @@
         <v>/images/pets/Queen Bee Slippers.png</v>
       </c>
       <c r="F658">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="659" ht="20" customHeight="1">
@@ -36450,7 +36484,7 @@
         <v>860</v>
       </c>
       <c r="F803">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="804" ht="20" customHeight="1">
@@ -36632,7 +36666,7 @@
         <v>940</v>
       </c>
       <c r="F816">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="817" ht="20" customHeight="1">
@@ -36660,7 +36694,7 @@
         <v>970</v>
       </c>
       <c r="F818">
-        <v>140</v>
+        <v>120</v>
       </c>
     </row>
     <row r="819" ht="20" customHeight="1">
@@ -40563,7 +40597,7 @@
         <v>3445</v>
       </c>
       <c r="D96">
-        <v>345</v>
+        <v>255</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -45996,7 +46030,7 @@
         <v>22500</v>
       </c>
       <c r="D510">
-        <v>1930</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="511" ht="20" customHeight="1">
@@ -52822,7 +52856,7 @@
         <v>60</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
